--- a/dataset/samsung_device_updates.xlsx
+++ b/dataset/samsung_device_updates.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C284"/>
+  <dimension ref="A1:C295"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -951,7 +951,7 @@
       <c r="C35" t="inlineStr">
         <is>
           <t>Galaxy S Series
-Galaxy S25</t>
+Galaxy S26</t>
         </is>
       </c>
     </row>
@@ -966,7 +966,7 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Galaxy S25+</t>
+          <t>Galaxy S26+</t>
         </is>
       </c>
     </row>
@@ -981,7 +981,8 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Galaxy S25 Ultra</t>
+          <t>Galaxy S26 Ultra
+Galaxy S25</t>
         </is>
       </c>
     </row>
@@ -996,7 +997,7 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Galaxy S25 Edge</t>
+          <t>Galaxy S25+</t>
         </is>
       </c>
     </row>
@@ -1011,8 +1012,7 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Galaxy S25 FE
-Galaxy S24</t>
+          <t>Galaxy S25 Ultra</t>
         </is>
       </c>
     </row>
@@ -1027,7 +1027,7 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Galaxy S24+</t>
+          <t>Galaxy S25 Edge</t>
         </is>
       </c>
     </row>
@@ -1042,7 +1042,8 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Galaxy S24 Ultra</t>
+          <t>Galaxy S25 FE
+Galaxy S24</t>
         </is>
       </c>
     </row>
@@ -1057,8 +1058,7 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Galaxy S24 FE
-Galaxy S23</t>
+          <t>Galaxy S24+</t>
         </is>
       </c>
     </row>
@@ -1073,7 +1073,7 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Galaxy S23+</t>
+          <t>Galaxy S24 Ultra</t>
         </is>
       </c>
     </row>
@@ -1088,7 +1088,8 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Galaxy S23 Ultra</t>
+          <t>Galaxy S24 FE
+Galaxy S23</t>
         </is>
       </c>
     </row>
@@ -1103,7 +1104,7 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Galaxy S23 FE</t>
+          <t>Galaxy S23+</t>
         </is>
       </c>
     </row>
@@ -1118,7 +1119,7 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Galaxy S25</t>
+          <t>Galaxy S23 Ultra</t>
         </is>
       </c>
     </row>
@@ -1133,7 +1134,7 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Galaxy S25+</t>
+          <t>Galaxy S23 FE</t>
         </is>
       </c>
     </row>
@@ -1148,7 +1149,7 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Galaxy S25 Ultra</t>
+          <t>Galaxy S26</t>
         </is>
       </c>
     </row>
@@ -1163,7 +1164,7 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Galaxy S25 Edge</t>
+          <t>Galaxy S26+</t>
         </is>
       </c>
     </row>
@@ -1178,7 +1179,7 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Galaxy S25 FE</t>
+          <t>Galaxy S26 Ultra</t>
         </is>
       </c>
     </row>
@@ -1193,7 +1194,7 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Galaxy S24</t>
+          <t>Galaxy S25</t>
         </is>
       </c>
     </row>
@@ -1208,7 +1209,7 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Galaxy S24+</t>
+          <t>Galaxy S25+</t>
         </is>
       </c>
     </row>
@@ -1223,7 +1224,7 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Galaxy S24 Ultra</t>
+          <t>Galaxy S25 Ultra</t>
         </is>
       </c>
     </row>
@@ -1238,7 +1239,7 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Galaxy S24 FE</t>
+          <t>Galaxy S25 Edge</t>
         </is>
       </c>
     </row>
@@ -1253,7 +1254,7 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Galaxy S23</t>
+          <t>Galaxy S25 FE</t>
         </is>
       </c>
     </row>
@@ -1268,7 +1269,7 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Galaxy S23+</t>
+          <t>Galaxy S24</t>
         </is>
       </c>
     </row>
@@ -1283,7 +1284,7 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Galaxy S23 Ultra</t>
+          <t>Galaxy S24+</t>
         </is>
       </c>
     </row>
@@ -1298,7 +1299,7 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Galaxy S23 FE</t>
+          <t>Galaxy S24 Ultra</t>
         </is>
       </c>
     </row>
@@ -1313,8 +1314,7 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Galaxy A Series
-Galaxy A56 5G</t>
+          <t>Galaxy S24 FE</t>
         </is>
       </c>
     </row>
@@ -1329,7 +1329,7 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Galaxy A56 5G</t>
+          <t>Galaxy S23</t>
         </is>
       </c>
     </row>
@@ -1344,8 +1344,7 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Enterprise Models
-Galaxy A53 5G</t>
+          <t>Galaxy S23+</t>
         </is>
       </c>
     </row>
@@ -1360,7 +1359,7 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Galaxy A54 5G</t>
+          <t>Galaxy S23 Ultra</t>
         </is>
       </c>
     </row>
@@ -1375,87 +1374,89 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
+          <t>Galaxy S23 FE</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" s="1" t="n">
+        <v>62</v>
+      </c>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>Monthly</t>
+        </is>
+      </c>
+      <c r="C64" t="inlineStr">
+        <is>
+          <t>Galaxy A Series
+Galaxy A56 5G</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" s="1" t="n">
+        <v>63</v>
+      </c>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>Monthly</t>
+        </is>
+      </c>
+      <c r="C65" t="inlineStr">
+        <is>
+          <t>Galaxy A56 5G</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" s="1" t="n">
+        <v>64</v>
+      </c>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>Monthly</t>
+        </is>
+      </c>
+      <c r="C66" t="inlineStr">
+        <is>
+          <t>Enterprise Models
+Galaxy A53 5G</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" s="1" t="n">
+        <v>65</v>
+      </c>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>Monthly</t>
+        </is>
+      </c>
+      <c r="C67" t="inlineStr">
+        <is>
+          <t>Galaxy A54 5G</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" s="1" t="n">
+        <v>66</v>
+      </c>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>Monthly</t>
+        </is>
+      </c>
+      <c r="C68" t="inlineStr">
+        <is>
           <t>Galaxy A55 5G
 Galaxy Tab Active5 Pro
 Galaxy XCover6 Pro</t>
         </is>
       </c>
     </row>
-    <row r="64">
-      <c r="A64" s="1" t="n">
-        <v>62</v>
-      </c>
-      <c r="B64" t="inlineStr">
-        <is>
-          <t>Monthly</t>
-        </is>
-      </c>
-      <c r="C64" t="inlineStr">
-        <is>
-          <t>Galaxy XCover7</t>
-        </is>
-      </c>
-    </row>
-    <row r="65">
-      <c r="A65" s="1" t="n">
-        <v>63</v>
-      </c>
-      <c r="B65" t="inlineStr">
-        <is>
-          <t>Monthly</t>
-        </is>
-      </c>
-      <c r="C65" t="inlineStr">
-        <is>
-          <t>Galaxy XCover7 Pro</t>
-        </is>
-      </c>
-    </row>
-    <row r="66">
-      <c r="A66" s="1" t="n">
-        <v>64</v>
-      </c>
-      <c r="B66" t="inlineStr">
-        <is>
-          <t>Monthly</t>
-        </is>
-      </c>
-      <c r="C66" t="inlineStr">
-        <is>
-          <t>Galaxy A53 5G</t>
-        </is>
-      </c>
-    </row>
-    <row r="67">
-      <c r="A67" s="1" t="n">
-        <v>65</v>
-      </c>
-      <c r="B67" t="inlineStr">
-        <is>
-          <t>Monthly</t>
-        </is>
-      </c>
-      <c r="C67" t="inlineStr">
-        <is>
-          <t>Galaxy A54 5G</t>
-        </is>
-      </c>
-    </row>
-    <row r="68">
-      <c r="A68" s="1" t="n">
-        <v>66</v>
-      </c>
-      <c r="B68" t="inlineStr">
-        <is>
-          <t>Monthly</t>
-        </is>
-      </c>
-      <c r="C68" t="inlineStr">
-        <is>
-          <t>Galaxy A55 5G</t>
-        </is>
-      </c>
-    </row>
     <row r="69">
       <c r="A69" s="1" t="n">
         <v>67</v>
@@ -1467,7 +1468,7 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Galaxy Tab Active5 Pro</t>
+          <t>Galaxy XCover7</t>
         </is>
       </c>
     </row>
@@ -1482,7 +1483,7 @@
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Galaxy XCover6 Pro</t>
+          <t>Galaxy XCover7 Pro</t>
         </is>
       </c>
     </row>
@@ -1497,7 +1498,7 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Galaxy XCover7</t>
+          <t>Galaxy A53 5G</t>
         </is>
       </c>
     </row>
@@ -1512,7 +1513,7 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Galaxy XCover7 Pro</t>
+          <t>Galaxy A54 5G</t>
         </is>
       </c>
     </row>
@@ -1522,10 +1523,85 @@
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>Quarterly</t>
+          <t>Monthly</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
+        <is>
+          <t>Galaxy A55 5G</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" s="1" t="n">
+        <v>72</v>
+      </c>
+      <c r="B74" t="inlineStr">
+        <is>
+          <t>Monthly</t>
+        </is>
+      </c>
+      <c r="C74" t="inlineStr">
+        <is>
+          <t>Galaxy Tab Active5 Pro</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" s="1" t="n">
+        <v>73</v>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>Monthly</t>
+        </is>
+      </c>
+      <c r="C75" t="inlineStr">
+        <is>
+          <t>Galaxy XCover6 Pro</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" s="1" t="n">
+        <v>74</v>
+      </c>
+      <c r="B76" t="inlineStr">
+        <is>
+          <t>Monthly</t>
+        </is>
+      </c>
+      <c r="C76" t="inlineStr">
+        <is>
+          <t>Galaxy XCover7</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" s="1" t="n">
+        <v>75</v>
+      </c>
+      <c r="B77" t="inlineStr">
+        <is>
+          <t>Monthly</t>
+        </is>
+      </c>
+      <c r="C77" t="inlineStr">
+        <is>
+          <t>Galaxy XCover7 Pro</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" s="1" t="n">
+        <v>76</v>
+      </c>
+      <c r="B78" t="inlineStr">
+        <is>
+          <t>Quarterly</t>
+        </is>
+      </c>
+      <c r="C78" t="inlineStr">
         <is>
           <t>Galaxy Foldable Series
 Galaxy Z Fold3 5G
@@ -1533,83 +1609,6 @@
         </is>
       </c>
     </row>
-    <row r="74">
-      <c r="A74" s="1" t="n">
-        <v>72</v>
-      </c>
-      <c r="B74" t="inlineStr">
-        <is>
-          <t>Quarterly</t>
-        </is>
-      </c>
-      <c r="C74" t="inlineStr">
-        <is>
-          <t>Galaxy Z Fold3 5G</t>
-        </is>
-      </c>
-    </row>
-    <row r="75">
-      <c r="A75" s="1" t="n">
-        <v>73</v>
-      </c>
-      <c r="B75" t="inlineStr">
-        <is>
-          <t>Quarterly</t>
-        </is>
-      </c>
-      <c r="C75" t="inlineStr">
-        <is>
-          <t>Galaxy Z Flip3 5G</t>
-        </is>
-      </c>
-    </row>
-    <row r="76">
-      <c r="A76" s="1" t="n">
-        <v>74</v>
-      </c>
-      <c r="B76" t="inlineStr">
-        <is>
-          <t>Quarterly</t>
-        </is>
-      </c>
-      <c r="C76" t="inlineStr">
-        <is>
-          <t>Galaxy S Series
-Galaxy S22</t>
-        </is>
-      </c>
-    </row>
-    <row r="77">
-      <c r="A77" s="1" t="n">
-        <v>75</v>
-      </c>
-      <c r="B77" t="inlineStr">
-        <is>
-          <t>Quarterly</t>
-        </is>
-      </c>
-      <c r="C77" t="inlineStr">
-        <is>
-          <t>Galaxy S22+</t>
-        </is>
-      </c>
-    </row>
-    <row r="78">
-      <c r="A78" s="1" t="n">
-        <v>76</v>
-      </c>
-      <c r="B78" t="inlineStr">
-        <is>
-          <t>Quarterly</t>
-        </is>
-      </c>
-      <c r="C78" t="inlineStr">
-        <is>
-          <t>Galaxy S22 Ultra
-Galaxy S21 FE 5G</t>
-        </is>
-      </c>
-    </row>
     <row r="79">
       <c r="A79" s="1" t="n">
         <v>77</v>
@@ -1621,7 +1620,7 @@
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Galaxy S22</t>
+          <t>Galaxy Z Fold3 5G</t>
         </is>
       </c>
     </row>
@@ -1636,7 +1635,7 @@
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Galaxy S22+</t>
+          <t>Galaxy Z Flip3 5G</t>
         </is>
       </c>
     </row>
@@ -1651,7 +1650,8 @@
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Galaxy S22 Ultra</t>
+          <t>Galaxy S Series
+Galaxy S22</t>
         </is>
       </c>
     </row>
@@ -1666,7 +1666,7 @@
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Galaxy S21 FE 5G</t>
+          <t>Galaxy S22+</t>
         </is>
       </c>
     </row>
@@ -1681,8 +1681,8 @@
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Galaxy A Series
-Galaxy A04</t>
+          <t>Galaxy S22 Ultra
+Galaxy S21 FE 5G</t>
         </is>
       </c>
     </row>
@@ -1697,7 +1697,7 @@
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Galaxy A04s</t>
+          <t>Galaxy S22</t>
         </is>
       </c>
     </row>
@@ -1712,7 +1712,7 @@
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Galaxy A04e</t>
+          <t>Galaxy S22+</t>
         </is>
       </c>
     </row>
@@ -1727,7 +1727,7 @@
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Galaxy A05</t>
+          <t>Galaxy S22 Ultra</t>
         </is>
       </c>
     </row>
@@ -1742,7 +1742,7 @@
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Galaxy A05s</t>
+          <t>Galaxy S21 FE 5G</t>
         </is>
       </c>
     </row>
@@ -1757,7 +1757,8 @@
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Galaxy A06</t>
+          <t>Galaxy A Series
+Galaxy A04</t>
         </is>
       </c>
     </row>
@@ -1772,7 +1773,7 @@
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Galaxy A06 5G</t>
+          <t>Galaxy A04s</t>
         </is>
       </c>
     </row>
@@ -1787,8 +1788,7 @@
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Galaxy A07
-Galaxy A13</t>
+          <t>Galaxy A04e</t>
         </is>
       </c>
     </row>
@@ -1803,7 +1803,7 @@
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Galaxy A14</t>
+          <t>Galaxy A05</t>
         </is>
       </c>
     </row>
@@ -1818,7 +1818,7 @@
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Galaxy A14 5G</t>
+          <t>Galaxy A05s</t>
         </is>
       </c>
     </row>
@@ -1833,7 +1833,7 @@
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>Galaxy A15</t>
+          <t>Galaxy A06</t>
         </is>
       </c>
     </row>
@@ -1848,7 +1848,7 @@
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Galaxy A15 5G</t>
+          <t>Galaxy A06 5G</t>
         </is>
       </c>
     </row>
@@ -1863,7 +1863,7 @@
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>Galaxy A16</t>
+          <t>Galaxy A07</t>
         </is>
       </c>
     </row>
@@ -1878,7 +1878,8 @@
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>Galaxy A16 5G</t>
+          <t>Galaxy A07 5G
+Galaxy A13</t>
         </is>
       </c>
     </row>
@@ -1893,7 +1894,7 @@
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>Galaxy A17</t>
+          <t>Galaxy A14</t>
         </is>
       </c>
     </row>
@@ -1908,8 +1909,7 @@
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>Galaxy A17 5G
-Galaxy A23</t>
+          <t>Galaxy A14 5G</t>
         </is>
       </c>
     </row>
@@ -1924,7 +1924,7 @@
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>Galaxy A23 5G</t>
+          <t>Galaxy A15</t>
         </is>
       </c>
     </row>
@@ -1939,7 +1939,7 @@
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>Galaxy A24</t>
+          <t>Galaxy A15 5G</t>
         </is>
       </c>
     </row>
@@ -1954,7 +1954,7 @@
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>Galaxy A25 5G</t>
+          <t>Galaxy A16</t>
         </is>
       </c>
     </row>
@@ -1969,8 +1969,7 @@
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>Galaxy A26 5G
-Galaxy A33 5G</t>
+          <t>Galaxy A16 5G</t>
         </is>
       </c>
     </row>
@@ -1985,7 +1984,7 @@
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>Galaxy A34 5G</t>
+          <t>Galaxy A17</t>
         </is>
       </c>
     </row>
@@ -2000,7 +1999,8 @@
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>Galaxy A35 5G</t>
+          <t>Galaxy A17 5G
+Galaxy A23</t>
         </is>
       </c>
     </row>
@@ -2015,8 +2015,7 @@
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>Galaxy A36 5G
-Galaxy A73 5G</t>
+          <t>Galaxy A23 5G</t>
         </is>
       </c>
     </row>
@@ -2031,7 +2030,7 @@
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>Galaxy A04</t>
+          <t>Galaxy A24</t>
         </is>
       </c>
     </row>
@@ -2046,7 +2045,7 @@
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>Galaxy A04s</t>
+          <t>Galaxy A25 5G</t>
         </is>
       </c>
     </row>
@@ -2061,7 +2060,8 @@
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>Galaxy A04e</t>
+          <t>Galaxy A26 5G
+Galaxy A33 5G</t>
         </is>
       </c>
     </row>
@@ -2076,7 +2076,7 @@
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>Galaxy A05</t>
+          <t>Galaxy A34 5G</t>
         </is>
       </c>
     </row>
@@ -2091,7 +2091,7 @@
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>Galaxy A05s</t>
+          <t>Galaxy A35 5G</t>
         </is>
       </c>
     </row>
@@ -2106,7 +2106,8 @@
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>Galaxy A06</t>
+          <t>Galaxy A36 5G
+Galaxy A73 5G</t>
         </is>
       </c>
     </row>
@@ -2121,7 +2122,7 @@
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>Galaxy A06 5G</t>
+          <t>Galaxy A04</t>
         </is>
       </c>
     </row>
@@ -2136,7 +2137,7 @@
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>Galaxy A07</t>
+          <t>Galaxy A04s</t>
         </is>
       </c>
     </row>
@@ -2151,7 +2152,7 @@
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>Galaxy A13</t>
+          <t>Galaxy A04e</t>
         </is>
       </c>
     </row>
@@ -2166,7 +2167,7 @@
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>Galaxy A14</t>
+          <t>Galaxy A05</t>
         </is>
       </c>
     </row>
@@ -2181,7 +2182,7 @@
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>Galaxy A14 5G</t>
+          <t>Galaxy A05s</t>
         </is>
       </c>
     </row>
@@ -2196,7 +2197,7 @@
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>Galaxy A15</t>
+          <t>Galaxy A06</t>
         </is>
       </c>
     </row>
@@ -2211,7 +2212,7 @@
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>Galaxy A15 5G</t>
+          <t>Galaxy A06 5G</t>
         </is>
       </c>
     </row>
@@ -2226,7 +2227,7 @@
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>Galaxy A16</t>
+          <t>Galaxy A07</t>
         </is>
       </c>
     </row>
@@ -2241,7 +2242,7 @@
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>Galaxy A16 5G</t>
+          <t>Galaxy A07 5G</t>
         </is>
       </c>
     </row>
@@ -2256,7 +2257,7 @@
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>Galaxy A17</t>
+          <t>Galaxy A13</t>
         </is>
       </c>
     </row>
@@ -2271,7 +2272,7 @@
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>Galaxy A17 5G</t>
+          <t>Galaxy A14</t>
         </is>
       </c>
     </row>
@@ -2286,7 +2287,7 @@
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>Galaxy A23</t>
+          <t>Galaxy A14 5G</t>
         </is>
       </c>
     </row>
@@ -2301,7 +2302,7 @@
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>Galaxy A23 5G</t>
+          <t>Galaxy A15</t>
         </is>
       </c>
     </row>
@@ -2316,7 +2317,7 @@
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>Galaxy A24</t>
+          <t>Galaxy A15 5G</t>
         </is>
       </c>
     </row>
@@ -2331,7 +2332,7 @@
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>Galaxy A25 5G</t>
+          <t>Galaxy A16</t>
         </is>
       </c>
     </row>
@@ -2346,7 +2347,7 @@
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>Galaxy A26 5G</t>
+          <t>Galaxy A16 5G</t>
         </is>
       </c>
     </row>
@@ -2361,7 +2362,7 @@
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>Galaxy A33 5G</t>
+          <t>Galaxy A17</t>
         </is>
       </c>
     </row>
@@ -2376,7 +2377,7 @@
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>Galaxy A34 5G</t>
+          <t>Galaxy A17 5G</t>
         </is>
       </c>
     </row>
@@ -2391,7 +2392,7 @@
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>Galaxy A35 5G</t>
+          <t>Galaxy A23</t>
         </is>
       </c>
     </row>
@@ -2406,7 +2407,7 @@
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>Galaxy A36 5G</t>
+          <t>Galaxy A23 5G</t>
         </is>
       </c>
     </row>
@@ -2421,7 +2422,7 @@
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>Galaxy A73 5G</t>
+          <t>Galaxy A24</t>
         </is>
       </c>
     </row>
@@ -2436,8 +2437,7 @@
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>Galaxy C Series
-Galaxy C55 5G</t>
+          <t>Galaxy A25 5G</t>
         </is>
       </c>
     </row>
@@ -2452,7 +2452,7 @@
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>Galaxy C55 5G</t>
+          <t>Galaxy A26 5G</t>
         </is>
       </c>
     </row>
@@ -2467,8 +2467,7 @@
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>Galaxy M Series
-Galaxy M04</t>
+          <t>Galaxy A33 5G</t>
         </is>
       </c>
     </row>
@@ -2483,7 +2482,7 @@
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>Galaxy M05</t>
+          <t>Galaxy A34 5G</t>
         </is>
       </c>
     </row>
@@ -2498,7 +2497,7 @@
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>Galaxy M06 5G</t>
+          <t>Galaxy A35 5G</t>
         </is>
       </c>
     </row>
@@ -2513,8 +2512,7 @@
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t>Galaxy M07
-Galaxy M13</t>
+          <t>Galaxy A36 5G</t>
         </is>
       </c>
     </row>
@@ -2529,7 +2527,7 @@
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t>Galaxy M13 5G</t>
+          <t>Galaxy A73 5G</t>
         </is>
       </c>
     </row>
@@ -2544,7 +2542,8 @@
       </c>
       <c r="C140" t="inlineStr">
         <is>
-          <t>Galaxy M14</t>
+          <t>Galaxy C Series
+Galaxy C55 5G</t>
         </is>
       </c>
     </row>
@@ -2559,7 +2558,7 @@
       </c>
       <c r="C141" t="inlineStr">
         <is>
-          <t>Galaxy M14 5G</t>
+          <t>Galaxy C55 5G</t>
         </is>
       </c>
     </row>
@@ -2574,7 +2573,8 @@
       </c>
       <c r="C142" t="inlineStr">
         <is>
-          <t>Galaxy M15 5G</t>
+          <t>Galaxy M Series
+Galaxy M04</t>
         </is>
       </c>
     </row>
@@ -2589,7 +2589,7 @@
       </c>
       <c r="C143" t="inlineStr">
         <is>
-          <t>Galaxy M16 5G</t>
+          <t>Galaxy M05</t>
         </is>
       </c>
     </row>
@@ -2604,9 +2604,7 @@
       </c>
       <c r="C144" t="inlineStr">
         <is>
-          <t>Galaxy M17 5G
-Galaxy M23 5G
-Galaxy M33 5G</t>
+          <t>Galaxy M06 5G</t>
         </is>
       </c>
     </row>
@@ -2621,7 +2619,8 @@
       </c>
       <c r="C145" t="inlineStr">
         <is>
-          <t>Galaxy M34 5G</t>
+          <t>Galaxy M07
+Galaxy M13</t>
         </is>
       </c>
     </row>
@@ -2636,7 +2635,7 @@
       </c>
       <c r="C146" t="inlineStr">
         <is>
-          <t>Galaxy M35 5G</t>
+          <t>Galaxy M13 5G</t>
         </is>
       </c>
     </row>
@@ -2651,132 +2650,134 @@
       </c>
       <c r="C147" t="inlineStr">
         <is>
+          <t>Galaxy M14</t>
+        </is>
+      </c>
+    </row>
+    <row r="148">
+      <c r="A148" s="1" t="n">
+        <v>146</v>
+      </c>
+      <c r="B148" t="inlineStr">
+        <is>
+          <t>Quarterly</t>
+        </is>
+      </c>
+      <c r="C148" t="inlineStr">
+        <is>
+          <t>Galaxy M14 5G</t>
+        </is>
+      </c>
+    </row>
+    <row r="149">
+      <c r="A149" s="1" t="n">
+        <v>147</v>
+      </c>
+      <c r="B149" t="inlineStr">
+        <is>
+          <t>Quarterly</t>
+        </is>
+      </c>
+      <c r="C149" t="inlineStr">
+        <is>
+          <t>Galaxy M15 5G</t>
+        </is>
+      </c>
+    </row>
+    <row r="150">
+      <c r="A150" s="1" t="n">
+        <v>148</v>
+      </c>
+      <c r="B150" t="inlineStr">
+        <is>
+          <t>Quarterly</t>
+        </is>
+      </c>
+      <c r="C150" t="inlineStr">
+        <is>
+          <t>Galaxy M16 5G</t>
+        </is>
+      </c>
+    </row>
+    <row r="151">
+      <c r="A151" s="1" t="n">
+        <v>149</v>
+      </c>
+      <c r="B151" t="inlineStr">
+        <is>
+          <t>Quarterly</t>
+        </is>
+      </c>
+      <c r="C151" t="inlineStr">
+        <is>
+          <t>Galaxy M17 5G</t>
+        </is>
+      </c>
+    </row>
+    <row r="152">
+      <c r="A152" s="1" t="n">
+        <v>150</v>
+      </c>
+      <c r="B152" t="inlineStr">
+        <is>
+          <t>Quarterly</t>
+        </is>
+      </c>
+      <c r="C152" t="inlineStr">
+        <is>
+          <t>Galaxy M17e 5G
+Galaxy M23 5G
+Galaxy M33 5G</t>
+        </is>
+      </c>
+    </row>
+    <row r="153">
+      <c r="A153" s="1" t="n">
+        <v>151</v>
+      </c>
+      <c r="B153" t="inlineStr">
+        <is>
+          <t>Quarterly</t>
+        </is>
+      </c>
+      <c r="C153" t="inlineStr">
+        <is>
+          <t>Galaxy M34 5G</t>
+        </is>
+      </c>
+    </row>
+    <row r="154">
+      <c r="A154" s="1" t="n">
+        <v>152</v>
+      </c>
+      <c r="B154" t="inlineStr">
+        <is>
+          <t>Quarterly</t>
+        </is>
+      </c>
+      <c r="C154" t="inlineStr">
+        <is>
+          <t>Galaxy M35 5G</t>
+        </is>
+      </c>
+    </row>
+    <row r="155">
+      <c r="A155" s="1" t="n">
+        <v>153</v>
+      </c>
+      <c r="B155" t="inlineStr">
+        <is>
+          <t>Quarterly</t>
+        </is>
+      </c>
+      <c r="C155" t="inlineStr">
+        <is>
           <t>Galaxy M36 5G
 Galaxy M44 5G
 Galaxy M53 5G</t>
         </is>
       </c>
     </row>
-    <row r="148">
-      <c r="A148" s="1" t="n">
-        <v>146</v>
-      </c>
-      <c r="B148" t="inlineStr">
-        <is>
-          <t>Quarterly</t>
-        </is>
-      </c>
-      <c r="C148" t="inlineStr">
-        <is>
-          <t>Galaxy M54 5G</t>
-        </is>
-      </c>
-    </row>
-    <row r="149">
-      <c r="A149" s="1" t="n">
-        <v>147</v>
-      </c>
-      <c r="B149" t="inlineStr">
-        <is>
-          <t>Quarterly</t>
-        </is>
-      </c>
-      <c r="C149" t="inlineStr">
-        <is>
-          <t>Galaxy M55 5G</t>
-        </is>
-      </c>
-    </row>
-    <row r="150">
-      <c r="A150" s="1" t="n">
-        <v>148</v>
-      </c>
-      <c r="B150" t="inlineStr">
-        <is>
-          <t>Quarterly</t>
-        </is>
-      </c>
-      <c r="C150" t="inlineStr">
-        <is>
-          <t>Galaxy M55s 5G</t>
-        </is>
-      </c>
-    </row>
-    <row r="151">
-      <c r="A151" s="1" t="n">
-        <v>149</v>
-      </c>
-      <c r="B151" t="inlineStr">
-        <is>
-          <t>Quarterly</t>
-        </is>
-      </c>
-      <c r="C151" t="inlineStr">
-        <is>
-          <t>Galaxy M56 5G</t>
-        </is>
-      </c>
-    </row>
-    <row r="152">
-      <c r="A152" s="1" t="n">
-        <v>150</v>
-      </c>
-      <c r="B152" t="inlineStr">
-        <is>
-          <t>Quarterly</t>
-        </is>
-      </c>
-      <c r="C152" t="inlineStr">
-        <is>
-          <t>Galaxy M04</t>
-        </is>
-      </c>
-    </row>
-    <row r="153">
-      <c r="A153" s="1" t="n">
-        <v>151</v>
-      </c>
-      <c r="B153" t="inlineStr">
-        <is>
-          <t>Quarterly</t>
-        </is>
-      </c>
-      <c r="C153" t="inlineStr">
-        <is>
-          <t>Galaxy M05</t>
-        </is>
-      </c>
-    </row>
-    <row r="154">
-      <c r="A154" s="1" t="n">
-        <v>152</v>
-      </c>
-      <c r="B154" t="inlineStr">
-        <is>
-          <t>Quarterly</t>
-        </is>
-      </c>
-      <c r="C154" t="inlineStr">
-        <is>
-          <t>Galaxy M06 5G</t>
-        </is>
-      </c>
-    </row>
-    <row r="155">
-      <c r="A155" s="1" t="n">
-        <v>153</v>
-      </c>
-      <c r="B155" t="inlineStr">
-        <is>
-          <t>Quarterly</t>
-        </is>
-      </c>
-      <c r="C155" t="inlineStr">
-        <is>
-          <t>Galaxy M07</t>
-        </is>
-      </c>
-    </row>
     <row r="156">
       <c r="A156" s="1" t="n">
         <v>154</v>
@@ -2788,7 +2789,7 @@
       </c>
       <c r="C156" t="inlineStr">
         <is>
-          <t>Galaxy M13</t>
+          <t>Galaxy M54 5G</t>
         </is>
       </c>
     </row>
@@ -2803,7 +2804,7 @@
       </c>
       <c r="C157" t="inlineStr">
         <is>
-          <t>Galaxy M13 5G</t>
+          <t>Galaxy M55 5G</t>
         </is>
       </c>
     </row>
@@ -2818,7 +2819,7 @@
       </c>
       <c r="C158" t="inlineStr">
         <is>
-          <t>Galaxy M14</t>
+          <t>Galaxy M55s 5G</t>
         </is>
       </c>
     </row>
@@ -2833,7 +2834,7 @@
       </c>
       <c r="C159" t="inlineStr">
         <is>
-          <t>Galaxy M14 5G</t>
+          <t>Galaxy M56 5G</t>
         </is>
       </c>
     </row>
@@ -2848,7 +2849,7 @@
       </c>
       <c r="C160" t="inlineStr">
         <is>
-          <t>Galaxy M15 5G</t>
+          <t>Galaxy M04</t>
         </is>
       </c>
     </row>
@@ -2863,7 +2864,7 @@
       </c>
       <c r="C161" t="inlineStr">
         <is>
-          <t>Galaxy M16 5G</t>
+          <t>Galaxy M05</t>
         </is>
       </c>
     </row>
@@ -2878,7 +2879,7 @@
       </c>
       <c r="C162" t="inlineStr">
         <is>
-          <t>Galaxy M17 5G</t>
+          <t>Galaxy M06 5G</t>
         </is>
       </c>
     </row>
@@ -2893,7 +2894,7 @@
       </c>
       <c r="C163" t="inlineStr">
         <is>
-          <t>Galaxy M23 5G</t>
+          <t>Galaxy M07</t>
         </is>
       </c>
     </row>
@@ -2908,7 +2909,7 @@
       </c>
       <c r="C164" t="inlineStr">
         <is>
-          <t>Galaxy M33 5G</t>
+          <t>Galaxy M13</t>
         </is>
       </c>
     </row>
@@ -2923,7 +2924,7 @@
       </c>
       <c r="C165" t="inlineStr">
         <is>
-          <t>Galaxy M34 5G</t>
+          <t>Galaxy M13 5G</t>
         </is>
       </c>
     </row>
@@ -2938,7 +2939,7 @@
       </c>
       <c r="C166" t="inlineStr">
         <is>
-          <t>Galaxy M35 5G</t>
+          <t>Galaxy M14</t>
         </is>
       </c>
     </row>
@@ -2953,7 +2954,7 @@
       </c>
       <c r="C167" t="inlineStr">
         <is>
-          <t>Galaxy M36 5G</t>
+          <t>Galaxy M14 5G</t>
         </is>
       </c>
     </row>
@@ -2968,7 +2969,7 @@
       </c>
       <c r="C168" t="inlineStr">
         <is>
-          <t>Galaxy M44 5G</t>
+          <t>Galaxy M15 5G</t>
         </is>
       </c>
     </row>
@@ -2983,7 +2984,7 @@
       </c>
       <c r="C169" t="inlineStr">
         <is>
-          <t>Galaxy M53 5G</t>
+          <t>Galaxy M16 5G</t>
         </is>
       </c>
     </row>
@@ -2998,7 +2999,7 @@
       </c>
       <c r="C170" t="inlineStr">
         <is>
-          <t>Galaxy M54 5G</t>
+          <t>Galaxy M17 5G</t>
         </is>
       </c>
     </row>
@@ -3013,7 +3014,7 @@
       </c>
       <c r="C171" t="inlineStr">
         <is>
-          <t>Galaxy M55 5G</t>
+          <t>Galaxy M17e 5G</t>
         </is>
       </c>
     </row>
@@ -3028,7 +3029,7 @@
       </c>
       <c r="C172" t="inlineStr">
         <is>
-          <t>Galaxy M55s 5G</t>
+          <t>Galaxy M23 5G</t>
         </is>
       </c>
     </row>
@@ -3043,7 +3044,7 @@
       </c>
       <c r="C173" t="inlineStr">
         <is>
-          <t>Galaxy M56 5G</t>
+          <t>Galaxy M33 5G</t>
         </is>
       </c>
     </row>
@@ -3058,8 +3059,7 @@
       </c>
       <c r="C174" t="inlineStr">
         <is>
-          <t>Galaxy F Series
-Galaxy F04</t>
+          <t>Galaxy M34 5G</t>
         </is>
       </c>
     </row>
@@ -3074,7 +3074,7 @@
       </c>
       <c r="C175" t="inlineStr">
         <is>
-          <t>Galaxy F05</t>
+          <t>Galaxy M35 5G</t>
         </is>
       </c>
     </row>
@@ -3089,7 +3089,7 @@
       </c>
       <c r="C176" t="inlineStr">
         <is>
-          <t>Galaxy F06 5G</t>
+          <t>Galaxy M36 5G</t>
         </is>
       </c>
     </row>
@@ -3104,8 +3104,7 @@
       </c>
       <c r="C177" t="inlineStr">
         <is>
-          <t>Galaxy F07
-Galaxy F13</t>
+          <t>Galaxy M44 5G</t>
         </is>
       </c>
     </row>
@@ -3120,7 +3119,7 @@
       </c>
       <c r="C178" t="inlineStr">
         <is>
-          <t>Galaxy F14</t>
+          <t>Galaxy M53 5G</t>
         </is>
       </c>
     </row>
@@ -3135,7 +3134,7 @@
       </c>
       <c r="C179" t="inlineStr">
         <is>
-          <t>Galaxy F14 5G</t>
+          <t>Galaxy M54 5G</t>
         </is>
       </c>
     </row>
@@ -3150,7 +3149,7 @@
       </c>
       <c r="C180" t="inlineStr">
         <is>
-          <t>Galaxy F15 5G</t>
+          <t>Galaxy M55 5G</t>
         </is>
       </c>
     </row>
@@ -3165,7 +3164,7 @@
       </c>
       <c r="C181" t="inlineStr">
         <is>
-          <t>Galaxy F16 5G</t>
+          <t>Galaxy M55s 5G</t>
         </is>
       </c>
     </row>
@@ -3180,8 +3179,7 @@
       </c>
       <c r="C182" t="inlineStr">
         <is>
-          <t>Galaxy F17 5G
-Galaxy F34 5G</t>
+          <t>Galaxy M56 5G</t>
         </is>
       </c>
     </row>
@@ -3196,8 +3194,8 @@
       </c>
       <c r="C183" t="inlineStr">
         <is>
-          <t>Galaxy F36 5G
-Galaxy F54 5G</t>
+          <t>Galaxy F Series
+Galaxy F04</t>
         </is>
       </c>
     </row>
@@ -3212,7 +3210,7 @@
       </c>
       <c r="C184" t="inlineStr">
         <is>
-          <t>Galaxy F55 5G</t>
+          <t>Galaxy F05</t>
         </is>
       </c>
     </row>
@@ -3227,7 +3225,7 @@
       </c>
       <c r="C185" t="inlineStr">
         <is>
-          <t>Galaxy F56 5G</t>
+          <t>Galaxy F06 5G</t>
         </is>
       </c>
     </row>
@@ -3242,7 +3240,7 @@
       </c>
       <c r="C186" t="inlineStr">
         <is>
-          <t>Galaxy F04</t>
+          <t>Galaxy F07</t>
         </is>
       </c>
     </row>
@@ -3257,7 +3255,8 @@
       </c>
       <c r="C187" t="inlineStr">
         <is>
-          <t>Galaxy F05</t>
+          <t>Galaxy F70e 5G
+Galaxy F13</t>
         </is>
       </c>
     </row>
@@ -3272,7 +3271,7 @@
       </c>
       <c r="C188" t="inlineStr">
         <is>
-          <t>Galaxy F06 5G</t>
+          <t>Galaxy F14</t>
         </is>
       </c>
     </row>
@@ -3287,7 +3286,7 @@
       </c>
       <c r="C189" t="inlineStr">
         <is>
-          <t>Galaxy F07</t>
+          <t>Galaxy F14 5G</t>
         </is>
       </c>
     </row>
@@ -3302,7 +3301,7 @@
       </c>
       <c r="C190" t="inlineStr">
         <is>
-          <t>Galaxy F13</t>
+          <t>Galaxy F15 5G</t>
         </is>
       </c>
     </row>
@@ -3317,7 +3316,7 @@
       </c>
       <c r="C191" t="inlineStr">
         <is>
-          <t>Galaxy F14</t>
+          <t>Galaxy F16 5G</t>
         </is>
       </c>
     </row>
@@ -3332,7 +3331,8 @@
       </c>
       <c r="C192" t="inlineStr">
         <is>
-          <t>Galaxy F14 5G</t>
+          <t>Galaxy F17 5G
+Galaxy F34 5G</t>
         </is>
       </c>
     </row>
@@ -3347,7 +3347,8 @@
       </c>
       <c r="C193" t="inlineStr">
         <is>
-          <t>Galaxy F15 5G</t>
+          <t>Galaxy F36 5G
+Galaxy F54 5G</t>
         </is>
       </c>
     </row>
@@ -3362,7 +3363,7 @@
       </c>
       <c r="C194" t="inlineStr">
         <is>
-          <t>Galaxy F16 5G</t>
+          <t>Galaxy F55 5G</t>
         </is>
       </c>
     </row>
@@ -3377,7 +3378,7 @@
       </c>
       <c r="C195" t="inlineStr">
         <is>
-          <t>Galaxy F17 5G</t>
+          <t>Galaxy F56 5G</t>
         </is>
       </c>
     </row>
@@ -3392,7 +3393,7 @@
       </c>
       <c r="C196" t="inlineStr">
         <is>
-          <t>Galaxy F34 5G</t>
+          <t>Galaxy F04</t>
         </is>
       </c>
     </row>
@@ -3407,7 +3408,7 @@
       </c>
       <c r="C197" t="inlineStr">
         <is>
-          <t>Galaxy F36 5G</t>
+          <t>Galaxy F05</t>
         </is>
       </c>
     </row>
@@ -3422,7 +3423,7 @@
       </c>
       <c r="C198" t="inlineStr">
         <is>
-          <t>Galaxy F54 5G</t>
+          <t>Galaxy F06 5G</t>
         </is>
       </c>
     </row>
@@ -3437,7 +3438,7 @@
       </c>
       <c r="C199" t="inlineStr">
         <is>
-          <t>Galaxy F55 5G</t>
+          <t>Galaxy F07</t>
         </is>
       </c>
     </row>
@@ -3452,7 +3453,7 @@
       </c>
       <c r="C200" t="inlineStr">
         <is>
-          <t>Galaxy F56 5G</t>
+          <t>Galaxy F70e 5G</t>
         </is>
       </c>
     </row>
@@ -3467,8 +3468,7 @@
       </c>
       <c r="C201" t="inlineStr">
         <is>
-          <t>Galaxy Tab S Series
-Galaxy Tab S11</t>
+          <t>Galaxy F13</t>
         </is>
       </c>
     </row>
@@ -3483,8 +3483,7 @@
       </c>
       <c r="C202" t="inlineStr">
         <is>
-          <t>Galaxy Tab S11 Ultra
-Galaxy Tab S10+</t>
+          <t>Galaxy F14</t>
         </is>
       </c>
     </row>
@@ -3499,7 +3498,7 @@
       </c>
       <c r="C203" t="inlineStr">
         <is>
-          <t>Galaxy Tab S10 Ultra</t>
+          <t>Galaxy F14 5G</t>
         </is>
       </c>
     </row>
@@ -3514,7 +3513,7 @@
       </c>
       <c r="C204" t="inlineStr">
         <is>
-          <t>Galaxy Tab S10 FE</t>
+          <t>Galaxy F15 5G</t>
         </is>
       </c>
     </row>
@@ -3529,7 +3528,7 @@
       </c>
       <c r="C205" t="inlineStr">
         <is>
-          <t>Galaxy Tab S10 FE+</t>
+          <t>Galaxy F16 5G</t>
         </is>
       </c>
     </row>
@@ -3544,8 +3543,7 @@
       </c>
       <c r="C206" t="inlineStr">
         <is>
-          <t>Galaxy Tab S10 Lite
-Galaxy Tab S9</t>
+          <t>Galaxy F17 5G</t>
         </is>
       </c>
     </row>
@@ -3560,7 +3558,7 @@
       </c>
       <c r="C207" t="inlineStr">
         <is>
-          <t>Galaxy Tab S9+</t>
+          <t>Galaxy F34 5G</t>
         </is>
       </c>
     </row>
@@ -3575,7 +3573,7 @@
       </c>
       <c r="C208" t="inlineStr">
         <is>
-          <t>Galaxy Tab S9 Ultra</t>
+          <t>Galaxy F36 5G</t>
         </is>
       </c>
     </row>
@@ -3590,7 +3588,7 @@
       </c>
       <c r="C209" t="inlineStr">
         <is>
-          <t>Galaxy Tab S9 FE</t>
+          <t>Galaxy F54 5G</t>
         </is>
       </c>
     </row>
@@ -3605,8 +3603,7 @@
       </c>
       <c r="C210" t="inlineStr">
         <is>
-          <t>Galaxy Tab S9 FE+
-Galaxy Tab S8</t>
+          <t>Galaxy F55 5G</t>
         </is>
       </c>
     </row>
@@ -3621,7 +3618,7 @@
       </c>
       <c r="C211" t="inlineStr">
         <is>
-          <t>Galaxy Tab S8+</t>
+          <t>Galaxy F56 5G</t>
         </is>
       </c>
     </row>
@@ -3636,8 +3633,8 @@
       </c>
       <c r="C212" t="inlineStr">
         <is>
-          <t>Galaxy Tab S8 Ultra
-Galaxy Tab S6 Lite (2024)</t>
+          <t>Galaxy Tab S Series
+Galaxy Tab S11</t>
         </is>
       </c>
     </row>
@@ -3652,7 +3649,8 @@
       </c>
       <c r="C213" t="inlineStr">
         <is>
-          <t>Galaxy Tab S11</t>
+          <t>Galaxy Tab S11 Ultra
+Galaxy Tab S10+</t>
         </is>
       </c>
     </row>
@@ -3667,7 +3665,7 @@
       </c>
       <c r="C214" t="inlineStr">
         <is>
-          <t>Galaxy Tab S11 Ultra</t>
+          <t>Galaxy Tab S10 Ultra</t>
         </is>
       </c>
     </row>
@@ -3682,7 +3680,7 @@
       </c>
       <c r="C215" t="inlineStr">
         <is>
-          <t>Galaxy Tab S10+</t>
+          <t>Galaxy Tab S10 FE</t>
         </is>
       </c>
     </row>
@@ -3697,7 +3695,7 @@
       </c>
       <c r="C216" t="inlineStr">
         <is>
-          <t>Galaxy Tab S10 Ultra</t>
+          <t>Galaxy Tab S10 FE+</t>
         </is>
       </c>
     </row>
@@ -3712,7 +3710,8 @@
       </c>
       <c r="C217" t="inlineStr">
         <is>
-          <t>Galaxy Tab S10 FE</t>
+          <t>Galaxy Tab S10 Lite
+Galaxy Tab S9</t>
         </is>
       </c>
     </row>
@@ -3727,7 +3726,7 @@
       </c>
       <c r="C218" t="inlineStr">
         <is>
-          <t>Galaxy Tab S10 FE+</t>
+          <t>Galaxy Tab S9+</t>
         </is>
       </c>
     </row>
@@ -3742,7 +3741,7 @@
       </c>
       <c r="C219" t="inlineStr">
         <is>
-          <t>Galaxy Tab S10 Lite</t>
+          <t>Galaxy Tab S9 Ultra</t>
         </is>
       </c>
     </row>
@@ -3757,7 +3756,7 @@
       </c>
       <c r="C220" t="inlineStr">
         <is>
-          <t>Galaxy Tab S9</t>
+          <t>Galaxy Tab S9 FE</t>
         </is>
       </c>
     </row>
@@ -3772,7 +3771,8 @@
       </c>
       <c r="C221" t="inlineStr">
         <is>
-          <t>Galaxy Tab S9+</t>
+          <t>Galaxy Tab S9 FE+
+Galaxy Tab S8</t>
         </is>
       </c>
     </row>
@@ -3787,7 +3787,7 @@
       </c>
       <c r="C222" t="inlineStr">
         <is>
-          <t>Galaxy Tab S9 Ultra</t>
+          <t>Galaxy Tab S8+</t>
         </is>
       </c>
     </row>
@@ -3802,7 +3802,8 @@
       </c>
       <c r="C223" t="inlineStr">
         <is>
-          <t>Galaxy Tab S9 FE</t>
+          <t>Galaxy Tab S8 Ultra
+Galaxy Tab S6 Lite (2024)</t>
         </is>
       </c>
     </row>
@@ -3817,7 +3818,7 @@
       </c>
       <c r="C224" t="inlineStr">
         <is>
-          <t>Galaxy Tab S9 FE+</t>
+          <t>Galaxy Tab S11</t>
         </is>
       </c>
     </row>
@@ -3832,7 +3833,7 @@
       </c>
       <c r="C225" t="inlineStr">
         <is>
-          <t>Galaxy Tab S8</t>
+          <t>Galaxy Tab S11 Ultra</t>
         </is>
       </c>
     </row>
@@ -3847,7 +3848,7 @@
       </c>
       <c r="C226" t="inlineStr">
         <is>
-          <t>Galaxy Tab S8+</t>
+          <t>Galaxy Tab S10+</t>
         </is>
       </c>
     </row>
@@ -3862,7 +3863,7 @@
       </c>
       <c r="C227" t="inlineStr">
         <is>
-          <t>Galaxy Tab S8 Ultra</t>
+          <t>Galaxy Tab S10 Ultra</t>
         </is>
       </c>
     </row>
@@ -3877,7 +3878,7 @@
       </c>
       <c r="C228" t="inlineStr">
         <is>
-          <t>Galaxy Tab S6 Lite (2024)</t>
+          <t>Galaxy Tab S10 FE</t>
         </is>
       </c>
     </row>
@@ -3892,8 +3893,7 @@
       </c>
       <c r="C229" t="inlineStr">
         <is>
-          <t>Galaxy Tab A Series
-Galaxy Tab A11</t>
+          <t>Galaxy Tab S10 FE+</t>
         </is>
       </c>
     </row>
@@ -3908,8 +3908,7 @@
       </c>
       <c r="C230" t="inlineStr">
         <is>
-          <t>Galaxy Tab A11+
-Galaxy Tab A9</t>
+          <t>Galaxy Tab S10 Lite</t>
         </is>
       </c>
     </row>
@@ -3924,7 +3923,7 @@
       </c>
       <c r="C231" t="inlineStr">
         <is>
-          <t>Galaxy Tab A9+</t>
+          <t>Galaxy Tab S9</t>
         </is>
       </c>
     </row>
@@ -3939,7 +3938,7 @@
       </c>
       <c r="C232" t="inlineStr">
         <is>
-          <t>Galaxy Tab A9+(2025)</t>
+          <t>Galaxy Tab S9+</t>
         </is>
       </c>
     </row>
@@ -3954,7 +3953,7 @@
       </c>
       <c r="C233" t="inlineStr">
         <is>
-          <t>Galaxy Tab A11</t>
+          <t>Galaxy Tab S9 Ultra</t>
         </is>
       </c>
     </row>
@@ -3969,7 +3968,7 @@
       </c>
       <c r="C234" t="inlineStr">
         <is>
-          <t>Galaxy Tab A11+</t>
+          <t>Galaxy Tab S9 FE</t>
         </is>
       </c>
     </row>
@@ -3984,7 +3983,7 @@
       </c>
       <c r="C235" t="inlineStr">
         <is>
-          <t>Galaxy Tab A9</t>
+          <t>Galaxy Tab S9 FE+</t>
         </is>
       </c>
     </row>
@@ -3999,7 +3998,7 @@
       </c>
       <c r="C236" t="inlineStr">
         <is>
-          <t>Galaxy Tab A9+</t>
+          <t>Galaxy Tab S8</t>
         </is>
       </c>
     </row>
@@ -4014,7 +4013,7 @@
       </c>
       <c r="C237" t="inlineStr">
         <is>
-          <t>Galaxy Tab A9+(2025)</t>
+          <t>Galaxy Tab S8+</t>
         </is>
       </c>
     </row>
@@ -4029,8 +4028,7 @@
       </c>
       <c r="C238" t="inlineStr">
         <is>
-          <t>Enterprise Models
-Galaxy Tab Active4 Pro</t>
+          <t>Galaxy Tab S8 Ultra</t>
         </is>
       </c>
     </row>
@@ -4045,8 +4043,7 @@
       </c>
       <c r="C239" t="inlineStr">
         <is>
-          <t>Galaxy Tab Active5
-Galaxy XCover5</t>
+          <t>Galaxy Tab S6 Lite (2024)</t>
         </is>
       </c>
     </row>
@@ -4061,7 +4058,8 @@
       </c>
       <c r="C240" t="inlineStr">
         <is>
-          <t>Galaxy Tab Active4 Pro</t>
+          <t>Galaxy Tab A Series
+Galaxy Tab A11</t>
         </is>
       </c>
     </row>
@@ -4076,7 +4074,8 @@
       </c>
       <c r="C241" t="inlineStr">
         <is>
-          <t>Galaxy Tab Active5</t>
+          <t>Galaxy Tab A11+
+Galaxy Tab A9</t>
         </is>
       </c>
     </row>
@@ -4091,7 +4090,7 @@
       </c>
       <c r="C242" t="inlineStr">
         <is>
-          <t>Galaxy XCover5</t>
+          <t>Galaxy Tab A9+</t>
         </is>
       </c>
     </row>
@@ -4106,8 +4105,7 @@
       </c>
       <c r="C243" t="inlineStr">
         <is>
-          <t>Galaxy Watch Series
-Galaxy Watch8 40mm</t>
+          <t>Galaxy Tab A9+(2025)</t>
         </is>
       </c>
     </row>
@@ -4122,7 +4120,7 @@
       </c>
       <c r="C244" t="inlineStr">
         <is>
-          <t>Galaxy Watch8 44mm</t>
+          <t>Galaxy Tab A11</t>
         </is>
       </c>
     </row>
@@ -4137,22 +4135,190 @@
       </c>
       <c r="C245" t="inlineStr">
         <is>
+          <t>Galaxy Tab A11+</t>
+        </is>
+      </c>
+    </row>
+    <row r="246">
+      <c r="A246" s="1" t="n">
+        <v>244</v>
+      </c>
+      <c r="B246" t="inlineStr">
+        <is>
+          <t>Quarterly</t>
+        </is>
+      </c>
+      <c r="C246" t="inlineStr">
+        <is>
+          <t>Galaxy Tab A9</t>
+        </is>
+      </c>
+    </row>
+    <row r="247">
+      <c r="A247" s="1" t="n">
+        <v>245</v>
+      </c>
+      <c r="B247" t="inlineStr">
+        <is>
+          <t>Quarterly</t>
+        </is>
+      </c>
+      <c r="C247" t="inlineStr">
+        <is>
+          <t>Galaxy Tab A9+</t>
+        </is>
+      </c>
+    </row>
+    <row r="248">
+      <c r="A248" s="1" t="n">
+        <v>246</v>
+      </c>
+      <c r="B248" t="inlineStr">
+        <is>
+          <t>Quarterly</t>
+        </is>
+      </c>
+      <c r="C248" t="inlineStr">
+        <is>
+          <t>Galaxy Tab A9+(2025)</t>
+        </is>
+      </c>
+    </row>
+    <row r="249">
+      <c r="A249" s="1" t="n">
+        <v>247</v>
+      </c>
+      <c r="B249" t="inlineStr">
+        <is>
+          <t>Quarterly</t>
+        </is>
+      </c>
+      <c r="C249" t="inlineStr">
+        <is>
+          <t>Enterprise Models
+Galaxy Tab Active4 Pro</t>
+        </is>
+      </c>
+    </row>
+    <row r="250">
+      <c r="A250" s="1" t="n">
+        <v>248</v>
+      </c>
+      <c r="B250" t="inlineStr">
+        <is>
+          <t>Quarterly</t>
+        </is>
+      </c>
+      <c r="C250" t="inlineStr">
+        <is>
+          <t>Galaxy Tab Active5
+Galaxy XCover5</t>
+        </is>
+      </c>
+    </row>
+    <row r="251">
+      <c r="A251" s="1" t="n">
+        <v>249</v>
+      </c>
+      <c r="B251" t="inlineStr">
+        <is>
+          <t>Quarterly</t>
+        </is>
+      </c>
+      <c r="C251" t="inlineStr">
+        <is>
+          <t>Galaxy Tab Active4 Pro</t>
+        </is>
+      </c>
+    </row>
+    <row r="252">
+      <c r="A252" s="1" t="n">
+        <v>250</v>
+      </c>
+      <c r="B252" t="inlineStr">
+        <is>
+          <t>Quarterly</t>
+        </is>
+      </c>
+      <c r="C252" t="inlineStr">
+        <is>
+          <t>Galaxy Tab Active5</t>
+        </is>
+      </c>
+    </row>
+    <row r="253">
+      <c r="A253" s="1" t="n">
+        <v>251</v>
+      </c>
+      <c r="B253" t="inlineStr">
+        <is>
+          <t>Quarterly</t>
+        </is>
+      </c>
+      <c r="C253" t="inlineStr">
+        <is>
+          <t>Galaxy XCover5</t>
+        </is>
+      </c>
+    </row>
+    <row r="254">
+      <c r="A254" s="1" t="n">
+        <v>252</v>
+      </c>
+      <c r="B254" t="inlineStr">
+        <is>
+          <t>Quarterly</t>
+        </is>
+      </c>
+      <c r="C254" t="inlineStr">
+        <is>
+          <t>Galaxy Watch Series
+Galaxy Watch8 40mm</t>
+        </is>
+      </c>
+    </row>
+    <row r="255">
+      <c r="A255" s="1" t="n">
+        <v>253</v>
+      </c>
+      <c r="B255" t="inlineStr">
+        <is>
+          <t>Quarterly</t>
+        </is>
+      </c>
+      <c r="C255" t="inlineStr">
+        <is>
+          <t>Galaxy Watch8 44mm</t>
+        </is>
+      </c>
+    </row>
+    <row r="256">
+      <c r="A256" s="1" t="n">
+        <v>254</v>
+      </c>
+      <c r="B256" t="inlineStr">
+        <is>
+          <t>Quarterly</t>
+        </is>
+      </c>
+      <c r="C256" t="inlineStr">
+        <is>
           <t>Galaxy Watch8 Classic 46mm
 Galaxy Watch Ultra
 Galaxy Watch7 40mm</t>
         </is>
       </c>
     </row>
-    <row r="246">
-      <c r="A246" s="1" t="n">
-        <v>244</v>
-      </c>
-      <c r="B246" t="inlineStr">
-        <is>
-          <t>Quarterly</t>
-        </is>
-      </c>
-      <c r="C246" t="inlineStr">
+    <row r="257">
+      <c r="A257" s="1" t="n">
+        <v>255</v>
+      </c>
+      <c r="B257" t="inlineStr">
+        <is>
+          <t>Quarterly</t>
+        </is>
+      </c>
+      <c r="C257" t="inlineStr">
         <is>
           <t>Galaxy Watch7 44mm
 Galaxy Watch FE
@@ -4160,173 +4326,6 @@
         </is>
       </c>
     </row>
-    <row r="247">
-      <c r="A247" s="1" t="n">
-        <v>245</v>
-      </c>
-      <c r="B247" t="inlineStr">
-        <is>
-          <t>Quarterly</t>
-        </is>
-      </c>
-      <c r="C247" t="inlineStr">
-        <is>
-          <t>Galaxy Watch6 44mm</t>
-        </is>
-      </c>
-    </row>
-    <row r="248">
-      <c r="A248" s="1" t="n">
-        <v>246</v>
-      </c>
-      <c r="B248" t="inlineStr">
-        <is>
-          <t>Quarterly</t>
-        </is>
-      </c>
-      <c r="C248" t="inlineStr">
-        <is>
-          <t>Galaxy Watch6 Classic 43mm</t>
-        </is>
-      </c>
-    </row>
-    <row r="249">
-      <c r="A249" s="1" t="n">
-        <v>247</v>
-      </c>
-      <c r="B249" t="inlineStr">
-        <is>
-          <t>Quarterly</t>
-        </is>
-      </c>
-      <c r="C249" t="inlineStr">
-        <is>
-          <t>Galaxy Watch6 Classic 47mm
-Galaxy Watch5 40mm</t>
-        </is>
-      </c>
-    </row>
-    <row r="250">
-      <c r="A250" s="1" t="n">
-        <v>248</v>
-      </c>
-      <c r="B250" t="inlineStr">
-        <is>
-          <t>Quarterly</t>
-        </is>
-      </c>
-      <c r="C250" t="inlineStr">
-        <is>
-          <t>Galaxy Watch5 44mm</t>
-        </is>
-      </c>
-    </row>
-    <row r="251">
-      <c r="A251" s="1" t="n">
-        <v>249</v>
-      </c>
-      <c r="B251" t="inlineStr">
-        <is>
-          <t>Quarterly</t>
-        </is>
-      </c>
-      <c r="C251" t="inlineStr">
-        <is>
-          <t>Galaxy Watch5 Pro
-Galaxy Watch4 40mm</t>
-        </is>
-      </c>
-    </row>
-    <row r="252">
-      <c r="A252" s="1" t="n">
-        <v>250</v>
-      </c>
-      <c r="B252" t="inlineStr">
-        <is>
-          <t>Quarterly</t>
-        </is>
-      </c>
-      <c r="C252" t="inlineStr">
-        <is>
-          <t>Galaxy Watch4 44mm</t>
-        </is>
-      </c>
-    </row>
-    <row r="253">
-      <c r="A253" s="1" t="n">
-        <v>251</v>
-      </c>
-      <c r="B253" t="inlineStr">
-        <is>
-          <t>Quarterly</t>
-        </is>
-      </c>
-      <c r="C253" t="inlineStr">
-        <is>
-          <t>Galaxy Watch4 Classic 42mm</t>
-        </is>
-      </c>
-    </row>
-    <row r="254">
-      <c r="A254" s="1" t="n">
-        <v>252</v>
-      </c>
-      <c r="B254" t="inlineStr">
-        <is>
-          <t>Quarterly</t>
-        </is>
-      </c>
-      <c r="C254" t="inlineStr">
-        <is>
-          <t>Galaxy Watch4 Classic 46mm</t>
-        </is>
-      </c>
-    </row>
-    <row r="255">
-      <c r="A255" s="1" t="n">
-        <v>253</v>
-      </c>
-      <c r="B255" t="inlineStr">
-        <is>
-          <t>Quarterly</t>
-        </is>
-      </c>
-      <c r="C255" t="inlineStr">
-        <is>
-          <t>Galaxy Watch8 40mm</t>
-        </is>
-      </c>
-    </row>
-    <row r="256">
-      <c r="A256" s="1" t="n">
-        <v>254</v>
-      </c>
-      <c r="B256" t="inlineStr">
-        <is>
-          <t>Quarterly</t>
-        </is>
-      </c>
-      <c r="C256" t="inlineStr">
-        <is>
-          <t>Galaxy Watch8 44mm</t>
-        </is>
-      </c>
-    </row>
-    <row r="257">
-      <c r="A257" s="1" t="n">
-        <v>255</v>
-      </c>
-      <c r="B257" t="inlineStr">
-        <is>
-          <t>Quarterly</t>
-        </is>
-      </c>
-      <c r="C257" t="inlineStr">
-        <is>
-          <t>Galaxy Watch8 Classic 46mm</t>
-        </is>
-      </c>
-    </row>
     <row r="258">
       <c r="A258" s="1" t="n">
         <v>256</v>
@@ -4338,7 +4337,7 @@
       </c>
       <c r="C258" t="inlineStr">
         <is>
-          <t>Galaxy Watch Ultra</t>
+          <t>Galaxy Watch6 44mm</t>
         </is>
       </c>
     </row>
@@ -4353,7 +4352,7 @@
       </c>
       <c r="C259" t="inlineStr">
         <is>
-          <t>Galaxy Watch7 40mm</t>
+          <t>Galaxy Watch6 Classic 43mm</t>
         </is>
       </c>
     </row>
@@ -4368,7 +4367,8 @@
       </c>
       <c r="C260" t="inlineStr">
         <is>
-          <t>Galaxy Watch7 44mm</t>
+          <t>Galaxy Watch6 Classic 47mm
+Galaxy Watch5 40mm</t>
         </is>
       </c>
     </row>
@@ -4383,7 +4383,7 @@
       </c>
       <c r="C261" t="inlineStr">
         <is>
-          <t>Galaxy Watch FE</t>
+          <t>Galaxy Watch5 44mm</t>
         </is>
       </c>
     </row>
@@ -4398,7 +4398,8 @@
       </c>
       <c r="C262" t="inlineStr">
         <is>
-          <t>Galaxy Watch6 40mm</t>
+          <t>Galaxy Watch5 Pro
+Galaxy Watch4 40mm</t>
         </is>
       </c>
     </row>
@@ -4413,7 +4414,7 @@
       </c>
       <c r="C263" t="inlineStr">
         <is>
-          <t>Galaxy Watch6 44mm</t>
+          <t>Galaxy Watch4 44mm</t>
         </is>
       </c>
     </row>
@@ -4428,7 +4429,7 @@
       </c>
       <c r="C264" t="inlineStr">
         <is>
-          <t>Galaxy Watch6 Classic 43mm</t>
+          <t>Galaxy Watch4 Classic 42mm</t>
         </is>
       </c>
     </row>
@@ -4443,7 +4444,7 @@
       </c>
       <c r="C265" t="inlineStr">
         <is>
-          <t>Galaxy Watch6 Classic 47mm</t>
+          <t>Galaxy Watch4 Classic 46mm</t>
         </is>
       </c>
     </row>
@@ -4458,7 +4459,7 @@
       </c>
       <c r="C266" t="inlineStr">
         <is>
-          <t>Galaxy Watch5 40mm</t>
+          <t>Galaxy Watch8 40mm</t>
         </is>
       </c>
     </row>
@@ -4473,7 +4474,7 @@
       </c>
       <c r="C267" t="inlineStr">
         <is>
-          <t>Galaxy Watch5 44mm</t>
+          <t>Galaxy Watch8 44mm</t>
         </is>
       </c>
     </row>
@@ -4488,7 +4489,7 @@
       </c>
       <c r="C268" t="inlineStr">
         <is>
-          <t>Galaxy Watch5 Pro</t>
+          <t>Galaxy Watch8 Classic 46mm</t>
         </is>
       </c>
     </row>
@@ -4503,7 +4504,7 @@
       </c>
       <c r="C269" t="inlineStr">
         <is>
-          <t>Galaxy Watch4 40mm</t>
+          <t>Galaxy Watch Ultra</t>
         </is>
       </c>
     </row>
@@ -4518,7 +4519,7 @@
       </c>
       <c r="C270" t="inlineStr">
         <is>
-          <t>Galaxy Watch4 44mm</t>
+          <t>Galaxy Watch7 40mm</t>
         </is>
       </c>
     </row>
@@ -4533,7 +4534,7 @@
       </c>
       <c r="C271" t="inlineStr">
         <is>
-          <t>Galaxy Watch4 Classic 42mm</t>
+          <t>Galaxy Watch7 44mm</t>
         </is>
       </c>
     </row>
@@ -4548,7 +4549,7 @@
       </c>
       <c r="C272" t="inlineStr">
         <is>
-          <t>Galaxy Watch4 Classic 46mm</t>
+          <t>Galaxy Watch FE</t>
         </is>
       </c>
     </row>
@@ -4563,8 +4564,7 @@
       </c>
       <c r="C273" t="inlineStr">
         <is>
-          <t>Galaxy XR Series
-Galaxy XR</t>
+          <t>Galaxy Watch6 40mm</t>
         </is>
       </c>
     </row>
@@ -4579,7 +4579,7 @@
       </c>
       <c r="C274" t="inlineStr">
         <is>
-          <t>Galaxy XR</t>
+          <t>Galaxy Watch6 44mm</t>
         </is>
       </c>
     </row>
@@ -4589,13 +4589,12 @@
       </c>
       <c r="B275" t="inlineStr">
         <is>
-          <t>No Information</t>
+          <t>Quarterly</t>
         </is>
       </c>
       <c r="C275" t="inlineStr">
         <is>
-          <t>Galaxy Book Series
-Galaxy Book4 Ultra</t>
+          <t>Galaxy Watch6 Classic 43mm</t>
         </is>
       </c>
     </row>
@@ -4605,12 +4604,12 @@
       </c>
       <c r="B276" t="inlineStr">
         <is>
-          <t>No Information</t>
+          <t>Quarterly</t>
         </is>
       </c>
       <c r="C276" t="inlineStr">
         <is>
-          <t>Galaxy Book4 Pro</t>
+          <t>Galaxy Watch6 Classic 47mm</t>
         </is>
       </c>
     </row>
@@ -4620,12 +4619,12 @@
       </c>
       <c r="B277" t="inlineStr">
         <is>
-          <t>No Information</t>
+          <t>Quarterly</t>
         </is>
       </c>
       <c r="C277" t="inlineStr">
         <is>
-          <t>Galaxy Book4 Pro 360</t>
+          <t>Galaxy Watch5 40mm</t>
         </is>
       </c>
     </row>
@@ -4635,12 +4634,12 @@
       </c>
       <c r="B278" t="inlineStr">
         <is>
-          <t>No Information</t>
+          <t>Quarterly</t>
         </is>
       </c>
       <c r="C278" t="inlineStr">
         <is>
-          <t>Galaxy Book4 360</t>
+          <t>Galaxy Watch5 44mm</t>
         </is>
       </c>
     </row>
@@ -4650,12 +4649,12 @@
       </c>
       <c r="B279" t="inlineStr">
         <is>
-          <t>No Information</t>
+          <t>Quarterly</t>
         </is>
       </c>
       <c r="C279" t="inlineStr">
         <is>
-          <t>Galaxy Book4</t>
+          <t>Galaxy Watch5 Pro</t>
         </is>
       </c>
     </row>
@@ -4665,12 +4664,12 @@
       </c>
       <c r="B280" t="inlineStr">
         <is>
-          <t>No Information</t>
+          <t>Quarterly</t>
         </is>
       </c>
       <c r="C280" t="inlineStr">
         <is>
-          <t>Galaxy Book4 Ultra</t>
+          <t>Galaxy Watch4 40mm</t>
         </is>
       </c>
     </row>
@@ -4680,12 +4679,12 @@
       </c>
       <c r="B281" t="inlineStr">
         <is>
-          <t>No Information</t>
+          <t>Quarterly</t>
         </is>
       </c>
       <c r="C281" t="inlineStr">
         <is>
-          <t>Galaxy Book4 Pro</t>
+          <t>Galaxy Watch4 44mm</t>
         </is>
       </c>
     </row>
@@ -4695,12 +4694,12 @@
       </c>
       <c r="B282" t="inlineStr">
         <is>
-          <t>No Information</t>
+          <t>Quarterly</t>
         </is>
       </c>
       <c r="C282" t="inlineStr">
         <is>
-          <t>Galaxy Book4 Pro 360</t>
+          <t>Galaxy Watch4 Classic 42mm</t>
         </is>
       </c>
     </row>
@@ -4710,12 +4709,12 @@
       </c>
       <c r="B283" t="inlineStr">
         <is>
-          <t>No Information</t>
+          <t>Quarterly</t>
         </is>
       </c>
       <c r="C283" t="inlineStr">
         <is>
-          <t>Galaxy Book4 360</t>
+          <t>Galaxy Watch4 Classic 46mm</t>
         </is>
       </c>
     </row>
@@ -4725,10 +4724,177 @@
       </c>
       <c r="B284" t="inlineStr">
         <is>
+          <t>Quarterly</t>
+        </is>
+      </c>
+      <c r="C284" t="inlineStr">
+        <is>
+          <t>Galaxy XR Series
+Galaxy XR</t>
+        </is>
+      </c>
+    </row>
+    <row r="285">
+      <c r="A285" s="1" t="n">
+        <v>283</v>
+      </c>
+      <c r="B285" t="inlineStr">
+        <is>
+          <t>Quarterly</t>
+        </is>
+      </c>
+      <c r="C285" t="inlineStr">
+        <is>
+          <t>Galaxy XR</t>
+        </is>
+      </c>
+    </row>
+    <row r="286">
+      <c r="A286" s="1" t="n">
+        <v>284</v>
+      </c>
+      <c r="B286" t="inlineStr">
+        <is>
           <t>No Information</t>
         </is>
       </c>
-      <c r="C284" t="inlineStr">
+      <c r="C286" t="inlineStr">
+        <is>
+          <t>Galaxy Book Series
+Galaxy Book4 Ultra</t>
+        </is>
+      </c>
+    </row>
+    <row r="287">
+      <c r="A287" s="1" t="n">
+        <v>285</v>
+      </c>
+      <c r="B287" t="inlineStr">
+        <is>
+          <t>No Information</t>
+        </is>
+      </c>
+      <c r="C287" t="inlineStr">
+        <is>
+          <t>Galaxy Book4 Pro</t>
+        </is>
+      </c>
+    </row>
+    <row r="288">
+      <c r="A288" s="1" t="n">
+        <v>286</v>
+      </c>
+      <c r="B288" t="inlineStr">
+        <is>
+          <t>No Information</t>
+        </is>
+      </c>
+      <c r="C288" t="inlineStr">
+        <is>
+          <t>Galaxy Book4 Pro 360</t>
+        </is>
+      </c>
+    </row>
+    <row r="289">
+      <c r="A289" s="1" t="n">
+        <v>287</v>
+      </c>
+      <c r="B289" t="inlineStr">
+        <is>
+          <t>No Information</t>
+        </is>
+      </c>
+      <c r="C289" t="inlineStr">
+        <is>
+          <t>Galaxy Book4 360</t>
+        </is>
+      </c>
+    </row>
+    <row r="290">
+      <c r="A290" s="1" t="n">
+        <v>288</v>
+      </c>
+      <c r="B290" t="inlineStr">
+        <is>
+          <t>No Information</t>
+        </is>
+      </c>
+      <c r="C290" t="inlineStr">
+        <is>
+          <t>Galaxy Book4</t>
+        </is>
+      </c>
+    </row>
+    <row r="291">
+      <c r="A291" s="1" t="n">
+        <v>289</v>
+      </c>
+      <c r="B291" t="inlineStr">
+        <is>
+          <t>No Information</t>
+        </is>
+      </c>
+      <c r="C291" t="inlineStr">
+        <is>
+          <t>Galaxy Book4 Ultra</t>
+        </is>
+      </c>
+    </row>
+    <row r="292">
+      <c r="A292" s="1" t="n">
+        <v>290</v>
+      </c>
+      <c r="B292" t="inlineStr">
+        <is>
+          <t>No Information</t>
+        </is>
+      </c>
+      <c r="C292" t="inlineStr">
+        <is>
+          <t>Galaxy Book4 Pro</t>
+        </is>
+      </c>
+    </row>
+    <row r="293">
+      <c r="A293" s="1" t="n">
+        <v>291</v>
+      </c>
+      <c r="B293" t="inlineStr">
+        <is>
+          <t>No Information</t>
+        </is>
+      </c>
+      <c r="C293" t="inlineStr">
+        <is>
+          <t>Galaxy Book4 Pro 360</t>
+        </is>
+      </c>
+    </row>
+    <row r="294">
+      <c r="A294" s="1" t="n">
+        <v>292</v>
+      </c>
+      <c r="B294" t="inlineStr">
+        <is>
+          <t>No Information</t>
+        </is>
+      </c>
+      <c r="C294" t="inlineStr">
+        <is>
+          <t>Galaxy Book4 360</t>
+        </is>
+      </c>
+    </row>
+    <row r="295">
+      <c r="A295" s="1" t="n">
+        <v>293</v>
+      </c>
+      <c r="B295" t="inlineStr">
+        <is>
+          <t>No Information</t>
+        </is>
+      </c>
+      <c r="C295" t="inlineStr">
         <is>
           <t>Galaxy Book4</t>
         </is>

--- a/dataset/samsung_device_updates.xlsx
+++ b/dataset/samsung_device_updates.xlsx
@@ -1389,8 +1389,8 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Galaxy A Series
-Galaxy A56 5G</t>
+          <t>Enterprise Models
+Galaxy A53 5G</t>
         </is>
       </c>
     </row>
@@ -1405,7 +1405,7 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Galaxy A56 5G</t>
+          <t>Galaxy A54 5G</t>
         </is>
       </c>
     </row>
@@ -1420,8 +1420,7 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Enterprise Models
-Galaxy A53 5G</t>
+          <t>Galaxy A55 5G</t>
         </is>
       </c>
     </row>
@@ -1436,7 +1435,9 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Galaxy A54 5G</t>
+          <t>Galaxy A56 5G
+Galaxy Tab Active5 Pro
+Galaxy XCover6 Pro</t>
         </is>
       </c>
     </row>
@@ -1451,9 +1452,7 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Galaxy A55 5G
-Galaxy Tab Active5 Pro
-Galaxy XCover6 Pro</t>
+          <t>Galaxy XCover7</t>
         </is>
       </c>
     </row>
@@ -1468,7 +1467,7 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Galaxy XCover7</t>
+          <t>Galaxy XCover7 Pro</t>
         </is>
       </c>
     </row>
@@ -1483,7 +1482,7 @@
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Galaxy XCover7 Pro</t>
+          <t>Galaxy A53 5G</t>
         </is>
       </c>
     </row>
@@ -1498,7 +1497,7 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Galaxy A53 5G</t>
+          <t>Galaxy A54 5G</t>
         </is>
       </c>
     </row>
@@ -1513,7 +1512,7 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Galaxy A54 5G</t>
+          <t>Galaxy A55 5G</t>
         </is>
       </c>
     </row>
@@ -1528,7 +1527,7 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Galaxy A55 5G</t>
+          <t>Galaxy A56 5G</t>
         </is>
       </c>
     </row>

--- a/dataset/samsung_device_updates.xlsx
+++ b/dataset/samsung_device_updates.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C295"/>
+  <dimension ref="A1:C297"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1390,7 +1390,7 @@
       <c r="C64" t="inlineStr">
         <is>
           <t>Enterprise Models
-Galaxy A53 5G</t>
+Galaxy A54 5G</t>
         </is>
       </c>
     </row>
@@ -1405,7 +1405,7 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Galaxy A54 5G</t>
+          <t>Galaxy A55 5G</t>
         </is>
       </c>
     </row>
@@ -1420,7 +1420,7 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Galaxy A55 5G</t>
+          <t>Galaxy A56 5G</t>
         </is>
       </c>
     </row>
@@ -1435,7 +1435,7 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Galaxy A56 5G
+          <t>Galaxy A57 5G
 Galaxy Tab Active5 Pro
 Galaxy XCover6 Pro</t>
         </is>
@@ -1482,7 +1482,7 @@
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Galaxy A53 5G</t>
+          <t>Galaxy A54 5G</t>
         </is>
       </c>
     </row>
@@ -1497,7 +1497,7 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Galaxy A54 5G</t>
+          <t>Galaxy A55 5G</t>
         </is>
       </c>
     </row>
@@ -1512,7 +1512,7 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Galaxy A55 5G</t>
+          <t>Galaxy A56 5G</t>
         </is>
       </c>
     </row>
@@ -1527,7 +1527,7 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Galaxy A56 5G</t>
+          <t>Galaxy A57 5G</t>
         </is>
       </c>
     </row>
@@ -2105,8 +2105,7 @@
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>Galaxy A36 5G
-Galaxy A73 5G</t>
+          <t>Galaxy A36 5G</t>
         </is>
       </c>
     </row>
@@ -2121,7 +2120,8 @@
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>Galaxy A04</t>
+          <t>Galaxy A37 5G
+Galaxy A73 5G</t>
         </is>
       </c>
     </row>
@@ -2136,7 +2136,7 @@
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>Galaxy A04s</t>
+          <t>Galaxy A04</t>
         </is>
       </c>
     </row>
@@ -2151,7 +2151,7 @@
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>Galaxy A04e</t>
+          <t>Galaxy A04s</t>
         </is>
       </c>
     </row>
@@ -2166,7 +2166,7 @@
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>Galaxy A05</t>
+          <t>Galaxy A04e</t>
         </is>
       </c>
     </row>
@@ -2181,7 +2181,7 @@
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>Galaxy A05s</t>
+          <t>Galaxy A05</t>
         </is>
       </c>
     </row>
@@ -2196,7 +2196,7 @@
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>Galaxy A06</t>
+          <t>Galaxy A05s</t>
         </is>
       </c>
     </row>
@@ -2211,7 +2211,7 @@
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>Galaxy A06 5G</t>
+          <t>Galaxy A06</t>
         </is>
       </c>
     </row>
@@ -2226,7 +2226,7 @@
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>Galaxy A07</t>
+          <t>Galaxy A06 5G</t>
         </is>
       </c>
     </row>
@@ -2241,7 +2241,7 @@
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>Galaxy A07 5G</t>
+          <t>Galaxy A07</t>
         </is>
       </c>
     </row>
@@ -2256,7 +2256,7 @@
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>Galaxy A13</t>
+          <t>Galaxy A07 5G</t>
         </is>
       </c>
     </row>
@@ -2271,7 +2271,7 @@
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>Galaxy A14</t>
+          <t>Galaxy A13</t>
         </is>
       </c>
     </row>
@@ -2286,7 +2286,7 @@
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>Galaxy A14 5G</t>
+          <t>Galaxy A14</t>
         </is>
       </c>
     </row>
@@ -2301,7 +2301,7 @@
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>Galaxy A15</t>
+          <t>Galaxy A14 5G</t>
         </is>
       </c>
     </row>
@@ -2316,7 +2316,7 @@
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>Galaxy A15 5G</t>
+          <t>Galaxy A15</t>
         </is>
       </c>
     </row>
@@ -2331,7 +2331,7 @@
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>Galaxy A16</t>
+          <t>Galaxy A15 5G</t>
         </is>
       </c>
     </row>
@@ -2346,7 +2346,7 @@
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>Galaxy A16 5G</t>
+          <t>Galaxy A16</t>
         </is>
       </c>
     </row>
@@ -2361,7 +2361,7 @@
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>Galaxy A17</t>
+          <t>Galaxy A16 5G</t>
         </is>
       </c>
     </row>
@@ -2376,7 +2376,7 @@
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>Galaxy A17 5G</t>
+          <t>Galaxy A17</t>
         </is>
       </c>
     </row>
@@ -2391,7 +2391,7 @@
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>Galaxy A23</t>
+          <t>Galaxy A17 5G</t>
         </is>
       </c>
     </row>
@@ -2406,7 +2406,7 @@
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>Galaxy A23 5G</t>
+          <t>Galaxy A23</t>
         </is>
       </c>
     </row>
@@ -2421,7 +2421,7 @@
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>Galaxy A24</t>
+          <t>Galaxy A23 5G</t>
         </is>
       </c>
     </row>
@@ -2436,7 +2436,7 @@
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>Galaxy A25 5G</t>
+          <t>Galaxy A24</t>
         </is>
       </c>
     </row>
@@ -2451,7 +2451,7 @@
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>Galaxy A26 5G</t>
+          <t>Galaxy A25 5G</t>
         </is>
       </c>
     </row>
@@ -2466,7 +2466,7 @@
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>Galaxy A33 5G</t>
+          <t>Galaxy A26 5G</t>
         </is>
       </c>
     </row>
@@ -2481,7 +2481,7 @@
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>Galaxy A34 5G</t>
+          <t>Galaxy A33 5G</t>
         </is>
       </c>
     </row>
@@ -2496,7 +2496,7 @@
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>Galaxy A35 5G</t>
+          <t>Galaxy A34 5G</t>
         </is>
       </c>
     </row>
@@ -2511,7 +2511,7 @@
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t>Galaxy A36 5G</t>
+          <t>Galaxy A35 5G</t>
         </is>
       </c>
     </row>
@@ -2526,7 +2526,7 @@
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t>Galaxy A73 5G</t>
+          <t>Galaxy A36 5G</t>
         </is>
       </c>
     </row>
@@ -2541,8 +2541,7 @@
       </c>
       <c r="C140" t="inlineStr">
         <is>
-          <t>Galaxy C Series
-Galaxy C55 5G</t>
+          <t>Galaxy A37 5G</t>
         </is>
       </c>
     </row>
@@ -2557,7 +2556,7 @@
       </c>
       <c r="C141" t="inlineStr">
         <is>
-          <t>Galaxy C55 5G</t>
+          <t>Galaxy A73 5G</t>
         </is>
       </c>
     </row>
@@ -2572,8 +2571,8 @@
       </c>
       <c r="C142" t="inlineStr">
         <is>
-          <t>Galaxy M Series
-Galaxy M04</t>
+          <t>Galaxy C Series
+Galaxy C55 5G</t>
         </is>
       </c>
     </row>
@@ -2588,7 +2587,7 @@
       </c>
       <c r="C143" t="inlineStr">
         <is>
-          <t>Galaxy M05</t>
+          <t>Galaxy C55 5G</t>
         </is>
       </c>
     </row>
@@ -2603,7 +2602,8 @@
       </c>
       <c r="C144" t="inlineStr">
         <is>
-          <t>Galaxy M06 5G</t>
+          <t>Galaxy M Series
+Galaxy M04</t>
         </is>
       </c>
     </row>
@@ -2618,8 +2618,7 @@
       </c>
       <c r="C145" t="inlineStr">
         <is>
-          <t>Galaxy M07
-Galaxy M13</t>
+          <t>Galaxy M05</t>
         </is>
       </c>
     </row>
@@ -2634,7 +2633,7 @@
       </c>
       <c r="C146" t="inlineStr">
         <is>
-          <t>Galaxy M13 5G</t>
+          <t>Galaxy M06 5G</t>
         </is>
       </c>
     </row>
@@ -2649,7 +2648,8 @@
       </c>
       <c r="C147" t="inlineStr">
         <is>
-          <t>Galaxy M14</t>
+          <t>Galaxy M07
+Galaxy M13</t>
         </is>
       </c>
     </row>
@@ -2664,7 +2664,7 @@
       </c>
       <c r="C148" t="inlineStr">
         <is>
-          <t>Galaxy M14 5G</t>
+          <t>Galaxy M13 5G</t>
         </is>
       </c>
     </row>
@@ -2679,7 +2679,7 @@
       </c>
       <c r="C149" t="inlineStr">
         <is>
-          <t>Galaxy M15 5G</t>
+          <t>Galaxy M14</t>
         </is>
       </c>
     </row>
@@ -2694,7 +2694,7 @@
       </c>
       <c r="C150" t="inlineStr">
         <is>
-          <t>Galaxy M16 5G</t>
+          <t>Galaxy M14 5G</t>
         </is>
       </c>
     </row>
@@ -2709,7 +2709,7 @@
       </c>
       <c r="C151" t="inlineStr">
         <is>
-          <t>Galaxy M17 5G</t>
+          <t>Galaxy M15 5G</t>
         </is>
       </c>
     </row>
@@ -2724,9 +2724,7 @@
       </c>
       <c r="C152" t="inlineStr">
         <is>
-          <t>Galaxy M17e 5G
-Galaxy M23 5G
-Galaxy M33 5G</t>
+          <t>Galaxy M16 5G</t>
         </is>
       </c>
     </row>
@@ -2741,7 +2739,7 @@
       </c>
       <c r="C153" t="inlineStr">
         <is>
-          <t>Galaxy M34 5G</t>
+          <t>Galaxy M17 5G</t>
         </is>
       </c>
     </row>
@@ -2756,7 +2754,8 @@
       </c>
       <c r="C154" t="inlineStr">
         <is>
-          <t>Galaxy M35 5G</t>
+          <t>Galaxy M17e 5G
+Galaxy M33 5G</t>
         </is>
       </c>
     </row>
@@ -2771,42 +2770,42 @@
       </c>
       <c r="C155" t="inlineStr">
         <is>
+          <t>Galaxy M34 5G</t>
+        </is>
+      </c>
+    </row>
+    <row r="156">
+      <c r="A156" s="1" t="n">
+        <v>154</v>
+      </c>
+      <c r="B156" t="inlineStr">
+        <is>
+          <t>Quarterly</t>
+        </is>
+      </c>
+      <c r="C156" t="inlineStr">
+        <is>
+          <t>Galaxy M35 5G</t>
+        </is>
+      </c>
+    </row>
+    <row r="157">
+      <c r="A157" s="1" t="n">
+        <v>155</v>
+      </c>
+      <c r="B157" t="inlineStr">
+        <is>
+          <t>Quarterly</t>
+        </is>
+      </c>
+      <c r="C157" t="inlineStr">
+        <is>
           <t>Galaxy M36 5G
 Galaxy M44 5G
 Galaxy M53 5G</t>
         </is>
       </c>
     </row>
-    <row r="156">
-      <c r="A156" s="1" t="n">
-        <v>154</v>
-      </c>
-      <c r="B156" t="inlineStr">
-        <is>
-          <t>Quarterly</t>
-        </is>
-      </c>
-      <c r="C156" t="inlineStr">
-        <is>
-          <t>Galaxy M54 5G</t>
-        </is>
-      </c>
-    </row>
-    <row r="157">
-      <c r="A157" s="1" t="n">
-        <v>155</v>
-      </c>
-      <c r="B157" t="inlineStr">
-        <is>
-          <t>Quarterly</t>
-        </is>
-      </c>
-      <c r="C157" t="inlineStr">
-        <is>
-          <t>Galaxy M55 5G</t>
-        </is>
-      </c>
-    </row>
     <row r="158">
       <c r="A158" s="1" t="n">
         <v>156</v>
@@ -2818,7 +2817,7 @@
       </c>
       <c r="C158" t="inlineStr">
         <is>
-          <t>Galaxy M55s 5G</t>
+          <t>Galaxy M54 5G</t>
         </is>
       </c>
     </row>
@@ -2833,7 +2832,7 @@
       </c>
       <c r="C159" t="inlineStr">
         <is>
-          <t>Galaxy M56 5G</t>
+          <t>Galaxy M55 5G</t>
         </is>
       </c>
     </row>
@@ -2848,7 +2847,7 @@
       </c>
       <c r="C160" t="inlineStr">
         <is>
-          <t>Galaxy M04</t>
+          <t>Galaxy M55s 5G</t>
         </is>
       </c>
     </row>
@@ -2863,7 +2862,7 @@
       </c>
       <c r="C161" t="inlineStr">
         <is>
-          <t>Galaxy M05</t>
+          <t>Galaxy M56 5G</t>
         </is>
       </c>
     </row>
@@ -2878,7 +2877,7 @@
       </c>
       <c r="C162" t="inlineStr">
         <is>
-          <t>Galaxy M06 5G</t>
+          <t>Galaxy M04</t>
         </is>
       </c>
     </row>
@@ -2893,7 +2892,7 @@
       </c>
       <c r="C163" t="inlineStr">
         <is>
-          <t>Galaxy M07</t>
+          <t>Galaxy M05</t>
         </is>
       </c>
     </row>
@@ -2908,7 +2907,7 @@
       </c>
       <c r="C164" t="inlineStr">
         <is>
-          <t>Galaxy M13</t>
+          <t>Galaxy M06 5G</t>
         </is>
       </c>
     </row>
@@ -2923,7 +2922,7 @@
       </c>
       <c r="C165" t="inlineStr">
         <is>
-          <t>Galaxy M13 5G</t>
+          <t>Galaxy M07</t>
         </is>
       </c>
     </row>
@@ -2938,7 +2937,7 @@
       </c>
       <c r="C166" t="inlineStr">
         <is>
-          <t>Galaxy M14</t>
+          <t>Galaxy M13</t>
         </is>
       </c>
     </row>
@@ -2953,7 +2952,7 @@
       </c>
       <c r="C167" t="inlineStr">
         <is>
-          <t>Galaxy M14 5G</t>
+          <t>Galaxy M13 5G</t>
         </is>
       </c>
     </row>
@@ -2968,7 +2967,7 @@
       </c>
       <c r="C168" t="inlineStr">
         <is>
-          <t>Galaxy M15 5G</t>
+          <t>Galaxy M14</t>
         </is>
       </c>
     </row>
@@ -2983,7 +2982,7 @@
       </c>
       <c r="C169" t="inlineStr">
         <is>
-          <t>Galaxy M16 5G</t>
+          <t>Galaxy M14 5G</t>
         </is>
       </c>
     </row>
@@ -2998,7 +2997,7 @@
       </c>
       <c r="C170" t="inlineStr">
         <is>
-          <t>Galaxy M17 5G</t>
+          <t>Galaxy M15 5G</t>
         </is>
       </c>
     </row>
@@ -3013,7 +3012,7 @@
       </c>
       <c r="C171" t="inlineStr">
         <is>
-          <t>Galaxy M17e 5G</t>
+          <t>Galaxy M16 5G</t>
         </is>
       </c>
     </row>
@@ -3028,7 +3027,7 @@
       </c>
       <c r="C172" t="inlineStr">
         <is>
-          <t>Galaxy M23 5G</t>
+          <t>Galaxy M17 5G</t>
         </is>
       </c>
     </row>
@@ -3043,7 +3042,7 @@
       </c>
       <c r="C173" t="inlineStr">
         <is>
-          <t>Galaxy M33 5G</t>
+          <t>Galaxy M17e 5G</t>
         </is>
       </c>
     </row>
@@ -3058,7 +3057,7 @@
       </c>
       <c r="C174" t="inlineStr">
         <is>
-          <t>Galaxy M34 5G</t>
+          <t>Galaxy M33 5G</t>
         </is>
       </c>
     </row>
@@ -3073,7 +3072,7 @@
       </c>
       <c r="C175" t="inlineStr">
         <is>
-          <t>Galaxy M35 5G</t>
+          <t>Galaxy M34 5G</t>
         </is>
       </c>
     </row>
@@ -3088,7 +3087,7 @@
       </c>
       <c r="C176" t="inlineStr">
         <is>
-          <t>Galaxy M36 5G</t>
+          <t>Galaxy M35 5G</t>
         </is>
       </c>
     </row>
@@ -3103,7 +3102,7 @@
       </c>
       <c r="C177" t="inlineStr">
         <is>
-          <t>Galaxy M44 5G</t>
+          <t>Galaxy M36 5G</t>
         </is>
       </c>
     </row>
@@ -3118,7 +3117,7 @@
       </c>
       <c r="C178" t="inlineStr">
         <is>
-          <t>Galaxy M53 5G</t>
+          <t>Galaxy M44 5G</t>
         </is>
       </c>
     </row>
@@ -3133,7 +3132,7 @@
       </c>
       <c r="C179" t="inlineStr">
         <is>
-          <t>Galaxy M54 5G</t>
+          <t>Galaxy M53 5G</t>
         </is>
       </c>
     </row>
@@ -3148,7 +3147,7 @@
       </c>
       <c r="C180" t="inlineStr">
         <is>
-          <t>Galaxy M55 5G</t>
+          <t>Galaxy M54 5G</t>
         </is>
       </c>
     </row>
@@ -3163,7 +3162,7 @@
       </c>
       <c r="C181" t="inlineStr">
         <is>
-          <t>Galaxy M55s 5G</t>
+          <t>Galaxy M55 5G</t>
         </is>
       </c>
     </row>
@@ -3178,7 +3177,7 @@
       </c>
       <c r="C182" t="inlineStr">
         <is>
-          <t>Galaxy M56 5G</t>
+          <t>Galaxy M55s 5G</t>
         </is>
       </c>
     </row>
@@ -3193,8 +3192,7 @@
       </c>
       <c r="C183" t="inlineStr">
         <is>
-          <t>Galaxy F Series
-Galaxy F04</t>
+          <t>Galaxy M56 5G</t>
         </is>
       </c>
     </row>
@@ -3209,7 +3207,8 @@
       </c>
       <c r="C184" t="inlineStr">
         <is>
-          <t>Galaxy F05</t>
+          <t>Galaxy F Series
+Galaxy F04</t>
         </is>
       </c>
     </row>
@@ -3224,7 +3223,7 @@
       </c>
       <c r="C185" t="inlineStr">
         <is>
-          <t>Galaxy F06 5G</t>
+          <t>Galaxy F05</t>
         </is>
       </c>
     </row>
@@ -3239,7 +3238,7 @@
       </c>
       <c r="C186" t="inlineStr">
         <is>
-          <t>Galaxy F07</t>
+          <t>Galaxy F06 5G</t>
         </is>
       </c>
     </row>
@@ -3254,8 +3253,7 @@
       </c>
       <c r="C187" t="inlineStr">
         <is>
-          <t>Galaxy F70e 5G
-Galaxy F13</t>
+          <t>Galaxy F07</t>
         </is>
       </c>
     </row>
@@ -3270,7 +3268,8 @@
       </c>
       <c r="C188" t="inlineStr">
         <is>
-          <t>Galaxy F14</t>
+          <t>Galaxy F70e 5G
+Galaxy F13</t>
         </is>
       </c>
     </row>
@@ -3285,7 +3284,7 @@
       </c>
       <c r="C189" t="inlineStr">
         <is>
-          <t>Galaxy F14 5G</t>
+          <t>Galaxy F14</t>
         </is>
       </c>
     </row>
@@ -3300,7 +3299,7 @@
       </c>
       <c r="C190" t="inlineStr">
         <is>
-          <t>Galaxy F15 5G</t>
+          <t>Galaxy F14 5G</t>
         </is>
       </c>
     </row>
@@ -3315,7 +3314,7 @@
       </c>
       <c r="C191" t="inlineStr">
         <is>
-          <t>Galaxy F16 5G</t>
+          <t>Galaxy F15 5G</t>
         </is>
       </c>
     </row>
@@ -3330,8 +3329,7 @@
       </c>
       <c r="C192" t="inlineStr">
         <is>
-          <t>Galaxy F17 5G
-Galaxy F34 5G</t>
+          <t>Galaxy F16 5G</t>
         </is>
       </c>
     </row>
@@ -3346,8 +3344,8 @@
       </c>
       <c r="C193" t="inlineStr">
         <is>
-          <t>Galaxy F36 5G
-Galaxy F54 5G</t>
+          <t>Galaxy F17 5G
+Galaxy F34 5G</t>
         </is>
       </c>
     </row>
@@ -3362,7 +3360,8 @@
       </c>
       <c r="C194" t="inlineStr">
         <is>
-          <t>Galaxy F55 5G</t>
+          <t>Galaxy F36 5G
+Galaxy F54 5G</t>
         </is>
       </c>
     </row>
@@ -3377,7 +3376,7 @@
       </c>
       <c r="C195" t="inlineStr">
         <is>
-          <t>Galaxy F56 5G</t>
+          <t>Galaxy F55 5G</t>
         </is>
       </c>
     </row>
@@ -3392,7 +3391,7 @@
       </c>
       <c r="C196" t="inlineStr">
         <is>
-          <t>Galaxy F04</t>
+          <t>Galaxy F56 5G</t>
         </is>
       </c>
     </row>
@@ -3407,7 +3406,7 @@
       </c>
       <c r="C197" t="inlineStr">
         <is>
-          <t>Galaxy F05</t>
+          <t>Galaxy F04</t>
         </is>
       </c>
     </row>
@@ -3422,7 +3421,7 @@
       </c>
       <c r="C198" t="inlineStr">
         <is>
-          <t>Galaxy F06 5G</t>
+          <t>Galaxy F05</t>
         </is>
       </c>
     </row>
@@ -3437,7 +3436,7 @@
       </c>
       <c r="C199" t="inlineStr">
         <is>
-          <t>Galaxy F07</t>
+          <t>Galaxy F06 5G</t>
         </is>
       </c>
     </row>
@@ -3452,7 +3451,7 @@
       </c>
       <c r="C200" t="inlineStr">
         <is>
-          <t>Galaxy F70e 5G</t>
+          <t>Galaxy F07</t>
         </is>
       </c>
     </row>
@@ -3467,7 +3466,7 @@
       </c>
       <c r="C201" t="inlineStr">
         <is>
-          <t>Galaxy F13</t>
+          <t>Galaxy F70e 5G</t>
         </is>
       </c>
     </row>
@@ -3482,7 +3481,7 @@
       </c>
       <c r="C202" t="inlineStr">
         <is>
-          <t>Galaxy F14</t>
+          <t>Galaxy F13</t>
         </is>
       </c>
     </row>
@@ -3497,7 +3496,7 @@
       </c>
       <c r="C203" t="inlineStr">
         <is>
-          <t>Galaxy F14 5G</t>
+          <t>Galaxy F14</t>
         </is>
       </c>
     </row>
@@ -3512,7 +3511,7 @@
       </c>
       <c r="C204" t="inlineStr">
         <is>
-          <t>Galaxy F15 5G</t>
+          <t>Galaxy F14 5G</t>
         </is>
       </c>
     </row>
@@ -3527,7 +3526,7 @@
       </c>
       <c r="C205" t="inlineStr">
         <is>
-          <t>Galaxy F16 5G</t>
+          <t>Galaxy F15 5G</t>
         </is>
       </c>
     </row>
@@ -3542,7 +3541,7 @@
       </c>
       <c r="C206" t="inlineStr">
         <is>
-          <t>Galaxy F17 5G</t>
+          <t>Galaxy F16 5G</t>
         </is>
       </c>
     </row>
@@ -3557,7 +3556,7 @@
       </c>
       <c r="C207" t="inlineStr">
         <is>
-          <t>Galaxy F34 5G</t>
+          <t>Galaxy F17 5G</t>
         </is>
       </c>
     </row>
@@ -3572,7 +3571,7 @@
       </c>
       <c r="C208" t="inlineStr">
         <is>
-          <t>Galaxy F36 5G</t>
+          <t>Galaxy F34 5G</t>
         </is>
       </c>
     </row>
@@ -3587,7 +3586,7 @@
       </c>
       <c r="C209" t="inlineStr">
         <is>
-          <t>Galaxy F54 5G</t>
+          <t>Galaxy F36 5G</t>
         </is>
       </c>
     </row>
@@ -3602,7 +3601,7 @@
       </c>
       <c r="C210" t="inlineStr">
         <is>
-          <t>Galaxy F55 5G</t>
+          <t>Galaxy F54 5G</t>
         </is>
       </c>
     </row>
@@ -3617,7 +3616,7 @@
       </c>
       <c r="C211" t="inlineStr">
         <is>
-          <t>Galaxy F56 5G</t>
+          <t>Galaxy F55 5G</t>
         </is>
       </c>
     </row>
@@ -3632,8 +3631,7 @@
       </c>
       <c r="C212" t="inlineStr">
         <is>
-          <t>Galaxy Tab S Series
-Galaxy Tab S11</t>
+          <t>Galaxy F56 5G</t>
         </is>
       </c>
     </row>
@@ -3648,8 +3646,8 @@
       </c>
       <c r="C213" t="inlineStr">
         <is>
-          <t>Galaxy Tab S11 Ultra
-Galaxy Tab S10+</t>
+          <t>Galaxy Tab S Series
+Galaxy Tab S11</t>
         </is>
       </c>
     </row>
@@ -3664,7 +3662,8 @@
       </c>
       <c r="C214" t="inlineStr">
         <is>
-          <t>Galaxy Tab S10 Ultra</t>
+          <t>Galaxy Tab S11 Ultra
+Galaxy Tab S10+</t>
         </is>
       </c>
     </row>
@@ -3679,7 +3678,7 @@
       </c>
       <c r="C215" t="inlineStr">
         <is>
-          <t>Galaxy Tab S10 FE</t>
+          <t>Galaxy Tab S10 Ultra</t>
         </is>
       </c>
     </row>
@@ -3694,7 +3693,7 @@
       </c>
       <c r="C216" t="inlineStr">
         <is>
-          <t>Galaxy Tab S10 FE+</t>
+          <t>Galaxy Tab S10 FE</t>
         </is>
       </c>
     </row>
@@ -3709,8 +3708,7 @@
       </c>
       <c r="C217" t="inlineStr">
         <is>
-          <t>Galaxy Tab S10 Lite
-Galaxy Tab S9</t>
+          <t>Galaxy Tab S10 FE+</t>
         </is>
       </c>
     </row>
@@ -3725,7 +3723,8 @@
       </c>
       <c r="C218" t="inlineStr">
         <is>
-          <t>Galaxy Tab S9+</t>
+          <t>Galaxy Tab S10 Lite
+Galaxy Tab S9</t>
         </is>
       </c>
     </row>
@@ -3740,7 +3739,7 @@
       </c>
       <c r="C219" t="inlineStr">
         <is>
-          <t>Galaxy Tab S9 Ultra</t>
+          <t>Galaxy Tab S9+</t>
         </is>
       </c>
     </row>
@@ -3755,7 +3754,7 @@
       </c>
       <c r="C220" t="inlineStr">
         <is>
-          <t>Galaxy Tab S9 FE</t>
+          <t>Galaxy Tab S9 Ultra</t>
         </is>
       </c>
     </row>
@@ -3770,8 +3769,7 @@
       </c>
       <c r="C221" t="inlineStr">
         <is>
-          <t>Galaxy Tab S9 FE+
-Galaxy Tab S8</t>
+          <t>Galaxy Tab S9 FE</t>
         </is>
       </c>
     </row>
@@ -3786,7 +3784,8 @@
       </c>
       <c r="C222" t="inlineStr">
         <is>
-          <t>Galaxy Tab S8+</t>
+          <t>Galaxy Tab S9 FE+
+Galaxy Tab S8</t>
         </is>
       </c>
     </row>
@@ -3801,8 +3800,7 @@
       </c>
       <c r="C223" t="inlineStr">
         <is>
-          <t>Galaxy Tab S8 Ultra
-Galaxy Tab S6 Lite (2024)</t>
+          <t>Galaxy Tab S8+</t>
         </is>
       </c>
     </row>
@@ -3817,7 +3815,8 @@
       </c>
       <c r="C224" t="inlineStr">
         <is>
-          <t>Galaxy Tab S11</t>
+          <t>Galaxy Tab S8 Ultra
+Galaxy Tab S6 Lite (2024)</t>
         </is>
       </c>
     </row>
@@ -3832,7 +3831,7 @@
       </c>
       <c r="C225" t="inlineStr">
         <is>
-          <t>Galaxy Tab S11 Ultra</t>
+          <t>Galaxy Tab S11</t>
         </is>
       </c>
     </row>
@@ -3847,7 +3846,7 @@
       </c>
       <c r="C226" t="inlineStr">
         <is>
-          <t>Galaxy Tab S10+</t>
+          <t>Galaxy Tab S11 Ultra</t>
         </is>
       </c>
     </row>
@@ -3862,7 +3861,7 @@
       </c>
       <c r="C227" t="inlineStr">
         <is>
-          <t>Galaxy Tab S10 Ultra</t>
+          <t>Galaxy Tab S10+</t>
         </is>
       </c>
     </row>
@@ -3877,7 +3876,7 @@
       </c>
       <c r="C228" t="inlineStr">
         <is>
-          <t>Galaxy Tab S10 FE</t>
+          <t>Galaxy Tab S10 Ultra</t>
         </is>
       </c>
     </row>
@@ -3892,7 +3891,7 @@
       </c>
       <c r="C229" t="inlineStr">
         <is>
-          <t>Galaxy Tab S10 FE+</t>
+          <t>Galaxy Tab S10 FE</t>
         </is>
       </c>
     </row>
@@ -3907,7 +3906,7 @@
       </c>
       <c r="C230" t="inlineStr">
         <is>
-          <t>Galaxy Tab S10 Lite</t>
+          <t>Galaxy Tab S10 FE+</t>
         </is>
       </c>
     </row>
@@ -3922,7 +3921,7 @@
       </c>
       <c r="C231" t="inlineStr">
         <is>
-          <t>Galaxy Tab S9</t>
+          <t>Galaxy Tab S10 Lite</t>
         </is>
       </c>
     </row>
@@ -3937,7 +3936,7 @@
       </c>
       <c r="C232" t="inlineStr">
         <is>
-          <t>Galaxy Tab S9+</t>
+          <t>Galaxy Tab S9</t>
         </is>
       </c>
     </row>
@@ -3952,7 +3951,7 @@
       </c>
       <c r="C233" t="inlineStr">
         <is>
-          <t>Galaxy Tab S9 Ultra</t>
+          <t>Galaxy Tab S9+</t>
         </is>
       </c>
     </row>
@@ -3967,7 +3966,7 @@
       </c>
       <c r="C234" t="inlineStr">
         <is>
-          <t>Galaxy Tab S9 FE</t>
+          <t>Galaxy Tab S9 Ultra</t>
         </is>
       </c>
     </row>
@@ -3982,7 +3981,7 @@
       </c>
       <c r="C235" t="inlineStr">
         <is>
-          <t>Galaxy Tab S9 FE+</t>
+          <t>Galaxy Tab S9 FE</t>
         </is>
       </c>
     </row>
@@ -3997,7 +3996,7 @@
       </c>
       <c r="C236" t="inlineStr">
         <is>
-          <t>Galaxy Tab S8</t>
+          <t>Galaxy Tab S9 FE+</t>
         </is>
       </c>
     </row>
@@ -4012,7 +4011,7 @@
       </c>
       <c r="C237" t="inlineStr">
         <is>
-          <t>Galaxy Tab S8+</t>
+          <t>Galaxy Tab S8</t>
         </is>
       </c>
     </row>
@@ -4027,7 +4026,7 @@
       </c>
       <c r="C238" t="inlineStr">
         <is>
-          <t>Galaxy Tab S8 Ultra</t>
+          <t>Galaxy Tab S8+</t>
         </is>
       </c>
     </row>
@@ -4042,7 +4041,7 @@
       </c>
       <c r="C239" t="inlineStr">
         <is>
-          <t>Galaxy Tab S6 Lite (2024)</t>
+          <t>Galaxy Tab S8 Ultra</t>
         </is>
       </c>
     </row>
@@ -4057,8 +4056,7 @@
       </c>
       <c r="C240" t="inlineStr">
         <is>
-          <t>Galaxy Tab A Series
-Galaxy Tab A11</t>
+          <t>Galaxy Tab S6 Lite (2024)</t>
         </is>
       </c>
     </row>
@@ -4073,8 +4071,8 @@
       </c>
       <c r="C241" t="inlineStr">
         <is>
-          <t>Galaxy Tab A11+
-Galaxy Tab A9</t>
+          <t>Galaxy Tab A Series
+Galaxy Tab A11</t>
         </is>
       </c>
     </row>
@@ -4089,7 +4087,8 @@
       </c>
       <c r="C242" t="inlineStr">
         <is>
-          <t>Galaxy Tab A9+</t>
+          <t>Galaxy Tab A11+
+Galaxy Tab A9</t>
         </is>
       </c>
     </row>
@@ -4104,7 +4103,7 @@
       </c>
       <c r="C243" t="inlineStr">
         <is>
-          <t>Galaxy Tab A9+(2025)</t>
+          <t>Galaxy Tab A9+</t>
         </is>
       </c>
     </row>
@@ -4119,7 +4118,7 @@
       </c>
       <c r="C244" t="inlineStr">
         <is>
-          <t>Galaxy Tab A11</t>
+          <t>Galaxy Tab A9+(2025)</t>
         </is>
       </c>
     </row>
@@ -4134,7 +4133,7 @@
       </c>
       <c r="C245" t="inlineStr">
         <is>
-          <t>Galaxy Tab A11+</t>
+          <t>Galaxy Tab A11</t>
         </is>
       </c>
     </row>
@@ -4149,7 +4148,7 @@
       </c>
       <c r="C246" t="inlineStr">
         <is>
-          <t>Galaxy Tab A9</t>
+          <t>Galaxy Tab A11+</t>
         </is>
       </c>
     </row>
@@ -4164,7 +4163,7 @@
       </c>
       <c r="C247" t="inlineStr">
         <is>
-          <t>Galaxy Tab A9+</t>
+          <t>Galaxy Tab A9</t>
         </is>
       </c>
     </row>
@@ -4179,7 +4178,7 @@
       </c>
       <c r="C248" t="inlineStr">
         <is>
-          <t>Galaxy Tab A9+(2025)</t>
+          <t>Galaxy Tab A9+</t>
         </is>
       </c>
     </row>
@@ -4194,8 +4193,7 @@
       </c>
       <c r="C249" t="inlineStr">
         <is>
-          <t>Enterprise Models
-Galaxy Tab Active4 Pro</t>
+          <t>Galaxy Tab A9+(2025)</t>
         </is>
       </c>
     </row>
@@ -4210,8 +4208,9 @@
       </c>
       <c r="C250" t="inlineStr">
         <is>
-          <t>Galaxy Tab Active5
-Galaxy XCover5</t>
+          <t>Enterprise Models
+Galaxy A53 5G 
+Galaxy Tab Active4 Pro</t>
         </is>
       </c>
     </row>
@@ -4226,7 +4225,8 @@
       </c>
       <c r="C251" t="inlineStr">
         <is>
-          <t>Galaxy Tab Active4 Pro</t>
+          <t>Galaxy Tab Active5
+Galaxy XCover5</t>
         </is>
       </c>
     </row>
@@ -4241,7 +4241,7 @@
       </c>
       <c r="C252" t="inlineStr">
         <is>
-          <t>Galaxy Tab Active5</t>
+          <t>Galaxy A53 5G</t>
         </is>
       </c>
     </row>
@@ -4256,7 +4256,7 @@
       </c>
       <c r="C253" t="inlineStr">
         <is>
-          <t>Galaxy XCover5</t>
+          <t>Galaxy Tab Active4 Pro</t>
         </is>
       </c>
     </row>
@@ -4271,8 +4271,7 @@
       </c>
       <c r="C254" t="inlineStr">
         <is>
-          <t>Galaxy Watch Series
-Galaxy Watch8 40mm</t>
+          <t>Galaxy Tab Active5</t>
         </is>
       </c>
     </row>
@@ -4287,7 +4286,7 @@
       </c>
       <c r="C255" t="inlineStr">
         <is>
-          <t>Galaxy Watch8 44mm</t>
+          <t>Galaxy XCover5</t>
         </is>
       </c>
     </row>
@@ -4302,22 +4301,53 @@
       </c>
       <c r="C256" t="inlineStr">
         <is>
+          <t>Galaxy Watch Series
+Galaxy Watch8 40mm</t>
+        </is>
+      </c>
+    </row>
+    <row r="257">
+      <c r="A257" s="1" t="n">
+        <v>255</v>
+      </c>
+      <c r="B257" t="inlineStr">
+        <is>
+          <t>Quarterly</t>
+        </is>
+      </c>
+      <c r="C257" t="inlineStr">
+        <is>
+          <t>Galaxy Watch8 44mm</t>
+        </is>
+      </c>
+    </row>
+    <row r="258">
+      <c r="A258" s="1" t="n">
+        <v>256</v>
+      </c>
+      <c r="B258" t="inlineStr">
+        <is>
+          <t>Quarterly</t>
+        </is>
+      </c>
+      <c r="C258" t="inlineStr">
+        <is>
           <t>Galaxy Watch8 Classic 46mm
 Galaxy Watch Ultra
 Galaxy Watch7 40mm</t>
         </is>
       </c>
     </row>
-    <row r="257">
-      <c r="A257" s="1" t="n">
-        <v>255</v>
-      </c>
-      <c r="B257" t="inlineStr">
-        <is>
-          <t>Quarterly</t>
-        </is>
-      </c>
-      <c r="C257" t="inlineStr">
+    <row r="259">
+      <c r="A259" s="1" t="n">
+        <v>257</v>
+      </c>
+      <c r="B259" t="inlineStr">
+        <is>
+          <t>Quarterly</t>
+        </is>
+      </c>
+      <c r="C259" t="inlineStr">
         <is>
           <t>Galaxy Watch7 44mm
 Galaxy Watch FE
@@ -4325,36 +4355,6 @@
         </is>
       </c>
     </row>
-    <row r="258">
-      <c r="A258" s="1" t="n">
-        <v>256</v>
-      </c>
-      <c r="B258" t="inlineStr">
-        <is>
-          <t>Quarterly</t>
-        </is>
-      </c>
-      <c r="C258" t="inlineStr">
-        <is>
-          <t>Galaxy Watch6 44mm</t>
-        </is>
-      </c>
-    </row>
-    <row r="259">
-      <c r="A259" s="1" t="n">
-        <v>257</v>
-      </c>
-      <c r="B259" t="inlineStr">
-        <is>
-          <t>Quarterly</t>
-        </is>
-      </c>
-      <c r="C259" t="inlineStr">
-        <is>
-          <t>Galaxy Watch6 Classic 43mm</t>
-        </is>
-      </c>
-    </row>
     <row r="260">
       <c r="A260" s="1" t="n">
         <v>258</v>
@@ -4366,8 +4366,7 @@
       </c>
       <c r="C260" t="inlineStr">
         <is>
-          <t>Galaxy Watch6 Classic 47mm
-Galaxy Watch5 40mm</t>
+          <t>Galaxy Watch6 44mm</t>
         </is>
       </c>
     </row>
@@ -4382,7 +4381,7 @@
       </c>
       <c r="C261" t="inlineStr">
         <is>
-          <t>Galaxy Watch5 44mm</t>
+          <t>Galaxy Watch6 Classic 43mm</t>
         </is>
       </c>
     </row>
@@ -4397,8 +4396,8 @@
       </c>
       <c r="C262" t="inlineStr">
         <is>
-          <t>Galaxy Watch5 Pro
-Galaxy Watch4 40mm</t>
+          <t>Galaxy Watch6 Classic 47mm
+Galaxy Watch5 40mm</t>
         </is>
       </c>
     </row>
@@ -4413,7 +4412,7 @@
       </c>
       <c r="C263" t="inlineStr">
         <is>
-          <t>Galaxy Watch4 44mm</t>
+          <t>Galaxy Watch5 44mm</t>
         </is>
       </c>
     </row>
@@ -4428,7 +4427,8 @@
       </c>
       <c r="C264" t="inlineStr">
         <is>
-          <t>Galaxy Watch4 Classic 42mm</t>
+          <t>Galaxy Watch5 Pro
+Galaxy Watch4 40mm</t>
         </is>
       </c>
     </row>
@@ -4443,7 +4443,7 @@
       </c>
       <c r="C265" t="inlineStr">
         <is>
-          <t>Galaxy Watch4 Classic 46mm</t>
+          <t>Galaxy Watch4 44mm</t>
         </is>
       </c>
     </row>
@@ -4458,7 +4458,7 @@
       </c>
       <c r="C266" t="inlineStr">
         <is>
-          <t>Galaxy Watch8 40mm</t>
+          <t>Galaxy Watch4 Classic 42mm</t>
         </is>
       </c>
     </row>
@@ -4473,7 +4473,7 @@
       </c>
       <c r="C267" t="inlineStr">
         <is>
-          <t>Galaxy Watch8 44mm</t>
+          <t>Galaxy Watch4 Classic 46mm</t>
         </is>
       </c>
     </row>
@@ -4488,7 +4488,7 @@
       </c>
       <c r="C268" t="inlineStr">
         <is>
-          <t>Galaxy Watch8 Classic 46mm</t>
+          <t>Galaxy Watch8 40mm</t>
         </is>
       </c>
     </row>
@@ -4503,7 +4503,7 @@
       </c>
       <c r="C269" t="inlineStr">
         <is>
-          <t>Galaxy Watch Ultra</t>
+          <t>Galaxy Watch8 44mm</t>
         </is>
       </c>
     </row>
@@ -4518,7 +4518,7 @@
       </c>
       <c r="C270" t="inlineStr">
         <is>
-          <t>Galaxy Watch7 40mm</t>
+          <t>Galaxy Watch8 Classic 46mm</t>
         </is>
       </c>
     </row>
@@ -4533,7 +4533,7 @@
       </c>
       <c r="C271" t="inlineStr">
         <is>
-          <t>Galaxy Watch7 44mm</t>
+          <t>Galaxy Watch Ultra</t>
         </is>
       </c>
     </row>
@@ -4548,7 +4548,7 @@
       </c>
       <c r="C272" t="inlineStr">
         <is>
-          <t>Galaxy Watch FE</t>
+          <t>Galaxy Watch7 40mm</t>
         </is>
       </c>
     </row>
@@ -4563,7 +4563,7 @@
       </c>
       <c r="C273" t="inlineStr">
         <is>
-          <t>Galaxy Watch6 40mm</t>
+          <t>Galaxy Watch7 44mm</t>
         </is>
       </c>
     </row>
@@ -4578,7 +4578,7 @@
       </c>
       <c r="C274" t="inlineStr">
         <is>
-          <t>Galaxy Watch6 44mm</t>
+          <t>Galaxy Watch FE</t>
         </is>
       </c>
     </row>
@@ -4593,7 +4593,7 @@
       </c>
       <c r="C275" t="inlineStr">
         <is>
-          <t>Galaxy Watch6 Classic 43mm</t>
+          <t>Galaxy Watch6 40mm</t>
         </is>
       </c>
     </row>
@@ -4608,7 +4608,7 @@
       </c>
       <c r="C276" t="inlineStr">
         <is>
-          <t>Galaxy Watch6 Classic 47mm</t>
+          <t>Galaxy Watch6 44mm</t>
         </is>
       </c>
     </row>
@@ -4623,7 +4623,7 @@
       </c>
       <c r="C277" t="inlineStr">
         <is>
-          <t>Galaxy Watch5 40mm</t>
+          <t>Galaxy Watch6 Classic 43mm</t>
         </is>
       </c>
     </row>
@@ -4638,7 +4638,7 @@
       </c>
       <c r="C278" t="inlineStr">
         <is>
-          <t>Galaxy Watch5 44mm</t>
+          <t>Galaxy Watch6 Classic 47mm</t>
         </is>
       </c>
     </row>
@@ -4653,7 +4653,7 @@
       </c>
       <c r="C279" t="inlineStr">
         <is>
-          <t>Galaxy Watch5 Pro</t>
+          <t>Galaxy Watch5 40mm</t>
         </is>
       </c>
     </row>
@@ -4668,7 +4668,7 @@
       </c>
       <c r="C280" t="inlineStr">
         <is>
-          <t>Galaxy Watch4 40mm</t>
+          <t>Galaxy Watch5 44mm</t>
         </is>
       </c>
     </row>
@@ -4683,7 +4683,7 @@
       </c>
       <c r="C281" t="inlineStr">
         <is>
-          <t>Galaxy Watch4 44mm</t>
+          <t>Galaxy Watch5 Pro</t>
         </is>
       </c>
     </row>
@@ -4698,7 +4698,7 @@
       </c>
       <c r="C282" t="inlineStr">
         <is>
-          <t>Galaxy Watch4 Classic 42mm</t>
+          <t>Galaxy Watch4 40mm</t>
         </is>
       </c>
     </row>
@@ -4713,7 +4713,7 @@
       </c>
       <c r="C283" t="inlineStr">
         <is>
-          <t>Galaxy Watch4 Classic 46mm</t>
+          <t>Galaxy Watch4 44mm</t>
         </is>
       </c>
     </row>
@@ -4728,8 +4728,7 @@
       </c>
       <c r="C284" t="inlineStr">
         <is>
-          <t>Galaxy XR Series
-Galaxy XR</t>
+          <t>Galaxy Watch4 Classic 42mm</t>
         </is>
       </c>
     </row>
@@ -4744,7 +4743,7 @@
       </c>
       <c r="C285" t="inlineStr">
         <is>
-          <t>Galaxy XR</t>
+          <t>Galaxy Watch4 Classic 46mm</t>
         </is>
       </c>
     </row>
@@ -4754,13 +4753,13 @@
       </c>
       <c r="B286" t="inlineStr">
         <is>
-          <t>No Information</t>
+          <t>Quarterly</t>
         </is>
       </c>
       <c r="C286" t="inlineStr">
         <is>
-          <t>Galaxy Book Series
-Galaxy Book4 Ultra</t>
+          <t>Galaxy XR Series
+Galaxy XR</t>
         </is>
       </c>
     </row>
@@ -4770,12 +4769,12 @@
       </c>
       <c r="B287" t="inlineStr">
         <is>
-          <t>No Information</t>
+          <t>Quarterly</t>
         </is>
       </c>
       <c r="C287" t="inlineStr">
         <is>
-          <t>Galaxy Book4 Pro</t>
+          <t>Galaxy XR</t>
         </is>
       </c>
     </row>
@@ -4790,7 +4789,8 @@
       </c>
       <c r="C288" t="inlineStr">
         <is>
-          <t>Galaxy Book4 Pro 360</t>
+          <t>Galaxy Book Series
+Galaxy Book4 Ultra</t>
         </is>
       </c>
     </row>
@@ -4805,7 +4805,7 @@
       </c>
       <c r="C289" t="inlineStr">
         <is>
-          <t>Galaxy Book4 360</t>
+          <t>Galaxy Book4 Pro</t>
         </is>
       </c>
     </row>
@@ -4820,7 +4820,7 @@
       </c>
       <c r="C290" t="inlineStr">
         <is>
-          <t>Galaxy Book4</t>
+          <t>Galaxy Book4 Pro 360</t>
         </is>
       </c>
     </row>
@@ -4835,7 +4835,7 @@
       </c>
       <c r="C291" t="inlineStr">
         <is>
-          <t>Galaxy Book4 Ultra</t>
+          <t>Galaxy Book4 360</t>
         </is>
       </c>
     </row>
@@ -4850,7 +4850,7 @@
       </c>
       <c r="C292" t="inlineStr">
         <is>
-          <t>Galaxy Book4 Pro</t>
+          <t>Galaxy Book4</t>
         </is>
       </c>
     </row>
@@ -4865,7 +4865,7 @@
       </c>
       <c r="C293" t="inlineStr">
         <is>
-          <t>Galaxy Book4 Pro 360</t>
+          <t>Galaxy Book4 Ultra</t>
         </is>
       </c>
     </row>
@@ -4880,7 +4880,7 @@
       </c>
       <c r="C294" t="inlineStr">
         <is>
-          <t>Galaxy Book4 360</t>
+          <t>Galaxy Book4 Pro</t>
         </is>
       </c>
     </row>
@@ -4894,6 +4894,36 @@
         </is>
       </c>
       <c r="C295" t="inlineStr">
+        <is>
+          <t>Galaxy Book4 Pro 360</t>
+        </is>
+      </c>
+    </row>
+    <row r="296">
+      <c r="A296" s="1" t="n">
+        <v>294</v>
+      </c>
+      <c r="B296" t="inlineStr">
+        <is>
+          <t>No Information</t>
+        </is>
+      </c>
+      <c r="C296" t="inlineStr">
+        <is>
+          <t>Galaxy Book4 360</t>
+        </is>
+      </c>
+    </row>
+    <row r="297">
+      <c r="A297" s="1" t="n">
+        <v>295</v>
+      </c>
+      <c r="B297" t="inlineStr">
+        <is>
+          <t>No Information</t>
+        </is>
+      </c>
+      <c r="C297" t="inlineStr">
         <is>
           <t>Galaxy Book4</t>
         </is>

--- a/dataset/samsung_device_updates.xlsx
+++ b/dataset/samsung_device_updates.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C297"/>
+  <dimension ref="A1:C291"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1878,7 +1878,7 @@
       <c r="C96" t="inlineStr">
         <is>
           <t>Galaxy A07 5G
-Galaxy A13</t>
+Galaxy A14</t>
         </is>
       </c>
     </row>
@@ -1893,7 +1893,7 @@
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>Galaxy A14</t>
+          <t>Galaxy A14 5G</t>
         </is>
       </c>
     </row>
@@ -1908,7 +1908,7 @@
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>Galaxy A14 5G</t>
+          <t>Galaxy A15</t>
         </is>
       </c>
     </row>
@@ -1923,7 +1923,7 @@
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>Galaxy A15</t>
+          <t>Galaxy A15 5G</t>
         </is>
       </c>
     </row>
@@ -1938,7 +1938,7 @@
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>Galaxy A15 5G</t>
+          <t>Galaxy A16</t>
         </is>
       </c>
     </row>
@@ -1953,7 +1953,7 @@
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>Galaxy A16</t>
+          <t>Galaxy A16 5G</t>
         </is>
       </c>
     </row>
@@ -1968,7 +1968,7 @@
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>Galaxy A16 5G</t>
+          <t>Galaxy A17</t>
         </is>
       </c>
     </row>
@@ -1983,7 +1983,8 @@
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>Galaxy A17</t>
+          <t>Galaxy A17 5G
+Galaxy A23 5G</t>
         </is>
       </c>
     </row>
@@ -1998,8 +1999,7 @@
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>Galaxy A17 5G
-Galaxy A23</t>
+          <t>Galaxy A24</t>
         </is>
       </c>
     </row>
@@ -2014,7 +2014,7 @@
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>Galaxy A23 5G</t>
+          <t>Galaxy A25 5G</t>
         </is>
       </c>
     </row>
@@ -2029,7 +2029,8 @@
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>Galaxy A24</t>
+          <t>Galaxy A26 5G
+Galaxy A33 5G</t>
         </is>
       </c>
     </row>
@@ -2044,7 +2045,7 @@
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>Galaxy A25 5G</t>
+          <t>Galaxy A34 5G</t>
         </is>
       </c>
     </row>
@@ -2059,8 +2060,7 @@
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>Galaxy A26 5G
-Galaxy A33 5G</t>
+          <t>Galaxy A35 5G</t>
         </is>
       </c>
     </row>
@@ -2075,7 +2075,7 @@
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>Galaxy A34 5G</t>
+          <t>Galaxy A36 5G</t>
         </is>
       </c>
     </row>
@@ -2090,7 +2090,8 @@
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>Galaxy A35 5G</t>
+          <t>Galaxy A37 5G
+Galaxy A73 5G</t>
         </is>
       </c>
     </row>
@@ -2105,7 +2106,7 @@
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>Galaxy A36 5G</t>
+          <t>Galaxy A04</t>
         </is>
       </c>
     </row>
@@ -2120,8 +2121,7 @@
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>Galaxy A37 5G
-Galaxy A73 5G</t>
+          <t>Galaxy A04s</t>
         </is>
       </c>
     </row>
@@ -2136,7 +2136,7 @@
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>Galaxy A04</t>
+          <t>Galaxy A04e</t>
         </is>
       </c>
     </row>
@@ -2151,7 +2151,7 @@
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>Galaxy A04s</t>
+          <t>Galaxy A05</t>
         </is>
       </c>
     </row>
@@ -2166,7 +2166,7 @@
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>Galaxy A04e</t>
+          <t>Galaxy A05s</t>
         </is>
       </c>
     </row>
@@ -2181,7 +2181,7 @@
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>Galaxy A05</t>
+          <t>Galaxy A06</t>
         </is>
       </c>
     </row>
@@ -2196,7 +2196,7 @@
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>Galaxy A05s</t>
+          <t>Galaxy A06 5G</t>
         </is>
       </c>
     </row>
@@ -2211,7 +2211,7 @@
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>Galaxy A06</t>
+          <t>Galaxy A07</t>
         </is>
       </c>
     </row>
@@ -2226,7 +2226,7 @@
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>Galaxy A06 5G</t>
+          <t>Galaxy A07 5G</t>
         </is>
       </c>
     </row>
@@ -2241,7 +2241,7 @@
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>Galaxy A07</t>
+          <t>Galaxy A14</t>
         </is>
       </c>
     </row>
@@ -2256,7 +2256,7 @@
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>Galaxy A07 5G</t>
+          <t>Galaxy A14 5G</t>
         </is>
       </c>
     </row>
@@ -2271,7 +2271,7 @@
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>Galaxy A13</t>
+          <t>Galaxy A15</t>
         </is>
       </c>
     </row>
@@ -2286,7 +2286,7 @@
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>Galaxy A14</t>
+          <t>Galaxy A15 5G</t>
         </is>
       </c>
     </row>
@@ -2301,7 +2301,7 @@
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>Galaxy A14 5G</t>
+          <t>Galaxy A16</t>
         </is>
       </c>
     </row>
@@ -2316,7 +2316,7 @@
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>Galaxy A15</t>
+          <t>Galaxy A16 5G</t>
         </is>
       </c>
     </row>
@@ -2331,7 +2331,7 @@
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>Galaxy A15 5G</t>
+          <t>Galaxy A17</t>
         </is>
       </c>
     </row>
@@ -2346,7 +2346,7 @@
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>Galaxy A16</t>
+          <t>Galaxy A17 5G</t>
         </is>
       </c>
     </row>
@@ -2361,7 +2361,7 @@
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>Galaxy A16 5G</t>
+          <t>Galaxy A23 5G</t>
         </is>
       </c>
     </row>
@@ -2376,7 +2376,7 @@
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>Galaxy A17</t>
+          <t>Galaxy A24</t>
         </is>
       </c>
     </row>
@@ -2391,7 +2391,7 @@
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>Galaxy A17 5G</t>
+          <t>Galaxy A25 5G</t>
         </is>
       </c>
     </row>
@@ -2406,7 +2406,7 @@
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>Galaxy A23</t>
+          <t>Galaxy A26 5G</t>
         </is>
       </c>
     </row>
@@ -2421,7 +2421,7 @@
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>Galaxy A23 5G</t>
+          <t>Galaxy A33 5G</t>
         </is>
       </c>
     </row>
@@ -2436,7 +2436,7 @@
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>Galaxy A24</t>
+          <t>Galaxy A34 5G</t>
         </is>
       </c>
     </row>
@@ -2451,7 +2451,7 @@
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>Galaxy A25 5G</t>
+          <t>Galaxy A35 5G</t>
         </is>
       </c>
     </row>
@@ -2466,7 +2466,7 @@
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>Galaxy A26 5G</t>
+          <t>Galaxy A36 5G</t>
         </is>
       </c>
     </row>
@@ -2481,7 +2481,7 @@
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>Galaxy A33 5G</t>
+          <t>Galaxy A37 5G</t>
         </is>
       </c>
     </row>
@@ -2496,7 +2496,7 @@
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>Galaxy A34 5G</t>
+          <t>Galaxy A73 5G</t>
         </is>
       </c>
     </row>
@@ -2511,7 +2511,8 @@
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t>Galaxy A35 5G</t>
+          <t>Galaxy C Series
+Galaxy C55 5G</t>
         </is>
       </c>
     </row>
@@ -2526,7 +2527,7 @@
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t>Galaxy A36 5G</t>
+          <t>Galaxy C55 5G</t>
         </is>
       </c>
     </row>
@@ -2541,7 +2542,8 @@
       </c>
       <c r="C140" t="inlineStr">
         <is>
-          <t>Galaxy A37 5G</t>
+          <t>Galaxy M Series
+Galaxy M04</t>
         </is>
       </c>
     </row>
@@ -2556,7 +2558,7 @@
       </c>
       <c r="C141" t="inlineStr">
         <is>
-          <t>Galaxy A73 5G</t>
+          <t>Galaxy M05</t>
         </is>
       </c>
     </row>
@@ -2571,8 +2573,7 @@
       </c>
       <c r="C142" t="inlineStr">
         <is>
-          <t>Galaxy C Series
-Galaxy C55 5G</t>
+          <t>Galaxy M06 5G</t>
         </is>
       </c>
     </row>
@@ -2587,7 +2588,8 @@
       </c>
       <c r="C143" t="inlineStr">
         <is>
-          <t>Galaxy C55 5G</t>
+          <t>Galaxy M07
+Galaxy M13</t>
         </is>
       </c>
     </row>
@@ -2602,8 +2604,7 @@
       </c>
       <c r="C144" t="inlineStr">
         <is>
-          <t>Galaxy M Series
-Galaxy M04</t>
+          <t>Galaxy M13 5G</t>
         </is>
       </c>
     </row>
@@ -2618,7 +2619,7 @@
       </c>
       <c r="C145" t="inlineStr">
         <is>
-          <t>Galaxy M05</t>
+          <t>Galaxy M14</t>
         </is>
       </c>
     </row>
@@ -2633,7 +2634,7 @@
       </c>
       <c r="C146" t="inlineStr">
         <is>
-          <t>Galaxy M06 5G</t>
+          <t>Galaxy M14 5G</t>
         </is>
       </c>
     </row>
@@ -2648,8 +2649,7 @@
       </c>
       <c r="C147" t="inlineStr">
         <is>
-          <t>Galaxy M07
-Galaxy M13</t>
+          <t>Galaxy M15 5G</t>
         </is>
       </c>
     </row>
@@ -2664,7 +2664,7 @@
       </c>
       <c r="C148" t="inlineStr">
         <is>
-          <t>Galaxy M13 5G</t>
+          <t>Galaxy M16 5G</t>
         </is>
       </c>
     </row>
@@ -2679,7 +2679,7 @@
       </c>
       <c r="C149" t="inlineStr">
         <is>
-          <t>Galaxy M14</t>
+          <t>Galaxy M17 5G</t>
         </is>
       </c>
     </row>
@@ -2694,7 +2694,8 @@
       </c>
       <c r="C150" t="inlineStr">
         <is>
-          <t>Galaxy M14 5G</t>
+          <t>Galaxy M17e 5G
+Galaxy M34 5G</t>
         </is>
       </c>
     </row>
@@ -2709,7 +2710,7 @@
       </c>
       <c r="C151" t="inlineStr">
         <is>
-          <t>Galaxy M15 5G</t>
+          <t>Galaxy M35 5G</t>
         </is>
       </c>
     </row>
@@ -2724,7 +2725,9 @@
       </c>
       <c r="C152" t="inlineStr">
         <is>
-          <t>Galaxy M16 5G</t>
+          <t>Galaxy M36 5G
+Galaxy M44 5G
+Galaxy M53 5G</t>
         </is>
       </c>
     </row>
@@ -2739,7 +2742,7 @@
       </c>
       <c r="C153" t="inlineStr">
         <is>
-          <t>Galaxy M17 5G</t>
+          <t>Galaxy M54 5G</t>
         </is>
       </c>
     </row>
@@ -2754,8 +2757,7 @@
       </c>
       <c r="C154" t="inlineStr">
         <is>
-          <t>Galaxy M17e 5G
-Galaxy M33 5G</t>
+          <t>Galaxy M55 5G</t>
         </is>
       </c>
     </row>
@@ -2770,7 +2772,7 @@
       </c>
       <c r="C155" t="inlineStr">
         <is>
-          <t>Galaxy M34 5G</t>
+          <t>Galaxy M55s 5G</t>
         </is>
       </c>
     </row>
@@ -2785,7 +2787,7 @@
       </c>
       <c r="C156" t="inlineStr">
         <is>
-          <t>Galaxy M35 5G</t>
+          <t>Galaxy M56 5G</t>
         </is>
       </c>
     </row>
@@ -2800,9 +2802,7 @@
       </c>
       <c r="C157" t="inlineStr">
         <is>
-          <t>Galaxy M36 5G
-Galaxy M44 5G
-Galaxy M53 5G</t>
+          <t>Galaxy M04</t>
         </is>
       </c>
     </row>
@@ -2817,7 +2817,7 @@
       </c>
       <c r="C158" t="inlineStr">
         <is>
-          <t>Galaxy M54 5G</t>
+          <t>Galaxy M05</t>
         </is>
       </c>
     </row>
@@ -2832,7 +2832,7 @@
       </c>
       <c r="C159" t="inlineStr">
         <is>
-          <t>Galaxy M55 5G</t>
+          <t>Galaxy M06 5G</t>
         </is>
       </c>
     </row>
@@ -2847,7 +2847,7 @@
       </c>
       <c r="C160" t="inlineStr">
         <is>
-          <t>Galaxy M55s 5G</t>
+          <t>Galaxy M07</t>
         </is>
       </c>
     </row>
@@ -2862,7 +2862,7 @@
       </c>
       <c r="C161" t="inlineStr">
         <is>
-          <t>Galaxy M56 5G</t>
+          <t>Galaxy M13</t>
         </is>
       </c>
     </row>
@@ -2877,7 +2877,7 @@
       </c>
       <c r="C162" t="inlineStr">
         <is>
-          <t>Galaxy M04</t>
+          <t>Galaxy M13 5G</t>
         </is>
       </c>
     </row>
@@ -2892,7 +2892,7 @@
       </c>
       <c r="C163" t="inlineStr">
         <is>
-          <t>Galaxy M05</t>
+          <t>Galaxy M14</t>
         </is>
       </c>
     </row>
@@ -2907,7 +2907,7 @@
       </c>
       <c r="C164" t="inlineStr">
         <is>
-          <t>Galaxy M06 5G</t>
+          <t>Galaxy M14 5G</t>
         </is>
       </c>
     </row>
@@ -2922,7 +2922,7 @@
       </c>
       <c r="C165" t="inlineStr">
         <is>
-          <t>Galaxy M07</t>
+          <t>Galaxy M15 5G</t>
         </is>
       </c>
     </row>
@@ -2937,7 +2937,7 @@
       </c>
       <c r="C166" t="inlineStr">
         <is>
-          <t>Galaxy M13</t>
+          <t>Galaxy M16 5G</t>
         </is>
       </c>
     </row>
@@ -2952,7 +2952,7 @@
       </c>
       <c r="C167" t="inlineStr">
         <is>
-          <t>Galaxy M13 5G</t>
+          <t>Galaxy M17 5G</t>
         </is>
       </c>
     </row>
@@ -2967,7 +2967,7 @@
       </c>
       <c r="C168" t="inlineStr">
         <is>
-          <t>Galaxy M14</t>
+          <t>Galaxy M17e 5G</t>
         </is>
       </c>
     </row>
@@ -2982,7 +2982,7 @@
       </c>
       <c r="C169" t="inlineStr">
         <is>
-          <t>Galaxy M14 5G</t>
+          <t>Galaxy M34 5G</t>
         </is>
       </c>
     </row>
@@ -2997,7 +2997,7 @@
       </c>
       <c r="C170" t="inlineStr">
         <is>
-          <t>Galaxy M15 5G</t>
+          <t>Galaxy M35 5G</t>
         </is>
       </c>
     </row>
@@ -3012,7 +3012,7 @@
       </c>
       <c r="C171" t="inlineStr">
         <is>
-          <t>Galaxy M16 5G</t>
+          <t>Galaxy M36 5G</t>
         </is>
       </c>
     </row>
@@ -3027,7 +3027,7 @@
       </c>
       <c r="C172" t="inlineStr">
         <is>
-          <t>Galaxy M17 5G</t>
+          <t>Galaxy M44 5G</t>
         </is>
       </c>
     </row>
@@ -3042,7 +3042,7 @@
       </c>
       <c r="C173" t="inlineStr">
         <is>
-          <t>Galaxy M17e 5G</t>
+          <t>Galaxy M53 5G</t>
         </is>
       </c>
     </row>
@@ -3057,7 +3057,7 @@
       </c>
       <c r="C174" t="inlineStr">
         <is>
-          <t>Galaxy M33 5G</t>
+          <t>Galaxy M54 5G</t>
         </is>
       </c>
     </row>
@@ -3072,7 +3072,7 @@
       </c>
       <c r="C175" t="inlineStr">
         <is>
-          <t>Galaxy M34 5G</t>
+          <t>Galaxy M55 5G</t>
         </is>
       </c>
     </row>
@@ -3087,7 +3087,7 @@
       </c>
       <c r="C176" t="inlineStr">
         <is>
-          <t>Galaxy M35 5G</t>
+          <t>Galaxy M55s 5G</t>
         </is>
       </c>
     </row>
@@ -3102,7 +3102,7 @@
       </c>
       <c r="C177" t="inlineStr">
         <is>
-          <t>Galaxy M36 5G</t>
+          <t>Galaxy M56 5G</t>
         </is>
       </c>
     </row>
@@ -3117,7 +3117,8 @@
       </c>
       <c r="C178" t="inlineStr">
         <is>
-          <t>Galaxy M44 5G</t>
+          <t>Galaxy F Series
+Galaxy F04</t>
         </is>
       </c>
     </row>
@@ -3132,7 +3133,7 @@
       </c>
       <c r="C179" t="inlineStr">
         <is>
-          <t>Galaxy M53 5G</t>
+          <t>Galaxy F05</t>
         </is>
       </c>
     </row>
@@ -3147,7 +3148,7 @@
       </c>
       <c r="C180" t="inlineStr">
         <is>
-          <t>Galaxy M54 5G</t>
+          <t>Galaxy F06 5G</t>
         </is>
       </c>
     </row>
@@ -3162,7 +3163,7 @@
       </c>
       <c r="C181" t="inlineStr">
         <is>
-          <t>Galaxy M55 5G</t>
+          <t>Galaxy F07</t>
         </is>
       </c>
     </row>
@@ -3177,7 +3178,8 @@
       </c>
       <c r="C182" t="inlineStr">
         <is>
-          <t>Galaxy M55s 5G</t>
+          <t>Galaxy F70e 5G
+Galaxy F13</t>
         </is>
       </c>
     </row>
@@ -3192,7 +3194,7 @@
       </c>
       <c r="C183" t="inlineStr">
         <is>
-          <t>Galaxy M56 5G</t>
+          <t>Galaxy F14</t>
         </is>
       </c>
     </row>
@@ -3207,8 +3209,7 @@
       </c>
       <c r="C184" t="inlineStr">
         <is>
-          <t>Galaxy F Series
-Galaxy F04</t>
+          <t>Galaxy F14 5G</t>
         </is>
       </c>
     </row>
@@ -3223,7 +3224,7 @@
       </c>
       <c r="C185" t="inlineStr">
         <is>
-          <t>Galaxy F05</t>
+          <t>Galaxy F15 5G</t>
         </is>
       </c>
     </row>
@@ -3238,7 +3239,7 @@
       </c>
       <c r="C186" t="inlineStr">
         <is>
-          <t>Galaxy F06 5G</t>
+          <t>Galaxy F16 5G</t>
         </is>
       </c>
     </row>
@@ -3253,7 +3254,8 @@
       </c>
       <c r="C187" t="inlineStr">
         <is>
-          <t>Galaxy F07</t>
+          <t>Galaxy F17 5G
+Galaxy F34 5G</t>
         </is>
       </c>
     </row>
@@ -3268,8 +3270,8 @@
       </c>
       <c r="C188" t="inlineStr">
         <is>
-          <t>Galaxy F70e 5G
-Galaxy F13</t>
+          <t>Galaxy F36 5G
+Galaxy F54 5G</t>
         </is>
       </c>
     </row>
@@ -3284,7 +3286,7 @@
       </c>
       <c r="C189" t="inlineStr">
         <is>
-          <t>Galaxy F14</t>
+          <t>Galaxy F55 5G</t>
         </is>
       </c>
     </row>
@@ -3299,7 +3301,7 @@
       </c>
       <c r="C190" t="inlineStr">
         <is>
-          <t>Galaxy F14 5G</t>
+          <t>Galaxy F56 5G</t>
         </is>
       </c>
     </row>
@@ -3314,7 +3316,7 @@
       </c>
       <c r="C191" t="inlineStr">
         <is>
-          <t>Galaxy F15 5G</t>
+          <t>Galaxy F04</t>
         </is>
       </c>
     </row>
@@ -3329,7 +3331,7 @@
       </c>
       <c r="C192" t="inlineStr">
         <is>
-          <t>Galaxy F16 5G</t>
+          <t>Galaxy F05</t>
         </is>
       </c>
     </row>
@@ -3344,8 +3346,7 @@
       </c>
       <c r="C193" t="inlineStr">
         <is>
-          <t>Galaxy F17 5G
-Galaxy F34 5G</t>
+          <t>Galaxy F06 5G</t>
         </is>
       </c>
     </row>
@@ -3360,8 +3361,7 @@
       </c>
       <c r="C194" t="inlineStr">
         <is>
-          <t>Galaxy F36 5G
-Galaxy F54 5G</t>
+          <t>Galaxy F07</t>
         </is>
       </c>
     </row>
@@ -3376,7 +3376,7 @@
       </c>
       <c r="C195" t="inlineStr">
         <is>
-          <t>Galaxy F55 5G</t>
+          <t>Galaxy F70e 5G</t>
         </is>
       </c>
     </row>
@@ -3391,7 +3391,7 @@
       </c>
       <c r="C196" t="inlineStr">
         <is>
-          <t>Galaxy F56 5G</t>
+          <t>Galaxy F13</t>
         </is>
       </c>
     </row>
@@ -3406,7 +3406,7 @@
       </c>
       <c r="C197" t="inlineStr">
         <is>
-          <t>Galaxy F04</t>
+          <t>Galaxy F14</t>
         </is>
       </c>
     </row>
@@ -3421,7 +3421,7 @@
       </c>
       <c r="C198" t="inlineStr">
         <is>
-          <t>Galaxy F05</t>
+          <t>Galaxy F14 5G</t>
         </is>
       </c>
     </row>
@@ -3436,7 +3436,7 @@
       </c>
       <c r="C199" t="inlineStr">
         <is>
-          <t>Galaxy F06 5G</t>
+          <t>Galaxy F15 5G</t>
         </is>
       </c>
     </row>
@@ -3451,7 +3451,7 @@
       </c>
       <c r="C200" t="inlineStr">
         <is>
-          <t>Galaxy F07</t>
+          <t>Galaxy F16 5G</t>
         </is>
       </c>
     </row>
@@ -3466,7 +3466,7 @@
       </c>
       <c r="C201" t="inlineStr">
         <is>
-          <t>Galaxy F70e 5G</t>
+          <t>Galaxy F17 5G</t>
         </is>
       </c>
     </row>
@@ -3481,7 +3481,7 @@
       </c>
       <c r="C202" t="inlineStr">
         <is>
-          <t>Galaxy F13</t>
+          <t>Galaxy F34 5G</t>
         </is>
       </c>
     </row>
@@ -3496,7 +3496,7 @@
       </c>
       <c r="C203" t="inlineStr">
         <is>
-          <t>Galaxy F14</t>
+          <t>Galaxy F36 5G</t>
         </is>
       </c>
     </row>
@@ -3511,7 +3511,7 @@
       </c>
       <c r="C204" t="inlineStr">
         <is>
-          <t>Galaxy F14 5G</t>
+          <t>Galaxy F54 5G</t>
         </is>
       </c>
     </row>
@@ -3526,7 +3526,7 @@
       </c>
       <c r="C205" t="inlineStr">
         <is>
-          <t>Galaxy F15 5G</t>
+          <t>Galaxy F55 5G</t>
         </is>
       </c>
     </row>
@@ -3541,7 +3541,7 @@
       </c>
       <c r="C206" t="inlineStr">
         <is>
-          <t>Galaxy F16 5G</t>
+          <t>Galaxy F56 5G</t>
         </is>
       </c>
     </row>
@@ -3556,7 +3556,8 @@
       </c>
       <c r="C207" t="inlineStr">
         <is>
-          <t>Galaxy F17 5G</t>
+          <t>Galaxy Tab S Series
+Galaxy Tab S11</t>
         </is>
       </c>
     </row>
@@ -3571,7 +3572,8 @@
       </c>
       <c r="C208" t="inlineStr">
         <is>
-          <t>Galaxy F34 5G</t>
+          <t>Galaxy Tab S11 Ultra
+Galaxy Tab S10+</t>
         </is>
       </c>
     </row>
@@ -3586,7 +3588,7 @@
       </c>
       <c r="C209" t="inlineStr">
         <is>
-          <t>Galaxy F36 5G</t>
+          <t>Galaxy Tab S10 Ultra</t>
         </is>
       </c>
     </row>
@@ -3601,7 +3603,7 @@
       </c>
       <c r="C210" t="inlineStr">
         <is>
-          <t>Galaxy F54 5G</t>
+          <t>Galaxy Tab S10 FE</t>
         </is>
       </c>
     </row>
@@ -3616,7 +3618,7 @@
       </c>
       <c r="C211" t="inlineStr">
         <is>
-          <t>Galaxy F55 5G</t>
+          <t>Galaxy Tab S10 FE+</t>
         </is>
       </c>
     </row>
@@ -3631,7 +3633,8 @@
       </c>
       <c r="C212" t="inlineStr">
         <is>
-          <t>Galaxy F56 5G</t>
+          <t>Galaxy Tab S10 Lite
+Galaxy Tab S9</t>
         </is>
       </c>
     </row>
@@ -3646,8 +3649,7 @@
       </c>
       <c r="C213" t="inlineStr">
         <is>
-          <t>Galaxy Tab S Series
-Galaxy Tab S11</t>
+          <t>Galaxy Tab S9+</t>
         </is>
       </c>
     </row>
@@ -3662,8 +3664,7 @@
       </c>
       <c r="C214" t="inlineStr">
         <is>
-          <t>Galaxy Tab S11 Ultra
-Galaxy Tab S10+</t>
+          <t>Galaxy Tab S9 Ultra</t>
         </is>
       </c>
     </row>
@@ -3678,7 +3679,7 @@
       </c>
       <c r="C215" t="inlineStr">
         <is>
-          <t>Galaxy Tab S10 Ultra</t>
+          <t>Galaxy Tab S9 FE</t>
         </is>
       </c>
     </row>
@@ -3693,7 +3694,8 @@
       </c>
       <c r="C216" t="inlineStr">
         <is>
-          <t>Galaxy Tab S10 FE</t>
+          <t>Galaxy Tab S9 FE+
+Galaxy Tab S8</t>
         </is>
       </c>
     </row>
@@ -3708,7 +3710,7 @@
       </c>
       <c r="C217" t="inlineStr">
         <is>
-          <t>Galaxy Tab S10 FE+</t>
+          <t>Galaxy Tab S8+</t>
         </is>
       </c>
     </row>
@@ -3723,8 +3725,8 @@
       </c>
       <c r="C218" t="inlineStr">
         <is>
-          <t>Galaxy Tab S10 Lite
-Galaxy Tab S9</t>
+          <t>Galaxy Tab S8 Ultra
+Galaxy Tab S6 Lite (2024)</t>
         </is>
       </c>
     </row>
@@ -3739,7 +3741,7 @@
       </c>
       <c r="C219" t="inlineStr">
         <is>
-          <t>Galaxy Tab S9+</t>
+          <t>Galaxy Tab S11</t>
         </is>
       </c>
     </row>
@@ -3754,7 +3756,7 @@
       </c>
       <c r="C220" t="inlineStr">
         <is>
-          <t>Galaxy Tab S9 Ultra</t>
+          <t>Galaxy Tab S11 Ultra</t>
         </is>
       </c>
     </row>
@@ -3769,7 +3771,7 @@
       </c>
       <c r="C221" t="inlineStr">
         <is>
-          <t>Galaxy Tab S9 FE</t>
+          <t>Galaxy Tab S10+</t>
         </is>
       </c>
     </row>
@@ -3784,8 +3786,7 @@
       </c>
       <c r="C222" t="inlineStr">
         <is>
-          <t>Galaxy Tab S9 FE+
-Galaxy Tab S8</t>
+          <t>Galaxy Tab S10 Ultra</t>
         </is>
       </c>
     </row>
@@ -3800,7 +3801,7 @@
       </c>
       <c r="C223" t="inlineStr">
         <is>
-          <t>Galaxy Tab S8+</t>
+          <t>Galaxy Tab S10 FE</t>
         </is>
       </c>
     </row>
@@ -3815,8 +3816,7 @@
       </c>
       <c r="C224" t="inlineStr">
         <is>
-          <t>Galaxy Tab S8 Ultra
-Galaxy Tab S6 Lite (2024)</t>
+          <t>Galaxy Tab S10 FE+</t>
         </is>
       </c>
     </row>
@@ -3831,7 +3831,7 @@
       </c>
       <c r="C225" t="inlineStr">
         <is>
-          <t>Galaxy Tab S11</t>
+          <t>Galaxy Tab S10 Lite</t>
         </is>
       </c>
     </row>
@@ -3846,7 +3846,7 @@
       </c>
       <c r="C226" t="inlineStr">
         <is>
-          <t>Galaxy Tab S11 Ultra</t>
+          <t>Galaxy Tab S9</t>
         </is>
       </c>
     </row>
@@ -3861,7 +3861,7 @@
       </c>
       <c r="C227" t="inlineStr">
         <is>
-          <t>Galaxy Tab S10+</t>
+          <t>Galaxy Tab S9+</t>
         </is>
       </c>
     </row>
@@ -3876,7 +3876,7 @@
       </c>
       <c r="C228" t="inlineStr">
         <is>
-          <t>Galaxy Tab S10 Ultra</t>
+          <t>Galaxy Tab S9 Ultra</t>
         </is>
       </c>
     </row>
@@ -3891,7 +3891,7 @@
       </c>
       <c r="C229" t="inlineStr">
         <is>
-          <t>Galaxy Tab S10 FE</t>
+          <t>Galaxy Tab S9 FE</t>
         </is>
       </c>
     </row>
@@ -3906,7 +3906,7 @@
       </c>
       <c r="C230" t="inlineStr">
         <is>
-          <t>Galaxy Tab S10 FE+</t>
+          <t>Galaxy Tab S9 FE+</t>
         </is>
       </c>
     </row>
@@ -3921,7 +3921,7 @@
       </c>
       <c r="C231" t="inlineStr">
         <is>
-          <t>Galaxy Tab S10 Lite</t>
+          <t>Galaxy Tab S8</t>
         </is>
       </c>
     </row>
@@ -3936,7 +3936,7 @@
       </c>
       <c r="C232" t="inlineStr">
         <is>
-          <t>Galaxy Tab S9</t>
+          <t>Galaxy Tab S8+</t>
         </is>
       </c>
     </row>
@@ -3951,7 +3951,7 @@
       </c>
       <c r="C233" t="inlineStr">
         <is>
-          <t>Galaxy Tab S9+</t>
+          <t>Galaxy Tab S8 Ultra</t>
         </is>
       </c>
     </row>
@@ -3966,7 +3966,7 @@
       </c>
       <c r="C234" t="inlineStr">
         <is>
-          <t>Galaxy Tab S9 Ultra</t>
+          <t>Galaxy Tab S6 Lite (2024)</t>
         </is>
       </c>
     </row>
@@ -3981,7 +3981,8 @@
       </c>
       <c r="C235" t="inlineStr">
         <is>
-          <t>Galaxy Tab S9 FE</t>
+          <t>Galaxy Tab A Series
+Galaxy Tab A11</t>
         </is>
       </c>
     </row>
@@ -3996,7 +3997,8 @@
       </c>
       <c r="C236" t="inlineStr">
         <is>
-          <t>Galaxy Tab S9 FE+</t>
+          <t>Galaxy Tab A11+
+Galaxy Tab A9</t>
         </is>
       </c>
     </row>
@@ -4011,7 +4013,7 @@
       </c>
       <c r="C237" t="inlineStr">
         <is>
-          <t>Galaxy Tab S8</t>
+          <t>Galaxy Tab A9+</t>
         </is>
       </c>
     </row>
@@ -4026,7 +4028,7 @@
       </c>
       <c r="C238" t="inlineStr">
         <is>
-          <t>Galaxy Tab S8+</t>
+          <t>Galaxy Tab A9+(2025)</t>
         </is>
       </c>
     </row>
@@ -4041,7 +4043,7 @@
       </c>
       <c r="C239" t="inlineStr">
         <is>
-          <t>Galaxy Tab S8 Ultra</t>
+          <t>Galaxy Tab A11</t>
         </is>
       </c>
     </row>
@@ -4056,7 +4058,7 @@
       </c>
       <c r="C240" t="inlineStr">
         <is>
-          <t>Galaxy Tab S6 Lite (2024)</t>
+          <t>Galaxy Tab A11+</t>
         </is>
       </c>
     </row>
@@ -4071,8 +4073,7 @@
       </c>
       <c r="C241" t="inlineStr">
         <is>
-          <t>Galaxy Tab A Series
-Galaxy Tab A11</t>
+          <t>Galaxy Tab A9</t>
         </is>
       </c>
     </row>
@@ -4087,8 +4088,7 @@
       </c>
       <c r="C242" t="inlineStr">
         <is>
-          <t>Galaxy Tab A11+
-Galaxy Tab A9</t>
+          <t>Galaxy Tab A9+</t>
         </is>
       </c>
     </row>
@@ -4103,7 +4103,7 @@
       </c>
       <c r="C243" t="inlineStr">
         <is>
-          <t>Galaxy Tab A9+</t>
+          <t>Galaxy Tab A9+(2025)</t>
         </is>
       </c>
     </row>
@@ -4118,7 +4118,9 @@
       </c>
       <c r="C244" t="inlineStr">
         <is>
-          <t>Galaxy Tab A9+(2025)</t>
+          <t>Enterprise Models
+Galaxy A53 5G 
+Galaxy Tab Active4 Pro</t>
         </is>
       </c>
     </row>
@@ -4133,7 +4135,8 @@
       </c>
       <c r="C245" t="inlineStr">
         <is>
-          <t>Galaxy Tab A11</t>
+          <t>Galaxy Tab Active5
+Galaxy XCover5</t>
         </is>
       </c>
     </row>
@@ -4148,7 +4151,7 @@
       </c>
       <c r="C246" t="inlineStr">
         <is>
-          <t>Galaxy Tab A11+</t>
+          <t>Galaxy A53 5G</t>
         </is>
       </c>
     </row>
@@ -4163,7 +4166,7 @@
       </c>
       <c r="C247" t="inlineStr">
         <is>
-          <t>Galaxy Tab A9</t>
+          <t>Galaxy Tab Active4 Pro</t>
         </is>
       </c>
     </row>
@@ -4178,7 +4181,7 @@
       </c>
       <c r="C248" t="inlineStr">
         <is>
-          <t>Galaxy Tab A9+</t>
+          <t>Galaxy Tab Active5</t>
         </is>
       </c>
     </row>
@@ -4193,7 +4196,7 @@
       </c>
       <c r="C249" t="inlineStr">
         <is>
-          <t>Galaxy Tab A9+(2025)</t>
+          <t>Galaxy XCover5</t>
         </is>
       </c>
     </row>
@@ -4208,9 +4211,8 @@
       </c>
       <c r="C250" t="inlineStr">
         <is>
-          <t>Enterprise Models
-Galaxy A53 5G 
-Galaxy Tab Active4 Pro</t>
+          <t>Galaxy Watch Series
+Galaxy Watch8 40mm</t>
         </is>
       </c>
     </row>
@@ -4225,8 +4227,7 @@
       </c>
       <c r="C251" t="inlineStr">
         <is>
-          <t>Galaxy Tab Active5
-Galaxy XCover5</t>
+          <t>Galaxy Watch8 44mm</t>
         </is>
       </c>
     </row>
@@ -4241,7 +4242,9 @@
       </c>
       <c r="C252" t="inlineStr">
         <is>
-          <t>Galaxy A53 5G</t>
+          <t>Galaxy Watch8 Classic 46mm
+Galaxy Watch Ultra
+Galaxy Watch7 40mm</t>
         </is>
       </c>
     </row>
@@ -4256,7 +4259,9 @@
       </c>
       <c r="C253" t="inlineStr">
         <is>
-          <t>Galaxy Tab Active4 Pro</t>
+          <t>Galaxy Watch7 44mm
+Galaxy Watch FE
+Galaxy Watch6 40mm</t>
         </is>
       </c>
     </row>
@@ -4271,7 +4276,7 @@
       </c>
       <c r="C254" t="inlineStr">
         <is>
-          <t>Galaxy Tab Active5</t>
+          <t>Galaxy Watch6 44mm</t>
         </is>
       </c>
     </row>
@@ -4286,7 +4291,7 @@
       </c>
       <c r="C255" t="inlineStr">
         <is>
-          <t>Galaxy XCover5</t>
+          <t>Galaxy Watch6 Classic 43mm</t>
         </is>
       </c>
     </row>
@@ -4301,8 +4306,8 @@
       </c>
       <c r="C256" t="inlineStr">
         <is>
-          <t>Galaxy Watch Series
-Galaxy Watch8 40mm</t>
+          <t>Galaxy Watch6 Classic 47mm
+Galaxy Watch5 40mm</t>
         </is>
       </c>
     </row>
@@ -4317,7 +4322,7 @@
       </c>
       <c r="C257" t="inlineStr">
         <is>
-          <t>Galaxy Watch8 44mm</t>
+          <t>Galaxy Watch5 44mm</t>
         </is>
       </c>
     </row>
@@ -4332,9 +4337,8 @@
       </c>
       <c r="C258" t="inlineStr">
         <is>
-          <t>Galaxy Watch8 Classic 46mm
-Galaxy Watch Ultra
-Galaxy Watch7 40mm</t>
+          <t>Galaxy Watch5 Pro
+Galaxy Watch4 40mm</t>
         </is>
       </c>
     </row>
@@ -4349,9 +4353,7 @@
       </c>
       <c r="C259" t="inlineStr">
         <is>
-          <t>Galaxy Watch7 44mm
-Galaxy Watch FE
-Galaxy Watch6 40mm</t>
+          <t>Galaxy Watch4 44mm</t>
         </is>
       </c>
     </row>
@@ -4366,7 +4368,7 @@
       </c>
       <c r="C260" t="inlineStr">
         <is>
-          <t>Galaxy Watch6 44mm</t>
+          <t>Galaxy Watch4 Classic 42mm</t>
         </is>
       </c>
     </row>
@@ -4381,7 +4383,7 @@
       </c>
       <c r="C261" t="inlineStr">
         <is>
-          <t>Galaxy Watch6 Classic 43mm</t>
+          <t>Galaxy Watch4 Classic 46mm</t>
         </is>
       </c>
     </row>
@@ -4396,8 +4398,7 @@
       </c>
       <c r="C262" t="inlineStr">
         <is>
-          <t>Galaxy Watch6 Classic 47mm
-Galaxy Watch5 40mm</t>
+          <t>Galaxy Watch8 40mm</t>
         </is>
       </c>
     </row>
@@ -4412,7 +4413,7 @@
       </c>
       <c r="C263" t="inlineStr">
         <is>
-          <t>Galaxy Watch5 44mm</t>
+          <t>Galaxy Watch8 44mm</t>
         </is>
       </c>
     </row>
@@ -4427,8 +4428,7 @@
       </c>
       <c r="C264" t="inlineStr">
         <is>
-          <t>Galaxy Watch5 Pro
-Galaxy Watch4 40mm</t>
+          <t>Galaxy Watch8 Classic 46mm</t>
         </is>
       </c>
     </row>
@@ -4443,7 +4443,7 @@
       </c>
       <c r="C265" t="inlineStr">
         <is>
-          <t>Galaxy Watch4 44mm</t>
+          <t>Galaxy Watch Ultra</t>
         </is>
       </c>
     </row>
@@ -4458,7 +4458,7 @@
       </c>
       <c r="C266" t="inlineStr">
         <is>
-          <t>Galaxy Watch4 Classic 42mm</t>
+          <t>Galaxy Watch7 40mm</t>
         </is>
       </c>
     </row>
@@ -4473,7 +4473,7 @@
       </c>
       <c r="C267" t="inlineStr">
         <is>
-          <t>Galaxy Watch4 Classic 46mm</t>
+          <t>Galaxy Watch7 44mm</t>
         </is>
       </c>
     </row>
@@ -4488,7 +4488,7 @@
       </c>
       <c r="C268" t="inlineStr">
         <is>
-          <t>Galaxy Watch8 40mm</t>
+          <t>Galaxy Watch FE</t>
         </is>
       </c>
     </row>
@@ -4503,7 +4503,7 @@
       </c>
       <c r="C269" t="inlineStr">
         <is>
-          <t>Galaxy Watch8 44mm</t>
+          <t>Galaxy Watch6 40mm</t>
         </is>
       </c>
     </row>
@@ -4518,7 +4518,7 @@
       </c>
       <c r="C270" t="inlineStr">
         <is>
-          <t>Galaxy Watch8 Classic 46mm</t>
+          <t>Galaxy Watch6 44mm</t>
         </is>
       </c>
     </row>
@@ -4533,7 +4533,7 @@
       </c>
       <c r="C271" t="inlineStr">
         <is>
-          <t>Galaxy Watch Ultra</t>
+          <t>Galaxy Watch6 Classic 43mm</t>
         </is>
       </c>
     </row>
@@ -4548,7 +4548,7 @@
       </c>
       <c r="C272" t="inlineStr">
         <is>
-          <t>Galaxy Watch7 40mm</t>
+          <t>Galaxy Watch6 Classic 47mm</t>
         </is>
       </c>
     </row>
@@ -4563,7 +4563,7 @@
       </c>
       <c r="C273" t="inlineStr">
         <is>
-          <t>Galaxy Watch7 44mm</t>
+          <t>Galaxy Watch5 40mm</t>
         </is>
       </c>
     </row>
@@ -4578,7 +4578,7 @@
       </c>
       <c r="C274" t="inlineStr">
         <is>
-          <t>Galaxy Watch FE</t>
+          <t>Galaxy Watch5 44mm</t>
         </is>
       </c>
     </row>
@@ -4593,7 +4593,7 @@
       </c>
       <c r="C275" t="inlineStr">
         <is>
-          <t>Galaxy Watch6 40mm</t>
+          <t>Galaxy Watch5 Pro</t>
         </is>
       </c>
     </row>
@@ -4608,7 +4608,7 @@
       </c>
       <c r="C276" t="inlineStr">
         <is>
-          <t>Galaxy Watch6 44mm</t>
+          <t>Galaxy Watch4 40mm</t>
         </is>
       </c>
     </row>
@@ -4623,7 +4623,7 @@
       </c>
       <c r="C277" t="inlineStr">
         <is>
-          <t>Galaxy Watch6 Classic 43mm</t>
+          <t>Galaxy Watch4 44mm</t>
         </is>
       </c>
     </row>
@@ -4638,7 +4638,7 @@
       </c>
       <c r="C278" t="inlineStr">
         <is>
-          <t>Galaxy Watch6 Classic 47mm</t>
+          <t>Galaxy Watch4 Classic 42mm</t>
         </is>
       </c>
     </row>
@@ -4653,7 +4653,7 @@
       </c>
       <c r="C279" t="inlineStr">
         <is>
-          <t>Galaxy Watch5 40mm</t>
+          <t>Galaxy Watch4 Classic 46mm</t>
         </is>
       </c>
     </row>
@@ -4668,7 +4668,8 @@
       </c>
       <c r="C280" t="inlineStr">
         <is>
-          <t>Galaxy Watch5 44mm</t>
+          <t>Galaxy XR Series
+Galaxy XR</t>
         </is>
       </c>
     </row>
@@ -4683,7 +4684,7 @@
       </c>
       <c r="C281" t="inlineStr">
         <is>
-          <t>Galaxy Watch5 Pro</t>
+          <t>Galaxy XR</t>
         </is>
       </c>
     </row>
@@ -4693,12 +4694,13 @@
       </c>
       <c r="B282" t="inlineStr">
         <is>
-          <t>Quarterly</t>
+          <t>No Information</t>
         </is>
       </c>
       <c r="C282" t="inlineStr">
         <is>
-          <t>Galaxy Watch4 40mm</t>
+          <t>Galaxy Book Series
+Galaxy Book4 Ultra</t>
         </is>
       </c>
     </row>
@@ -4708,12 +4710,12 @@
       </c>
       <c r="B283" t="inlineStr">
         <is>
-          <t>Quarterly</t>
+          <t>No Information</t>
         </is>
       </c>
       <c r="C283" t="inlineStr">
         <is>
-          <t>Galaxy Watch4 44mm</t>
+          <t>Galaxy Book4 Pro</t>
         </is>
       </c>
     </row>
@@ -4723,12 +4725,12 @@
       </c>
       <c r="B284" t="inlineStr">
         <is>
-          <t>Quarterly</t>
+          <t>No Information</t>
         </is>
       </c>
       <c r="C284" t="inlineStr">
         <is>
-          <t>Galaxy Watch4 Classic 42mm</t>
+          <t>Galaxy Book4 Pro 360</t>
         </is>
       </c>
     </row>
@@ -4738,12 +4740,12 @@
       </c>
       <c r="B285" t="inlineStr">
         <is>
-          <t>Quarterly</t>
+          <t>No Information</t>
         </is>
       </c>
       <c r="C285" t="inlineStr">
         <is>
-          <t>Galaxy Watch4 Classic 46mm</t>
+          <t>Galaxy Book4 360</t>
         </is>
       </c>
     </row>
@@ -4753,13 +4755,12 @@
       </c>
       <c r="B286" t="inlineStr">
         <is>
-          <t>Quarterly</t>
+          <t>No Information</t>
         </is>
       </c>
       <c r="C286" t="inlineStr">
         <is>
-          <t>Galaxy XR Series
-Galaxy XR</t>
+          <t>Galaxy Book4</t>
         </is>
       </c>
     </row>
@@ -4769,12 +4770,12 @@
       </c>
       <c r="B287" t="inlineStr">
         <is>
-          <t>Quarterly</t>
+          <t>No Information</t>
         </is>
       </c>
       <c r="C287" t="inlineStr">
         <is>
-          <t>Galaxy XR</t>
+          <t>Galaxy Book4 Ultra</t>
         </is>
       </c>
     </row>
@@ -4789,8 +4790,7 @@
       </c>
       <c r="C288" t="inlineStr">
         <is>
-          <t>Galaxy Book Series
-Galaxy Book4 Ultra</t>
+          <t>Galaxy Book4 Pro</t>
         </is>
       </c>
     </row>
@@ -4805,7 +4805,7 @@
       </c>
       <c r="C289" t="inlineStr">
         <is>
-          <t>Galaxy Book4 Pro</t>
+          <t>Galaxy Book4 Pro 360</t>
         </is>
       </c>
     </row>
@@ -4820,7 +4820,7 @@
       </c>
       <c r="C290" t="inlineStr">
         <is>
-          <t>Galaxy Book4 Pro 360</t>
+          <t>Galaxy Book4 360</t>
         </is>
       </c>
     </row>
@@ -4834,96 +4834,6 @@
         </is>
       </c>
       <c r="C291" t="inlineStr">
-        <is>
-          <t>Galaxy Book4 360</t>
-        </is>
-      </c>
-    </row>
-    <row r="292">
-      <c r="A292" s="1" t="n">
-        <v>290</v>
-      </c>
-      <c r="B292" t="inlineStr">
-        <is>
-          <t>No Information</t>
-        </is>
-      </c>
-      <c r="C292" t="inlineStr">
-        <is>
-          <t>Galaxy Book4</t>
-        </is>
-      </c>
-    </row>
-    <row r="293">
-      <c r="A293" s="1" t="n">
-        <v>291</v>
-      </c>
-      <c r="B293" t="inlineStr">
-        <is>
-          <t>No Information</t>
-        </is>
-      </c>
-      <c r="C293" t="inlineStr">
-        <is>
-          <t>Galaxy Book4 Ultra</t>
-        </is>
-      </c>
-    </row>
-    <row r="294">
-      <c r="A294" s="1" t="n">
-        <v>292</v>
-      </c>
-      <c r="B294" t="inlineStr">
-        <is>
-          <t>No Information</t>
-        </is>
-      </c>
-      <c r="C294" t="inlineStr">
-        <is>
-          <t>Galaxy Book4 Pro</t>
-        </is>
-      </c>
-    </row>
-    <row r="295">
-      <c r="A295" s="1" t="n">
-        <v>293</v>
-      </c>
-      <c r="B295" t="inlineStr">
-        <is>
-          <t>No Information</t>
-        </is>
-      </c>
-      <c r="C295" t="inlineStr">
-        <is>
-          <t>Galaxy Book4 Pro 360</t>
-        </is>
-      </c>
-    </row>
-    <row r="296">
-      <c r="A296" s="1" t="n">
-        <v>294</v>
-      </c>
-      <c r="B296" t="inlineStr">
-        <is>
-          <t>No Information</t>
-        </is>
-      </c>
-      <c r="C296" t="inlineStr">
-        <is>
-          <t>Galaxy Book4 360</t>
-        </is>
-      </c>
-    </row>
-    <row r="297">
-      <c r="A297" s="1" t="n">
-        <v>295</v>
-      </c>
-      <c r="B297" t="inlineStr">
-        <is>
-          <t>No Information</t>
-        </is>
-      </c>
-      <c r="C297" t="inlineStr">
         <is>
           <t>Galaxy Book4</t>
         </is>

--- a/dataset/samsung_device_updates.xlsx
+++ b/dataset/samsung_device_updates.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C291"/>
+  <dimension ref="A1:C289"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2727,7 +2727,7 @@
         <is>
           <t>Galaxy M36 5G
 Galaxy M44 5G
-Galaxy M53 5G</t>
+Galaxy M54 5G</t>
         </is>
       </c>
     </row>
@@ -2742,7 +2742,7 @@
       </c>
       <c r="C153" t="inlineStr">
         <is>
-          <t>Galaxy M54 5G</t>
+          <t>Galaxy M55 5G</t>
         </is>
       </c>
     </row>
@@ -2757,7 +2757,7 @@
       </c>
       <c r="C154" t="inlineStr">
         <is>
-          <t>Galaxy M55 5G</t>
+          <t>Galaxy M55s 5G</t>
         </is>
       </c>
     </row>
@@ -2772,7 +2772,7 @@
       </c>
       <c r="C155" t="inlineStr">
         <is>
-          <t>Galaxy M55s 5G</t>
+          <t>Galaxy M56 5G</t>
         </is>
       </c>
     </row>
@@ -2787,7 +2787,7 @@
       </c>
       <c r="C156" t="inlineStr">
         <is>
-          <t>Galaxy M56 5G</t>
+          <t>Galaxy M04</t>
         </is>
       </c>
     </row>
@@ -2802,7 +2802,7 @@
       </c>
       <c r="C157" t="inlineStr">
         <is>
-          <t>Galaxy M04</t>
+          <t>Galaxy M05</t>
         </is>
       </c>
     </row>
@@ -2817,7 +2817,7 @@
       </c>
       <c r="C158" t="inlineStr">
         <is>
-          <t>Galaxy M05</t>
+          <t>Galaxy M06 5G</t>
         </is>
       </c>
     </row>
@@ -2832,7 +2832,7 @@
       </c>
       <c r="C159" t="inlineStr">
         <is>
-          <t>Galaxy M06 5G</t>
+          <t>Galaxy M07</t>
         </is>
       </c>
     </row>
@@ -2847,7 +2847,7 @@
       </c>
       <c r="C160" t="inlineStr">
         <is>
-          <t>Galaxy M07</t>
+          <t>Galaxy M13</t>
         </is>
       </c>
     </row>
@@ -2862,7 +2862,7 @@
       </c>
       <c r="C161" t="inlineStr">
         <is>
-          <t>Galaxy M13</t>
+          <t>Galaxy M13 5G</t>
         </is>
       </c>
     </row>
@@ -2877,7 +2877,7 @@
       </c>
       <c r="C162" t="inlineStr">
         <is>
-          <t>Galaxy M13 5G</t>
+          <t>Galaxy M14</t>
         </is>
       </c>
     </row>
@@ -2892,7 +2892,7 @@
       </c>
       <c r="C163" t="inlineStr">
         <is>
-          <t>Galaxy M14</t>
+          <t>Galaxy M14 5G</t>
         </is>
       </c>
     </row>
@@ -2907,7 +2907,7 @@
       </c>
       <c r="C164" t="inlineStr">
         <is>
-          <t>Galaxy M14 5G</t>
+          <t>Galaxy M15 5G</t>
         </is>
       </c>
     </row>
@@ -2922,7 +2922,7 @@
       </c>
       <c r="C165" t="inlineStr">
         <is>
-          <t>Galaxy M15 5G</t>
+          <t>Galaxy M16 5G</t>
         </is>
       </c>
     </row>
@@ -2937,7 +2937,7 @@
       </c>
       <c r="C166" t="inlineStr">
         <is>
-          <t>Galaxy M16 5G</t>
+          <t>Galaxy M17 5G</t>
         </is>
       </c>
     </row>
@@ -2952,7 +2952,7 @@
       </c>
       <c r="C167" t="inlineStr">
         <is>
-          <t>Galaxy M17 5G</t>
+          <t>Galaxy M17e 5G</t>
         </is>
       </c>
     </row>
@@ -2967,7 +2967,7 @@
       </c>
       <c r="C168" t="inlineStr">
         <is>
-          <t>Galaxy M17e 5G</t>
+          <t>Galaxy M34 5G</t>
         </is>
       </c>
     </row>
@@ -2982,7 +2982,7 @@
       </c>
       <c r="C169" t="inlineStr">
         <is>
-          <t>Galaxy M34 5G</t>
+          <t>Galaxy M35 5G</t>
         </is>
       </c>
     </row>
@@ -2997,7 +2997,7 @@
       </c>
       <c r="C170" t="inlineStr">
         <is>
-          <t>Galaxy M35 5G</t>
+          <t>Galaxy M36 5G</t>
         </is>
       </c>
     </row>
@@ -3012,7 +3012,7 @@
       </c>
       <c r="C171" t="inlineStr">
         <is>
-          <t>Galaxy M36 5G</t>
+          <t>Galaxy M44 5G</t>
         </is>
       </c>
     </row>
@@ -3027,7 +3027,7 @@
       </c>
       <c r="C172" t="inlineStr">
         <is>
-          <t>Galaxy M44 5G</t>
+          <t>Galaxy M54 5G</t>
         </is>
       </c>
     </row>
@@ -3042,7 +3042,7 @@
       </c>
       <c r="C173" t="inlineStr">
         <is>
-          <t>Galaxy M53 5G</t>
+          <t>Galaxy M55 5G</t>
         </is>
       </c>
     </row>
@@ -3057,7 +3057,7 @@
       </c>
       <c r="C174" t="inlineStr">
         <is>
-          <t>Galaxy M54 5G</t>
+          <t>Galaxy M55s 5G</t>
         </is>
       </c>
     </row>
@@ -3072,7 +3072,7 @@
       </c>
       <c r="C175" t="inlineStr">
         <is>
-          <t>Galaxy M55 5G</t>
+          <t>Galaxy M56 5G</t>
         </is>
       </c>
     </row>
@@ -3087,7 +3087,8 @@
       </c>
       <c r="C176" t="inlineStr">
         <is>
-          <t>Galaxy M55s 5G</t>
+          <t>Galaxy F Series
+Galaxy F04</t>
         </is>
       </c>
     </row>
@@ -3102,7 +3103,7 @@
       </c>
       <c r="C177" t="inlineStr">
         <is>
-          <t>Galaxy M56 5G</t>
+          <t>Galaxy F05</t>
         </is>
       </c>
     </row>
@@ -3117,8 +3118,7 @@
       </c>
       <c r="C178" t="inlineStr">
         <is>
-          <t>Galaxy F Series
-Galaxy F04</t>
+          <t>Galaxy F06 5G</t>
         </is>
       </c>
     </row>
@@ -3133,7 +3133,7 @@
       </c>
       <c r="C179" t="inlineStr">
         <is>
-          <t>Galaxy F05</t>
+          <t>Galaxy F07</t>
         </is>
       </c>
     </row>
@@ -3148,7 +3148,8 @@
       </c>
       <c r="C180" t="inlineStr">
         <is>
-          <t>Galaxy F06 5G</t>
+          <t>Galaxy F70e 5G
+Galaxy F13</t>
         </is>
       </c>
     </row>
@@ -3163,7 +3164,7 @@
       </c>
       <c r="C181" t="inlineStr">
         <is>
-          <t>Galaxy F07</t>
+          <t>Galaxy F14</t>
         </is>
       </c>
     </row>
@@ -3178,8 +3179,7 @@
       </c>
       <c r="C182" t="inlineStr">
         <is>
-          <t>Galaxy F70e 5G
-Galaxy F13</t>
+          <t>Galaxy F14 5G</t>
         </is>
       </c>
     </row>
@@ -3194,7 +3194,7 @@
       </c>
       <c r="C183" t="inlineStr">
         <is>
-          <t>Galaxy F14</t>
+          <t>Galaxy F15 5G</t>
         </is>
       </c>
     </row>
@@ -3209,7 +3209,7 @@
       </c>
       <c r="C184" t="inlineStr">
         <is>
-          <t>Galaxy F14 5G</t>
+          <t>Galaxy F16 5G</t>
         </is>
       </c>
     </row>
@@ -3224,7 +3224,8 @@
       </c>
       <c r="C185" t="inlineStr">
         <is>
-          <t>Galaxy F15 5G</t>
+          <t>Galaxy F17 5G
+Galaxy F34 5G</t>
         </is>
       </c>
     </row>
@@ -3239,7 +3240,8 @@
       </c>
       <c r="C186" t="inlineStr">
         <is>
-          <t>Galaxy F16 5G</t>
+          <t>Galaxy F36 5G
+Galaxy F54 5G</t>
         </is>
       </c>
     </row>
@@ -3254,8 +3256,7 @@
       </c>
       <c r="C187" t="inlineStr">
         <is>
-          <t>Galaxy F17 5G
-Galaxy F34 5G</t>
+          <t>Galaxy F55 5G</t>
         </is>
       </c>
     </row>
@@ -3270,8 +3271,7 @@
       </c>
       <c r="C188" t="inlineStr">
         <is>
-          <t>Galaxy F36 5G
-Galaxy F54 5G</t>
+          <t>Galaxy F56 5G</t>
         </is>
       </c>
     </row>
@@ -3286,7 +3286,7 @@
       </c>
       <c r="C189" t="inlineStr">
         <is>
-          <t>Galaxy F55 5G</t>
+          <t>Galaxy F04</t>
         </is>
       </c>
     </row>
@@ -3301,7 +3301,7 @@
       </c>
       <c r="C190" t="inlineStr">
         <is>
-          <t>Galaxy F56 5G</t>
+          <t>Galaxy F05</t>
         </is>
       </c>
     </row>
@@ -3316,7 +3316,7 @@
       </c>
       <c r="C191" t="inlineStr">
         <is>
-          <t>Galaxy F04</t>
+          <t>Galaxy F06 5G</t>
         </is>
       </c>
     </row>
@@ -3331,7 +3331,7 @@
       </c>
       <c r="C192" t="inlineStr">
         <is>
-          <t>Galaxy F05</t>
+          <t>Galaxy F07</t>
         </is>
       </c>
     </row>
@@ -3346,7 +3346,7 @@
       </c>
       <c r="C193" t="inlineStr">
         <is>
-          <t>Galaxy F06 5G</t>
+          <t>Galaxy F70e 5G</t>
         </is>
       </c>
     </row>
@@ -3361,7 +3361,7 @@
       </c>
       <c r="C194" t="inlineStr">
         <is>
-          <t>Galaxy F07</t>
+          <t>Galaxy F13</t>
         </is>
       </c>
     </row>
@@ -3376,7 +3376,7 @@
       </c>
       <c r="C195" t="inlineStr">
         <is>
-          <t>Galaxy F70e 5G</t>
+          <t>Galaxy F14</t>
         </is>
       </c>
     </row>
@@ -3391,7 +3391,7 @@
       </c>
       <c r="C196" t="inlineStr">
         <is>
-          <t>Galaxy F13</t>
+          <t>Galaxy F14 5G</t>
         </is>
       </c>
     </row>
@@ -3406,7 +3406,7 @@
       </c>
       <c r="C197" t="inlineStr">
         <is>
-          <t>Galaxy F14</t>
+          <t>Galaxy F15 5G</t>
         </is>
       </c>
     </row>
@@ -3421,7 +3421,7 @@
       </c>
       <c r="C198" t="inlineStr">
         <is>
-          <t>Galaxy F14 5G</t>
+          <t>Galaxy F16 5G</t>
         </is>
       </c>
     </row>
@@ -3436,7 +3436,7 @@
       </c>
       <c r="C199" t="inlineStr">
         <is>
-          <t>Galaxy F15 5G</t>
+          <t>Galaxy F17 5G</t>
         </is>
       </c>
     </row>
@@ -3451,7 +3451,7 @@
       </c>
       <c r="C200" t="inlineStr">
         <is>
-          <t>Galaxy F16 5G</t>
+          <t>Galaxy F34 5G</t>
         </is>
       </c>
     </row>
@@ -3466,7 +3466,7 @@
       </c>
       <c r="C201" t="inlineStr">
         <is>
-          <t>Galaxy F17 5G</t>
+          <t>Galaxy F36 5G</t>
         </is>
       </c>
     </row>
@@ -3481,7 +3481,7 @@
       </c>
       <c r="C202" t="inlineStr">
         <is>
-          <t>Galaxy F34 5G</t>
+          <t>Galaxy F54 5G</t>
         </is>
       </c>
     </row>
@@ -3496,7 +3496,7 @@
       </c>
       <c r="C203" t="inlineStr">
         <is>
-          <t>Galaxy F36 5G</t>
+          <t>Galaxy F55 5G</t>
         </is>
       </c>
     </row>
@@ -3511,7 +3511,7 @@
       </c>
       <c r="C204" t="inlineStr">
         <is>
-          <t>Galaxy F54 5G</t>
+          <t>Galaxy F56 5G</t>
         </is>
       </c>
     </row>
@@ -3526,7 +3526,8 @@
       </c>
       <c r="C205" t="inlineStr">
         <is>
-          <t>Galaxy F55 5G</t>
+          <t>Galaxy Tab S Series
+Galaxy Tab S11</t>
         </is>
       </c>
     </row>
@@ -3541,7 +3542,8 @@
       </c>
       <c r="C206" t="inlineStr">
         <is>
-          <t>Galaxy F56 5G</t>
+          <t>Galaxy Tab S11 Ultra
+Galaxy Tab S10+</t>
         </is>
       </c>
     </row>
@@ -3556,8 +3558,7 @@
       </c>
       <c r="C207" t="inlineStr">
         <is>
-          <t>Galaxy Tab S Series
-Galaxy Tab S11</t>
+          <t>Galaxy Tab S10 Ultra</t>
         </is>
       </c>
     </row>
@@ -3572,8 +3573,7 @@
       </c>
       <c r="C208" t="inlineStr">
         <is>
-          <t>Galaxy Tab S11 Ultra
-Galaxy Tab S10+</t>
+          <t>Galaxy Tab S10 FE</t>
         </is>
       </c>
     </row>
@@ -3588,7 +3588,7 @@
       </c>
       <c r="C209" t="inlineStr">
         <is>
-          <t>Galaxy Tab S10 Ultra</t>
+          <t>Galaxy Tab S10 FE+</t>
         </is>
       </c>
     </row>
@@ -3603,7 +3603,8 @@
       </c>
       <c r="C210" t="inlineStr">
         <is>
-          <t>Galaxy Tab S10 FE</t>
+          <t>Galaxy Tab S10 Lite
+Galaxy Tab S9</t>
         </is>
       </c>
     </row>
@@ -3618,7 +3619,7 @@
       </c>
       <c r="C211" t="inlineStr">
         <is>
-          <t>Galaxy Tab S10 FE+</t>
+          <t>Galaxy Tab S9+</t>
         </is>
       </c>
     </row>
@@ -3633,8 +3634,7 @@
       </c>
       <c r="C212" t="inlineStr">
         <is>
-          <t>Galaxy Tab S10 Lite
-Galaxy Tab S9</t>
+          <t>Galaxy Tab S9 Ultra</t>
         </is>
       </c>
     </row>
@@ -3649,7 +3649,7 @@
       </c>
       <c r="C213" t="inlineStr">
         <is>
-          <t>Galaxy Tab S9+</t>
+          <t>Galaxy Tab S9 FE</t>
         </is>
       </c>
     </row>
@@ -3664,7 +3664,8 @@
       </c>
       <c r="C214" t="inlineStr">
         <is>
-          <t>Galaxy Tab S9 Ultra</t>
+          <t>Galaxy Tab S9 FE+
+Galaxy Tab S8</t>
         </is>
       </c>
     </row>
@@ -3679,7 +3680,7 @@
       </c>
       <c r="C215" t="inlineStr">
         <is>
-          <t>Galaxy Tab S9 FE</t>
+          <t>Galaxy Tab S8+</t>
         </is>
       </c>
     </row>
@@ -3694,8 +3695,8 @@
       </c>
       <c r="C216" t="inlineStr">
         <is>
-          <t>Galaxy Tab S9 FE+
-Galaxy Tab S8</t>
+          <t>Galaxy Tab S8 Ultra
+Galaxy Tab S6 Lite (2024)</t>
         </is>
       </c>
     </row>
@@ -3710,7 +3711,7 @@
       </c>
       <c r="C217" t="inlineStr">
         <is>
-          <t>Galaxy Tab S8+</t>
+          <t>Galaxy Tab S11</t>
         </is>
       </c>
     </row>
@@ -3725,8 +3726,7 @@
       </c>
       <c r="C218" t="inlineStr">
         <is>
-          <t>Galaxy Tab S8 Ultra
-Galaxy Tab S6 Lite (2024)</t>
+          <t>Galaxy Tab S11 Ultra</t>
         </is>
       </c>
     </row>
@@ -3741,7 +3741,7 @@
       </c>
       <c r="C219" t="inlineStr">
         <is>
-          <t>Galaxy Tab S11</t>
+          <t>Galaxy Tab S10+</t>
         </is>
       </c>
     </row>
@@ -3756,7 +3756,7 @@
       </c>
       <c r="C220" t="inlineStr">
         <is>
-          <t>Galaxy Tab S11 Ultra</t>
+          <t>Galaxy Tab S10 Ultra</t>
         </is>
       </c>
     </row>
@@ -3771,7 +3771,7 @@
       </c>
       <c r="C221" t="inlineStr">
         <is>
-          <t>Galaxy Tab S10+</t>
+          <t>Galaxy Tab S10 FE</t>
         </is>
       </c>
     </row>
@@ -3786,7 +3786,7 @@
       </c>
       <c r="C222" t="inlineStr">
         <is>
-          <t>Galaxy Tab S10 Ultra</t>
+          <t>Galaxy Tab S10 FE+</t>
         </is>
       </c>
     </row>
@@ -3801,7 +3801,7 @@
       </c>
       <c r="C223" t="inlineStr">
         <is>
-          <t>Galaxy Tab S10 FE</t>
+          <t>Galaxy Tab S10 Lite</t>
         </is>
       </c>
     </row>
@@ -3816,7 +3816,7 @@
       </c>
       <c r="C224" t="inlineStr">
         <is>
-          <t>Galaxy Tab S10 FE+</t>
+          <t>Galaxy Tab S9</t>
         </is>
       </c>
     </row>
@@ -3831,7 +3831,7 @@
       </c>
       <c r="C225" t="inlineStr">
         <is>
-          <t>Galaxy Tab S10 Lite</t>
+          <t>Galaxy Tab S9+</t>
         </is>
       </c>
     </row>
@@ -3846,7 +3846,7 @@
       </c>
       <c r="C226" t="inlineStr">
         <is>
-          <t>Galaxy Tab S9</t>
+          <t>Galaxy Tab S9 Ultra</t>
         </is>
       </c>
     </row>
@@ -3861,7 +3861,7 @@
       </c>
       <c r="C227" t="inlineStr">
         <is>
-          <t>Galaxy Tab S9+</t>
+          <t>Galaxy Tab S9 FE</t>
         </is>
       </c>
     </row>
@@ -3876,7 +3876,7 @@
       </c>
       <c r="C228" t="inlineStr">
         <is>
-          <t>Galaxy Tab S9 Ultra</t>
+          <t>Galaxy Tab S9 FE+</t>
         </is>
       </c>
     </row>
@@ -3891,7 +3891,7 @@
       </c>
       <c r="C229" t="inlineStr">
         <is>
-          <t>Galaxy Tab S9 FE</t>
+          <t>Galaxy Tab S8</t>
         </is>
       </c>
     </row>
@@ -3906,7 +3906,7 @@
       </c>
       <c r="C230" t="inlineStr">
         <is>
-          <t>Galaxy Tab S9 FE+</t>
+          <t>Galaxy Tab S8+</t>
         </is>
       </c>
     </row>
@@ -3921,7 +3921,7 @@
       </c>
       <c r="C231" t="inlineStr">
         <is>
-          <t>Galaxy Tab S8</t>
+          <t>Galaxy Tab S8 Ultra</t>
         </is>
       </c>
     </row>
@@ -3936,7 +3936,7 @@
       </c>
       <c r="C232" t="inlineStr">
         <is>
-          <t>Galaxy Tab S8+</t>
+          <t>Galaxy Tab S6 Lite (2024)</t>
         </is>
       </c>
     </row>
@@ -3951,7 +3951,8 @@
       </c>
       <c r="C233" t="inlineStr">
         <is>
-          <t>Galaxy Tab S8 Ultra</t>
+          <t>Galaxy Tab A Series
+Galaxy Tab A11</t>
         </is>
       </c>
     </row>
@@ -3966,7 +3967,8 @@
       </c>
       <c r="C234" t="inlineStr">
         <is>
-          <t>Galaxy Tab S6 Lite (2024)</t>
+          <t>Galaxy Tab A11+
+Galaxy Tab A9</t>
         </is>
       </c>
     </row>
@@ -3981,8 +3983,7 @@
       </c>
       <c r="C235" t="inlineStr">
         <is>
-          <t>Galaxy Tab A Series
-Galaxy Tab A11</t>
+          <t>Galaxy Tab A9+</t>
         </is>
       </c>
     </row>
@@ -3997,8 +3998,7 @@
       </c>
       <c r="C236" t="inlineStr">
         <is>
-          <t>Galaxy Tab A11+
-Galaxy Tab A9</t>
+          <t>Galaxy Tab A9+(2025)</t>
         </is>
       </c>
     </row>
@@ -4013,7 +4013,7 @@
       </c>
       <c r="C237" t="inlineStr">
         <is>
-          <t>Galaxy Tab A9+</t>
+          <t>Galaxy Tab A11</t>
         </is>
       </c>
     </row>
@@ -4028,7 +4028,7 @@
       </c>
       <c r="C238" t="inlineStr">
         <is>
-          <t>Galaxy Tab A9+(2025)</t>
+          <t>Galaxy Tab A11+</t>
         </is>
       </c>
     </row>
@@ -4043,7 +4043,7 @@
       </c>
       <c r="C239" t="inlineStr">
         <is>
-          <t>Galaxy Tab A11</t>
+          <t>Galaxy Tab A9</t>
         </is>
       </c>
     </row>
@@ -4058,7 +4058,7 @@
       </c>
       <c r="C240" t="inlineStr">
         <is>
-          <t>Galaxy Tab A11+</t>
+          <t>Galaxy Tab A9+</t>
         </is>
       </c>
     </row>
@@ -4073,7 +4073,7 @@
       </c>
       <c r="C241" t="inlineStr">
         <is>
-          <t>Galaxy Tab A9</t>
+          <t>Galaxy Tab A9+(2025)</t>
         </is>
       </c>
     </row>
@@ -4088,7 +4088,9 @@
       </c>
       <c r="C242" t="inlineStr">
         <is>
-          <t>Galaxy Tab A9+</t>
+          <t>Enterprise Models
+Galaxy A53 5G 
+Galaxy Tab Active4 Pro</t>
         </is>
       </c>
     </row>
@@ -4103,7 +4105,8 @@
       </c>
       <c r="C243" t="inlineStr">
         <is>
-          <t>Galaxy Tab A9+(2025)</t>
+          <t>Galaxy Tab Active5
+Galaxy XCover5</t>
         </is>
       </c>
     </row>
@@ -4118,9 +4121,7 @@
       </c>
       <c r="C244" t="inlineStr">
         <is>
-          <t>Enterprise Models
-Galaxy A53 5G 
-Galaxy Tab Active4 Pro</t>
+          <t>Galaxy A53 5G</t>
         </is>
       </c>
     </row>
@@ -4135,8 +4136,7 @@
       </c>
       <c r="C245" t="inlineStr">
         <is>
-          <t>Galaxy Tab Active5
-Galaxy XCover5</t>
+          <t>Galaxy Tab Active4 Pro</t>
         </is>
       </c>
     </row>
@@ -4151,7 +4151,7 @@
       </c>
       <c r="C246" t="inlineStr">
         <is>
-          <t>Galaxy A53 5G</t>
+          <t>Galaxy Tab Active5</t>
         </is>
       </c>
     </row>
@@ -4166,7 +4166,7 @@
       </c>
       <c r="C247" t="inlineStr">
         <is>
-          <t>Galaxy Tab Active4 Pro</t>
+          <t>Galaxy XCover5</t>
         </is>
       </c>
     </row>
@@ -4181,7 +4181,8 @@
       </c>
       <c r="C248" t="inlineStr">
         <is>
-          <t>Galaxy Tab Active5</t>
+          <t>Galaxy Watch Series
+Galaxy Watch8 40mm</t>
         </is>
       </c>
     </row>
@@ -4196,7 +4197,7 @@
       </c>
       <c r="C249" t="inlineStr">
         <is>
-          <t>Galaxy XCover5</t>
+          <t>Galaxy Watch8 44mm</t>
         </is>
       </c>
     </row>
@@ -4211,8 +4212,9 @@
       </c>
       <c r="C250" t="inlineStr">
         <is>
-          <t>Galaxy Watch Series
-Galaxy Watch8 40mm</t>
+          <t>Galaxy Watch8 Classic 46mm
+Galaxy Watch Ultra
+Galaxy Watch7 40mm</t>
         </is>
       </c>
     </row>
@@ -4227,7 +4229,9 @@
       </c>
       <c r="C251" t="inlineStr">
         <is>
-          <t>Galaxy Watch8 44mm</t>
+          <t>Galaxy Watch7 44mm
+Galaxy Watch FE
+Galaxy Watch6 40mm</t>
         </is>
       </c>
     </row>
@@ -4242,9 +4246,7 @@
       </c>
       <c r="C252" t="inlineStr">
         <is>
-          <t>Galaxy Watch8 Classic 46mm
-Galaxy Watch Ultra
-Galaxy Watch7 40mm</t>
+          <t>Galaxy Watch6 44mm</t>
         </is>
       </c>
     </row>
@@ -4259,9 +4261,7 @@
       </c>
       <c r="C253" t="inlineStr">
         <is>
-          <t>Galaxy Watch7 44mm
-Galaxy Watch FE
-Galaxy Watch6 40mm</t>
+          <t>Galaxy Watch6 Classic 43mm</t>
         </is>
       </c>
     </row>
@@ -4276,7 +4276,8 @@
       </c>
       <c r="C254" t="inlineStr">
         <is>
-          <t>Galaxy Watch6 44mm</t>
+          <t>Galaxy Watch6 Classic 47mm
+Galaxy Watch5 40mm</t>
         </is>
       </c>
     </row>
@@ -4291,7 +4292,7 @@
       </c>
       <c r="C255" t="inlineStr">
         <is>
-          <t>Galaxy Watch6 Classic 43mm</t>
+          <t>Galaxy Watch5 44mm</t>
         </is>
       </c>
     </row>
@@ -4306,8 +4307,8 @@
       </c>
       <c r="C256" t="inlineStr">
         <is>
-          <t>Galaxy Watch6 Classic 47mm
-Galaxy Watch5 40mm</t>
+          <t>Galaxy Watch5 Pro
+Galaxy Watch4 40mm</t>
         </is>
       </c>
     </row>
@@ -4322,7 +4323,7 @@
       </c>
       <c r="C257" t="inlineStr">
         <is>
-          <t>Galaxy Watch5 44mm</t>
+          <t>Galaxy Watch4 44mm</t>
         </is>
       </c>
     </row>
@@ -4337,8 +4338,7 @@
       </c>
       <c r="C258" t="inlineStr">
         <is>
-          <t>Galaxy Watch5 Pro
-Galaxy Watch4 40mm</t>
+          <t>Galaxy Watch4 Classic 42mm</t>
         </is>
       </c>
     </row>
@@ -4353,7 +4353,7 @@
       </c>
       <c r="C259" t="inlineStr">
         <is>
-          <t>Galaxy Watch4 44mm</t>
+          <t>Galaxy Watch4 Classic 46mm</t>
         </is>
       </c>
     </row>
@@ -4368,7 +4368,7 @@
       </c>
       <c r="C260" t="inlineStr">
         <is>
-          <t>Galaxy Watch4 Classic 42mm</t>
+          <t>Galaxy Watch8 40mm</t>
         </is>
       </c>
     </row>
@@ -4383,7 +4383,7 @@
       </c>
       <c r="C261" t="inlineStr">
         <is>
-          <t>Galaxy Watch4 Classic 46mm</t>
+          <t>Galaxy Watch8 44mm</t>
         </is>
       </c>
     </row>
@@ -4398,7 +4398,7 @@
       </c>
       <c r="C262" t="inlineStr">
         <is>
-          <t>Galaxy Watch8 40mm</t>
+          <t>Galaxy Watch8 Classic 46mm</t>
         </is>
       </c>
     </row>
@@ -4413,7 +4413,7 @@
       </c>
       <c r="C263" t="inlineStr">
         <is>
-          <t>Galaxy Watch8 44mm</t>
+          <t>Galaxy Watch Ultra</t>
         </is>
       </c>
     </row>
@@ -4428,7 +4428,7 @@
       </c>
       <c r="C264" t="inlineStr">
         <is>
-          <t>Galaxy Watch8 Classic 46mm</t>
+          <t>Galaxy Watch7 40mm</t>
         </is>
       </c>
     </row>
@@ -4443,7 +4443,7 @@
       </c>
       <c r="C265" t="inlineStr">
         <is>
-          <t>Galaxy Watch Ultra</t>
+          <t>Galaxy Watch7 44mm</t>
         </is>
       </c>
     </row>
@@ -4458,7 +4458,7 @@
       </c>
       <c r="C266" t="inlineStr">
         <is>
-          <t>Galaxy Watch7 40mm</t>
+          <t>Galaxy Watch FE</t>
         </is>
       </c>
     </row>
@@ -4473,7 +4473,7 @@
       </c>
       <c r="C267" t="inlineStr">
         <is>
-          <t>Galaxy Watch7 44mm</t>
+          <t>Galaxy Watch6 40mm</t>
         </is>
       </c>
     </row>
@@ -4488,7 +4488,7 @@
       </c>
       <c r="C268" t="inlineStr">
         <is>
-          <t>Galaxy Watch FE</t>
+          <t>Galaxy Watch6 44mm</t>
         </is>
       </c>
     </row>
@@ -4503,7 +4503,7 @@
       </c>
       <c r="C269" t="inlineStr">
         <is>
-          <t>Galaxy Watch6 40mm</t>
+          <t>Galaxy Watch6 Classic 43mm</t>
         </is>
       </c>
     </row>
@@ -4518,7 +4518,7 @@
       </c>
       <c r="C270" t="inlineStr">
         <is>
-          <t>Galaxy Watch6 44mm</t>
+          <t>Galaxy Watch6 Classic 47mm</t>
         </is>
       </c>
     </row>
@@ -4533,7 +4533,7 @@
       </c>
       <c r="C271" t="inlineStr">
         <is>
-          <t>Galaxy Watch6 Classic 43mm</t>
+          <t>Galaxy Watch5 40mm</t>
         </is>
       </c>
     </row>
@@ -4548,7 +4548,7 @@
       </c>
       <c r="C272" t="inlineStr">
         <is>
-          <t>Galaxy Watch6 Classic 47mm</t>
+          <t>Galaxy Watch5 44mm</t>
         </is>
       </c>
     </row>
@@ -4563,7 +4563,7 @@
       </c>
       <c r="C273" t="inlineStr">
         <is>
-          <t>Galaxy Watch5 40mm</t>
+          <t>Galaxy Watch5 Pro</t>
         </is>
       </c>
     </row>
@@ -4578,7 +4578,7 @@
       </c>
       <c r="C274" t="inlineStr">
         <is>
-          <t>Galaxy Watch5 44mm</t>
+          <t>Galaxy Watch4 40mm</t>
         </is>
       </c>
     </row>
@@ -4593,7 +4593,7 @@
       </c>
       <c r="C275" t="inlineStr">
         <is>
-          <t>Galaxy Watch5 Pro</t>
+          <t>Galaxy Watch4 44mm</t>
         </is>
       </c>
     </row>
@@ -4608,7 +4608,7 @@
       </c>
       <c r="C276" t="inlineStr">
         <is>
-          <t>Galaxy Watch4 40mm</t>
+          <t>Galaxy Watch4 Classic 42mm</t>
         </is>
       </c>
     </row>
@@ -4623,7 +4623,7 @@
       </c>
       <c r="C277" t="inlineStr">
         <is>
-          <t>Galaxy Watch4 44mm</t>
+          <t>Galaxy Watch4 Classic 46mm</t>
         </is>
       </c>
     </row>
@@ -4638,7 +4638,8 @@
       </c>
       <c r="C278" t="inlineStr">
         <is>
-          <t>Galaxy Watch4 Classic 42mm</t>
+          <t>Galaxy XR Series
+Galaxy XR</t>
         </is>
       </c>
     </row>
@@ -4653,7 +4654,7 @@
       </c>
       <c r="C279" t="inlineStr">
         <is>
-          <t>Galaxy Watch4 Classic 46mm</t>
+          <t>Galaxy XR</t>
         </is>
       </c>
     </row>
@@ -4663,13 +4664,13 @@
       </c>
       <c r="B280" t="inlineStr">
         <is>
-          <t>Quarterly</t>
+          <t>No Information</t>
         </is>
       </c>
       <c r="C280" t="inlineStr">
         <is>
-          <t>Galaxy XR Series
-Galaxy XR</t>
+          <t>Galaxy Book Series
+Galaxy Book4 Ultra</t>
         </is>
       </c>
     </row>
@@ -4679,12 +4680,12 @@
       </c>
       <c r="B281" t="inlineStr">
         <is>
-          <t>Quarterly</t>
+          <t>No Information</t>
         </is>
       </c>
       <c r="C281" t="inlineStr">
         <is>
-          <t>Galaxy XR</t>
+          <t>Galaxy Book4 Pro</t>
         </is>
       </c>
     </row>
@@ -4699,8 +4700,7 @@
       </c>
       <c r="C282" t="inlineStr">
         <is>
-          <t>Galaxy Book Series
-Galaxy Book4 Ultra</t>
+          <t>Galaxy Book4 Pro 360</t>
         </is>
       </c>
     </row>
@@ -4715,7 +4715,7 @@
       </c>
       <c r="C283" t="inlineStr">
         <is>
-          <t>Galaxy Book4 Pro</t>
+          <t>Galaxy Book4 360</t>
         </is>
       </c>
     </row>
@@ -4730,7 +4730,7 @@
       </c>
       <c r="C284" t="inlineStr">
         <is>
-          <t>Galaxy Book4 Pro 360</t>
+          <t>Galaxy Book4</t>
         </is>
       </c>
     </row>
@@ -4745,7 +4745,7 @@
       </c>
       <c r="C285" t="inlineStr">
         <is>
-          <t>Galaxy Book4 360</t>
+          <t>Galaxy Book4 Ultra</t>
         </is>
       </c>
     </row>
@@ -4760,7 +4760,7 @@
       </c>
       <c r="C286" t="inlineStr">
         <is>
-          <t>Galaxy Book4</t>
+          <t>Galaxy Book4 Pro</t>
         </is>
       </c>
     </row>
@@ -4775,7 +4775,7 @@
       </c>
       <c r="C287" t="inlineStr">
         <is>
-          <t>Galaxy Book4 Ultra</t>
+          <t>Galaxy Book4 Pro 360</t>
         </is>
       </c>
     </row>
@@ -4790,7 +4790,7 @@
       </c>
       <c r="C288" t="inlineStr">
         <is>
-          <t>Galaxy Book4 Pro</t>
+          <t>Galaxy Book4 360</t>
         </is>
       </c>
     </row>
@@ -4804,36 +4804,6 @@
         </is>
       </c>
       <c r="C289" t="inlineStr">
-        <is>
-          <t>Galaxy Book4 Pro 360</t>
-        </is>
-      </c>
-    </row>
-    <row r="290">
-      <c r="A290" s="1" t="n">
-        <v>288</v>
-      </c>
-      <c r="B290" t="inlineStr">
-        <is>
-          <t>No Information</t>
-        </is>
-      </c>
-      <c r="C290" t="inlineStr">
-        <is>
-          <t>Galaxy Book4 360</t>
-        </is>
-      </c>
-    </row>
-    <row r="291">
-      <c r="A291" s="1" t="n">
-        <v>289</v>
-      </c>
-      <c r="B291" t="inlineStr">
-        <is>
-          <t>No Information</t>
-        </is>
-      </c>
-      <c r="C291" t="inlineStr">
         <is>
           <t>Galaxy Book4</t>
         </is>

--- a/dataset/samsung_device_updates.xlsx
+++ b/dataset/samsung_device_updates.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C289"/>
+  <dimension ref="A1:C291"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2029,8 +2029,7 @@
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>Galaxy A26 5G
-Galaxy A33 5G</t>
+          <t>Galaxy A26 5G</t>
         </is>
       </c>
     </row>
@@ -2045,7 +2044,8 @@
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>Galaxy A34 5G</t>
+          <t>Galaxy A27 5G
+Galaxy A33 5G</t>
         </is>
       </c>
     </row>
@@ -2060,7 +2060,7 @@
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>Galaxy A35 5G</t>
+          <t>Galaxy A34 5G</t>
         </is>
       </c>
     </row>
@@ -2075,7 +2075,7 @@
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>Galaxy A36 5G</t>
+          <t>Galaxy A35 5G</t>
         </is>
       </c>
     </row>
@@ -2090,8 +2090,7 @@
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>Galaxy A37 5G
-Galaxy A73 5G</t>
+          <t>Galaxy A36 5G</t>
         </is>
       </c>
     </row>
@@ -2106,7 +2105,8 @@
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>Galaxy A04</t>
+          <t>Galaxy A37 5G
+Galaxy A73 5G</t>
         </is>
       </c>
     </row>
@@ -2121,7 +2121,7 @@
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>Galaxy A04s</t>
+          <t>Galaxy A04</t>
         </is>
       </c>
     </row>
@@ -2136,7 +2136,7 @@
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>Galaxy A04e</t>
+          <t>Galaxy A04s</t>
         </is>
       </c>
     </row>
@@ -2151,7 +2151,7 @@
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>Galaxy A05</t>
+          <t>Galaxy A04e</t>
         </is>
       </c>
     </row>
@@ -2166,7 +2166,7 @@
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>Galaxy A05s</t>
+          <t>Galaxy A05</t>
         </is>
       </c>
     </row>
@@ -2181,7 +2181,7 @@
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>Galaxy A06</t>
+          <t>Galaxy A05s</t>
         </is>
       </c>
     </row>
@@ -2196,7 +2196,7 @@
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>Galaxy A06 5G</t>
+          <t>Galaxy A06</t>
         </is>
       </c>
     </row>
@@ -2211,7 +2211,7 @@
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>Galaxy A07</t>
+          <t>Galaxy A06 5G</t>
         </is>
       </c>
     </row>
@@ -2226,7 +2226,7 @@
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>Galaxy A07 5G</t>
+          <t>Galaxy A07</t>
         </is>
       </c>
     </row>
@@ -2241,7 +2241,7 @@
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>Galaxy A14</t>
+          <t>Galaxy A07 5G</t>
         </is>
       </c>
     </row>
@@ -2256,7 +2256,7 @@
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>Galaxy A14 5G</t>
+          <t>Galaxy A14</t>
         </is>
       </c>
     </row>
@@ -2271,7 +2271,7 @@
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>Galaxy A15</t>
+          <t>Galaxy A14 5G</t>
         </is>
       </c>
     </row>
@@ -2286,7 +2286,7 @@
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>Galaxy A15 5G</t>
+          <t>Galaxy A15</t>
         </is>
       </c>
     </row>
@@ -2301,7 +2301,7 @@
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>Galaxy A16</t>
+          <t>Galaxy A15 5G</t>
         </is>
       </c>
     </row>
@@ -2316,7 +2316,7 @@
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>Galaxy A16 5G</t>
+          <t>Galaxy A16</t>
         </is>
       </c>
     </row>
@@ -2331,7 +2331,7 @@
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>Galaxy A17</t>
+          <t>Galaxy A16 5G</t>
         </is>
       </c>
     </row>
@@ -2346,7 +2346,7 @@
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>Galaxy A17 5G</t>
+          <t>Galaxy A17</t>
         </is>
       </c>
     </row>
@@ -2361,7 +2361,7 @@
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>Galaxy A23 5G</t>
+          <t>Galaxy A17 5G</t>
         </is>
       </c>
     </row>
@@ -2376,7 +2376,7 @@
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>Galaxy A24</t>
+          <t>Galaxy A23 5G</t>
         </is>
       </c>
     </row>
@@ -2391,7 +2391,7 @@
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>Galaxy A25 5G</t>
+          <t>Galaxy A24</t>
         </is>
       </c>
     </row>
@@ -2406,7 +2406,7 @@
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>Galaxy A26 5G</t>
+          <t>Galaxy A25 5G</t>
         </is>
       </c>
     </row>
@@ -2421,7 +2421,7 @@
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>Galaxy A33 5G</t>
+          <t>Galaxy A26 5G</t>
         </is>
       </c>
     </row>
@@ -2436,7 +2436,7 @@
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>Galaxy A34 5G</t>
+          <t>Galaxy A27 5G</t>
         </is>
       </c>
     </row>
@@ -2451,7 +2451,7 @@
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>Galaxy A35 5G</t>
+          <t>Galaxy A33 5G</t>
         </is>
       </c>
     </row>
@@ -2466,7 +2466,7 @@
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>Galaxy A36 5G</t>
+          <t>Galaxy A34 5G</t>
         </is>
       </c>
     </row>
@@ -2481,7 +2481,7 @@
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>Galaxy A37 5G</t>
+          <t>Galaxy A35 5G</t>
         </is>
       </c>
     </row>
@@ -2496,7 +2496,7 @@
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>Galaxy A73 5G</t>
+          <t>Galaxy A36 5G</t>
         </is>
       </c>
     </row>
@@ -2511,8 +2511,7 @@
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t>Galaxy C Series
-Galaxy C55 5G</t>
+          <t>Galaxy A37 5G</t>
         </is>
       </c>
     </row>
@@ -2527,7 +2526,7 @@
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t>Galaxy C55 5G</t>
+          <t>Galaxy A73 5G</t>
         </is>
       </c>
     </row>
@@ -2542,8 +2541,8 @@
       </c>
       <c r="C140" t="inlineStr">
         <is>
-          <t>Galaxy M Series
-Galaxy M04</t>
+          <t>Galaxy C Series
+Galaxy C55 5G</t>
         </is>
       </c>
     </row>
@@ -2558,7 +2557,7 @@
       </c>
       <c r="C141" t="inlineStr">
         <is>
-          <t>Galaxy M05</t>
+          <t>Galaxy C55 5G</t>
         </is>
       </c>
     </row>
@@ -2573,7 +2572,8 @@
       </c>
       <c r="C142" t="inlineStr">
         <is>
-          <t>Galaxy M06 5G</t>
+          <t>Galaxy M Series
+Galaxy M04</t>
         </is>
       </c>
     </row>
@@ -2588,8 +2588,7 @@
       </c>
       <c r="C143" t="inlineStr">
         <is>
-          <t>Galaxy M07
-Galaxy M13</t>
+          <t>Galaxy M05</t>
         </is>
       </c>
     </row>
@@ -2604,7 +2603,7 @@
       </c>
       <c r="C144" t="inlineStr">
         <is>
-          <t>Galaxy M13 5G</t>
+          <t>Galaxy M06 5G</t>
         </is>
       </c>
     </row>
@@ -2619,7 +2618,8 @@
       </c>
       <c r="C145" t="inlineStr">
         <is>
-          <t>Galaxy M14</t>
+          <t>Galaxy M07
+Galaxy M13 5G</t>
         </is>
       </c>
     </row>
@@ -2634,7 +2634,7 @@
       </c>
       <c r="C146" t="inlineStr">
         <is>
-          <t>Galaxy M14 5G</t>
+          <t>Galaxy M14</t>
         </is>
       </c>
     </row>
@@ -2649,7 +2649,7 @@
       </c>
       <c r="C147" t="inlineStr">
         <is>
-          <t>Galaxy M15 5G</t>
+          <t>Galaxy M14 5G</t>
         </is>
       </c>
     </row>
@@ -2664,7 +2664,7 @@
       </c>
       <c r="C148" t="inlineStr">
         <is>
-          <t>Galaxy M16 5G</t>
+          <t>Galaxy M15 5G</t>
         </is>
       </c>
     </row>
@@ -2679,7 +2679,7 @@
       </c>
       <c r="C149" t="inlineStr">
         <is>
-          <t>Galaxy M17 5G</t>
+          <t>Galaxy M16 5G</t>
         </is>
       </c>
     </row>
@@ -2694,8 +2694,7 @@
       </c>
       <c r="C150" t="inlineStr">
         <is>
-          <t>Galaxy M17e 5G
-Galaxy M34 5G</t>
+          <t>Galaxy M17 5G</t>
         </is>
       </c>
     </row>
@@ -2710,7 +2709,8 @@
       </c>
       <c r="C151" t="inlineStr">
         <is>
-          <t>Galaxy M35 5G</t>
+          <t>Galaxy M17e 5G
+Galaxy M34 5G</t>
         </is>
       </c>
     </row>
@@ -2725,9 +2725,7 @@
       </c>
       <c r="C152" t="inlineStr">
         <is>
-          <t>Galaxy M36 5G
-Galaxy M44 5G
-Galaxy M54 5G</t>
+          <t>Galaxy M35 5G</t>
         </is>
       </c>
     </row>
@@ -2742,7 +2740,8 @@
       </c>
       <c r="C153" t="inlineStr">
         <is>
-          <t>Galaxy M55 5G</t>
+          <t>Galaxy M36 5G
+Galaxy M44 5G</t>
         </is>
       </c>
     </row>
@@ -2757,7 +2756,8 @@
       </c>
       <c r="C154" t="inlineStr">
         <is>
-          <t>Galaxy M55s 5G</t>
+          <t>Galaxy M47 5G
+Galaxy M54 5G</t>
         </is>
       </c>
     </row>
@@ -2772,7 +2772,7 @@
       </c>
       <c r="C155" t="inlineStr">
         <is>
-          <t>Galaxy M56 5G</t>
+          <t>Galaxy M55 5G</t>
         </is>
       </c>
     </row>
@@ -2787,7 +2787,7 @@
       </c>
       <c r="C156" t="inlineStr">
         <is>
-          <t>Galaxy M04</t>
+          <t>Galaxy M55s 5G</t>
         </is>
       </c>
     </row>
@@ -2802,7 +2802,7 @@
       </c>
       <c r="C157" t="inlineStr">
         <is>
-          <t>Galaxy M05</t>
+          <t>Galaxy M56 5G</t>
         </is>
       </c>
     </row>
@@ -2817,7 +2817,7 @@
       </c>
       <c r="C158" t="inlineStr">
         <is>
-          <t>Galaxy M06 5G</t>
+          <t>Galaxy M04</t>
         </is>
       </c>
     </row>
@@ -2832,7 +2832,7 @@
       </c>
       <c r="C159" t="inlineStr">
         <is>
-          <t>Galaxy M07</t>
+          <t>Galaxy M05</t>
         </is>
       </c>
     </row>
@@ -2847,7 +2847,7 @@
       </c>
       <c r="C160" t="inlineStr">
         <is>
-          <t>Galaxy M13</t>
+          <t>Galaxy M06 5G</t>
         </is>
       </c>
     </row>
@@ -2862,7 +2862,7 @@
       </c>
       <c r="C161" t="inlineStr">
         <is>
-          <t>Galaxy M13 5G</t>
+          <t>Galaxy M07</t>
         </is>
       </c>
     </row>
@@ -2877,7 +2877,7 @@
       </c>
       <c r="C162" t="inlineStr">
         <is>
-          <t>Galaxy M14</t>
+          <t>Galaxy M13 5G</t>
         </is>
       </c>
     </row>
@@ -2892,7 +2892,7 @@
       </c>
       <c r="C163" t="inlineStr">
         <is>
-          <t>Galaxy M14 5G</t>
+          <t>Galaxy M14</t>
         </is>
       </c>
     </row>
@@ -2907,7 +2907,7 @@
       </c>
       <c r="C164" t="inlineStr">
         <is>
-          <t>Galaxy M15 5G</t>
+          <t>Galaxy M14 5G</t>
         </is>
       </c>
     </row>
@@ -2922,7 +2922,7 @@
       </c>
       <c r="C165" t="inlineStr">
         <is>
-          <t>Galaxy M16 5G</t>
+          <t>Galaxy M15 5G</t>
         </is>
       </c>
     </row>
@@ -2937,7 +2937,7 @@
       </c>
       <c r="C166" t="inlineStr">
         <is>
-          <t>Galaxy M17 5G</t>
+          <t>Galaxy M16 5G</t>
         </is>
       </c>
     </row>
@@ -2952,7 +2952,7 @@
       </c>
       <c r="C167" t="inlineStr">
         <is>
-          <t>Galaxy M17e 5G</t>
+          <t>Galaxy M17 5G</t>
         </is>
       </c>
     </row>
@@ -2967,7 +2967,7 @@
       </c>
       <c r="C168" t="inlineStr">
         <is>
-          <t>Galaxy M34 5G</t>
+          <t>Galaxy M17e 5G</t>
         </is>
       </c>
     </row>
@@ -2982,7 +2982,7 @@
       </c>
       <c r="C169" t="inlineStr">
         <is>
-          <t>Galaxy M35 5G</t>
+          <t>Galaxy M34 5G</t>
         </is>
       </c>
     </row>
@@ -2997,7 +2997,7 @@
       </c>
       <c r="C170" t="inlineStr">
         <is>
-          <t>Galaxy M36 5G</t>
+          <t>Galaxy M35 5G</t>
         </is>
       </c>
     </row>
@@ -3012,7 +3012,7 @@
       </c>
       <c r="C171" t="inlineStr">
         <is>
-          <t>Galaxy M44 5G</t>
+          <t>Galaxy M36 5G</t>
         </is>
       </c>
     </row>
@@ -3027,7 +3027,7 @@
       </c>
       <c r="C172" t="inlineStr">
         <is>
-          <t>Galaxy M54 5G</t>
+          <t>Galaxy M44 5G</t>
         </is>
       </c>
     </row>
@@ -3042,7 +3042,7 @@
       </c>
       <c r="C173" t="inlineStr">
         <is>
-          <t>Galaxy M55 5G</t>
+          <t>Galaxy M47 5G</t>
         </is>
       </c>
     </row>
@@ -3057,7 +3057,7 @@
       </c>
       <c r="C174" t="inlineStr">
         <is>
-          <t>Galaxy M55s 5G</t>
+          <t>Galaxy M54 5G</t>
         </is>
       </c>
     </row>
@@ -3072,7 +3072,7 @@
       </c>
       <c r="C175" t="inlineStr">
         <is>
-          <t>Galaxy M56 5G</t>
+          <t>Galaxy M55 5G</t>
         </is>
       </c>
     </row>
@@ -3087,8 +3087,7 @@
       </c>
       <c r="C176" t="inlineStr">
         <is>
-          <t>Galaxy F Series
-Galaxy F04</t>
+          <t>Galaxy M55s 5G</t>
         </is>
       </c>
     </row>
@@ -3103,7 +3102,7 @@
       </c>
       <c r="C177" t="inlineStr">
         <is>
-          <t>Galaxy F05</t>
+          <t>Galaxy M56 5G</t>
         </is>
       </c>
     </row>
@@ -3118,7 +3117,8 @@
       </c>
       <c r="C178" t="inlineStr">
         <is>
-          <t>Galaxy F06 5G</t>
+          <t>Galaxy F Series
+Galaxy F04</t>
         </is>
       </c>
     </row>
@@ -3133,7 +3133,7 @@
       </c>
       <c r="C179" t="inlineStr">
         <is>
-          <t>Galaxy F07</t>
+          <t>Galaxy F05</t>
         </is>
       </c>
     </row>
@@ -3148,8 +3148,7 @@
       </c>
       <c r="C180" t="inlineStr">
         <is>
-          <t>Galaxy F70e 5G
-Galaxy F13</t>
+          <t>Galaxy F06 5G</t>
         </is>
       </c>
     </row>
@@ -3164,7 +3163,7 @@
       </c>
       <c r="C181" t="inlineStr">
         <is>
-          <t>Galaxy F14</t>
+          <t>Galaxy F07</t>
         </is>
       </c>
     </row>
@@ -3179,7 +3178,8 @@
       </c>
       <c r="C182" t="inlineStr">
         <is>
-          <t>Galaxy F14 5G</t>
+          <t>Galaxy F70e 5G
+Galaxy F13</t>
         </is>
       </c>
     </row>
@@ -3194,7 +3194,7 @@
       </c>
       <c r="C183" t="inlineStr">
         <is>
-          <t>Galaxy F15 5G</t>
+          <t>Galaxy F14</t>
         </is>
       </c>
     </row>
@@ -3209,7 +3209,7 @@
       </c>
       <c r="C184" t="inlineStr">
         <is>
-          <t>Galaxy F16 5G</t>
+          <t>Galaxy F14 5G</t>
         </is>
       </c>
     </row>
@@ -3224,8 +3224,7 @@
       </c>
       <c r="C185" t="inlineStr">
         <is>
-          <t>Galaxy F17 5G
-Galaxy F34 5G</t>
+          <t>Galaxy F15 5G</t>
         </is>
       </c>
     </row>
@@ -3240,8 +3239,7 @@
       </c>
       <c r="C186" t="inlineStr">
         <is>
-          <t>Galaxy F36 5G
-Galaxy F54 5G</t>
+          <t>Galaxy F16 5G</t>
         </is>
       </c>
     </row>
@@ -3256,7 +3254,8 @@
       </c>
       <c r="C187" t="inlineStr">
         <is>
-          <t>Galaxy F55 5G</t>
+          <t>Galaxy F17 5G
+Galaxy F34 5G</t>
         </is>
       </c>
     </row>
@@ -3271,7 +3270,8 @@
       </c>
       <c r="C188" t="inlineStr">
         <is>
-          <t>Galaxy F56 5G</t>
+          <t>Galaxy F36 5G
+Galaxy F54 5G</t>
         </is>
       </c>
     </row>
@@ -3286,7 +3286,7 @@
       </c>
       <c r="C189" t="inlineStr">
         <is>
-          <t>Galaxy F04</t>
+          <t>Galaxy F55 5G</t>
         </is>
       </c>
     </row>
@@ -3301,7 +3301,7 @@
       </c>
       <c r="C190" t="inlineStr">
         <is>
-          <t>Galaxy F05</t>
+          <t>Galaxy F56 5G</t>
         </is>
       </c>
     </row>
@@ -3316,7 +3316,7 @@
       </c>
       <c r="C191" t="inlineStr">
         <is>
-          <t>Galaxy F06 5G</t>
+          <t>Galaxy F04</t>
         </is>
       </c>
     </row>
@@ -3331,7 +3331,7 @@
       </c>
       <c r="C192" t="inlineStr">
         <is>
-          <t>Galaxy F07</t>
+          <t>Galaxy F05</t>
         </is>
       </c>
     </row>
@@ -3346,7 +3346,7 @@
       </c>
       <c r="C193" t="inlineStr">
         <is>
-          <t>Galaxy F70e 5G</t>
+          <t>Galaxy F06 5G</t>
         </is>
       </c>
     </row>
@@ -3361,7 +3361,7 @@
       </c>
       <c r="C194" t="inlineStr">
         <is>
-          <t>Galaxy F13</t>
+          <t>Galaxy F07</t>
         </is>
       </c>
     </row>
@@ -3376,7 +3376,7 @@
       </c>
       <c r="C195" t="inlineStr">
         <is>
-          <t>Galaxy F14</t>
+          <t>Galaxy F70e 5G</t>
         </is>
       </c>
     </row>
@@ -3391,7 +3391,7 @@
       </c>
       <c r="C196" t="inlineStr">
         <is>
-          <t>Galaxy F14 5G</t>
+          <t>Galaxy F13</t>
         </is>
       </c>
     </row>
@@ -3406,7 +3406,7 @@
       </c>
       <c r="C197" t="inlineStr">
         <is>
-          <t>Galaxy F15 5G</t>
+          <t>Galaxy F14</t>
         </is>
       </c>
     </row>
@@ -3421,7 +3421,7 @@
       </c>
       <c r="C198" t="inlineStr">
         <is>
-          <t>Galaxy F16 5G</t>
+          <t>Galaxy F14 5G</t>
         </is>
       </c>
     </row>
@@ -3436,7 +3436,7 @@
       </c>
       <c r="C199" t="inlineStr">
         <is>
-          <t>Galaxy F17 5G</t>
+          <t>Galaxy F15 5G</t>
         </is>
       </c>
     </row>
@@ -3451,7 +3451,7 @@
       </c>
       <c r="C200" t="inlineStr">
         <is>
-          <t>Galaxy F34 5G</t>
+          <t>Galaxy F16 5G</t>
         </is>
       </c>
     </row>
@@ -3466,7 +3466,7 @@
       </c>
       <c r="C201" t="inlineStr">
         <is>
-          <t>Galaxy F36 5G</t>
+          <t>Galaxy F17 5G</t>
         </is>
       </c>
     </row>
@@ -3481,7 +3481,7 @@
       </c>
       <c r="C202" t="inlineStr">
         <is>
-          <t>Galaxy F54 5G</t>
+          <t>Galaxy F34 5G</t>
         </is>
       </c>
     </row>
@@ -3496,7 +3496,7 @@
       </c>
       <c r="C203" t="inlineStr">
         <is>
-          <t>Galaxy F55 5G</t>
+          <t>Galaxy F36 5G</t>
         </is>
       </c>
     </row>
@@ -3511,7 +3511,7 @@
       </c>
       <c r="C204" t="inlineStr">
         <is>
-          <t>Galaxy F56 5G</t>
+          <t>Galaxy F54 5G</t>
         </is>
       </c>
     </row>
@@ -3526,8 +3526,7 @@
       </c>
       <c r="C205" t="inlineStr">
         <is>
-          <t>Galaxy Tab S Series
-Galaxy Tab S11</t>
+          <t>Galaxy F55 5G</t>
         </is>
       </c>
     </row>
@@ -3542,8 +3541,7 @@
       </c>
       <c r="C206" t="inlineStr">
         <is>
-          <t>Galaxy Tab S11 Ultra
-Galaxy Tab S10+</t>
+          <t>Galaxy F56 5G</t>
         </is>
       </c>
     </row>
@@ -3558,7 +3556,8 @@
       </c>
       <c r="C207" t="inlineStr">
         <is>
-          <t>Galaxy Tab S10 Ultra</t>
+          <t>Galaxy Tab S Series
+Galaxy Tab S11</t>
         </is>
       </c>
     </row>
@@ -3573,7 +3572,8 @@
       </c>
       <c r="C208" t="inlineStr">
         <is>
-          <t>Galaxy Tab S10 FE</t>
+          <t>Galaxy Tab S11 Ultra
+Galaxy Tab S10+</t>
         </is>
       </c>
     </row>
@@ -3588,7 +3588,7 @@
       </c>
       <c r="C209" t="inlineStr">
         <is>
-          <t>Galaxy Tab S10 FE+</t>
+          <t>Galaxy Tab S10 Ultra</t>
         </is>
       </c>
     </row>
@@ -3603,8 +3603,7 @@
       </c>
       <c r="C210" t="inlineStr">
         <is>
-          <t>Galaxy Tab S10 Lite
-Galaxy Tab S9</t>
+          <t>Galaxy Tab S10 FE</t>
         </is>
       </c>
     </row>
@@ -3619,7 +3618,7 @@
       </c>
       <c r="C211" t="inlineStr">
         <is>
-          <t>Galaxy Tab S9+</t>
+          <t>Galaxy Tab S10 FE+</t>
         </is>
       </c>
     </row>
@@ -3634,7 +3633,8 @@
       </c>
       <c r="C212" t="inlineStr">
         <is>
-          <t>Galaxy Tab S9 Ultra</t>
+          <t>Galaxy Tab S10 Lite
+Galaxy Tab S9</t>
         </is>
       </c>
     </row>
@@ -3649,7 +3649,7 @@
       </c>
       <c r="C213" t="inlineStr">
         <is>
-          <t>Galaxy Tab S9 FE</t>
+          <t>Galaxy Tab S9+</t>
         </is>
       </c>
     </row>
@@ -3664,8 +3664,7 @@
       </c>
       <c r="C214" t="inlineStr">
         <is>
-          <t>Galaxy Tab S9 FE+
-Galaxy Tab S8</t>
+          <t>Galaxy Tab S9 Ultra</t>
         </is>
       </c>
     </row>
@@ -3680,7 +3679,7 @@
       </c>
       <c r="C215" t="inlineStr">
         <is>
-          <t>Galaxy Tab S8+</t>
+          <t>Galaxy Tab S9 FE</t>
         </is>
       </c>
     </row>
@@ -3695,8 +3694,8 @@
       </c>
       <c r="C216" t="inlineStr">
         <is>
-          <t>Galaxy Tab S8 Ultra
-Galaxy Tab S6 Lite (2024)</t>
+          <t>Galaxy Tab S9 FE+
+Galaxy Tab S8</t>
         </is>
       </c>
     </row>
@@ -3711,7 +3710,7 @@
       </c>
       <c r="C217" t="inlineStr">
         <is>
-          <t>Galaxy Tab S11</t>
+          <t>Galaxy Tab S8+</t>
         </is>
       </c>
     </row>
@@ -3726,7 +3725,8 @@
       </c>
       <c r="C218" t="inlineStr">
         <is>
-          <t>Galaxy Tab S11 Ultra</t>
+          <t>Galaxy Tab S8 Ultra
+Galaxy Tab S6 Lite (2024)</t>
         </is>
       </c>
     </row>
@@ -3741,7 +3741,7 @@
       </c>
       <c r="C219" t="inlineStr">
         <is>
-          <t>Galaxy Tab S10+</t>
+          <t>Galaxy Tab S11</t>
         </is>
       </c>
     </row>
@@ -3756,7 +3756,7 @@
       </c>
       <c r="C220" t="inlineStr">
         <is>
-          <t>Galaxy Tab S10 Ultra</t>
+          <t>Galaxy Tab S11 Ultra</t>
         </is>
       </c>
     </row>
@@ -3771,7 +3771,7 @@
       </c>
       <c r="C221" t="inlineStr">
         <is>
-          <t>Galaxy Tab S10 FE</t>
+          <t>Galaxy Tab S10+</t>
         </is>
       </c>
     </row>
@@ -3786,7 +3786,7 @@
       </c>
       <c r="C222" t="inlineStr">
         <is>
-          <t>Galaxy Tab S10 FE+</t>
+          <t>Galaxy Tab S10 Ultra</t>
         </is>
       </c>
     </row>
@@ -3801,7 +3801,7 @@
       </c>
       <c r="C223" t="inlineStr">
         <is>
-          <t>Galaxy Tab S10 Lite</t>
+          <t>Galaxy Tab S10 FE</t>
         </is>
       </c>
     </row>
@@ -3816,7 +3816,7 @@
       </c>
       <c r="C224" t="inlineStr">
         <is>
-          <t>Galaxy Tab S9</t>
+          <t>Galaxy Tab S10 FE+</t>
         </is>
       </c>
     </row>
@@ -3831,7 +3831,7 @@
       </c>
       <c r="C225" t="inlineStr">
         <is>
-          <t>Galaxy Tab S9+</t>
+          <t>Galaxy Tab S10 Lite</t>
         </is>
       </c>
     </row>
@@ -3846,7 +3846,7 @@
       </c>
       <c r="C226" t="inlineStr">
         <is>
-          <t>Galaxy Tab S9 Ultra</t>
+          <t>Galaxy Tab S9</t>
         </is>
       </c>
     </row>
@@ -3861,7 +3861,7 @@
       </c>
       <c r="C227" t="inlineStr">
         <is>
-          <t>Galaxy Tab S9 FE</t>
+          <t>Galaxy Tab S9+</t>
         </is>
       </c>
     </row>
@@ -3876,7 +3876,7 @@
       </c>
       <c r="C228" t="inlineStr">
         <is>
-          <t>Galaxy Tab S9 FE+</t>
+          <t>Galaxy Tab S9 Ultra</t>
         </is>
       </c>
     </row>
@@ -3891,7 +3891,7 @@
       </c>
       <c r="C229" t="inlineStr">
         <is>
-          <t>Galaxy Tab S8</t>
+          <t>Galaxy Tab S9 FE</t>
         </is>
       </c>
     </row>
@@ -3906,7 +3906,7 @@
       </c>
       <c r="C230" t="inlineStr">
         <is>
-          <t>Galaxy Tab S8+</t>
+          <t>Galaxy Tab S9 FE+</t>
         </is>
       </c>
     </row>
@@ -3921,7 +3921,7 @@
       </c>
       <c r="C231" t="inlineStr">
         <is>
-          <t>Galaxy Tab S8 Ultra</t>
+          <t>Galaxy Tab S8</t>
         </is>
       </c>
     </row>
@@ -3936,7 +3936,7 @@
       </c>
       <c r="C232" t="inlineStr">
         <is>
-          <t>Galaxy Tab S6 Lite (2024)</t>
+          <t>Galaxy Tab S8+</t>
         </is>
       </c>
     </row>
@@ -3951,8 +3951,7 @@
       </c>
       <c r="C233" t="inlineStr">
         <is>
-          <t>Galaxy Tab A Series
-Galaxy Tab A11</t>
+          <t>Galaxy Tab S8 Ultra</t>
         </is>
       </c>
     </row>
@@ -3967,8 +3966,7 @@
       </c>
       <c r="C234" t="inlineStr">
         <is>
-          <t>Galaxy Tab A11+
-Galaxy Tab A9</t>
+          <t>Galaxy Tab S6 Lite (2024)</t>
         </is>
       </c>
     </row>
@@ -3983,7 +3981,8 @@
       </c>
       <c r="C235" t="inlineStr">
         <is>
-          <t>Galaxy Tab A9+</t>
+          <t>Galaxy Tab A Series
+Galaxy Tab A11</t>
         </is>
       </c>
     </row>
@@ -3998,7 +3997,8 @@
       </c>
       <c r="C236" t="inlineStr">
         <is>
-          <t>Galaxy Tab A9+(2025)</t>
+          <t>Galaxy Tab A11+
+Galaxy Tab A9</t>
         </is>
       </c>
     </row>
@@ -4013,7 +4013,7 @@
       </c>
       <c r="C237" t="inlineStr">
         <is>
-          <t>Galaxy Tab A11</t>
+          <t>Galaxy Tab A9+</t>
         </is>
       </c>
     </row>
@@ -4028,7 +4028,7 @@
       </c>
       <c r="C238" t="inlineStr">
         <is>
-          <t>Galaxy Tab A11+</t>
+          <t>Galaxy Tab A9+(2025)</t>
         </is>
       </c>
     </row>
@@ -4043,7 +4043,7 @@
       </c>
       <c r="C239" t="inlineStr">
         <is>
-          <t>Galaxy Tab A9</t>
+          <t>Galaxy Tab A11</t>
         </is>
       </c>
     </row>
@@ -4058,7 +4058,7 @@
       </c>
       <c r="C240" t="inlineStr">
         <is>
-          <t>Galaxy Tab A9+</t>
+          <t>Galaxy Tab A11+</t>
         </is>
       </c>
     </row>
@@ -4073,7 +4073,7 @@
       </c>
       <c r="C241" t="inlineStr">
         <is>
-          <t>Galaxy Tab A9+(2025)</t>
+          <t>Galaxy Tab A9</t>
         </is>
       </c>
     </row>
@@ -4088,43 +4088,42 @@
       </c>
       <c r="C242" t="inlineStr">
         <is>
+          <t>Galaxy Tab A9+</t>
+        </is>
+      </c>
+    </row>
+    <row r="243">
+      <c r="A243" s="1" t="n">
+        <v>241</v>
+      </c>
+      <c r="B243" t="inlineStr">
+        <is>
+          <t>Quarterly</t>
+        </is>
+      </c>
+      <c r="C243" t="inlineStr">
+        <is>
+          <t>Galaxy Tab A9+(2025)</t>
+        </is>
+      </c>
+    </row>
+    <row r="244">
+      <c r="A244" s="1" t="n">
+        <v>242</v>
+      </c>
+      <c r="B244" t="inlineStr">
+        <is>
+          <t>Quarterly</t>
+        </is>
+      </c>
+      <c r="C244" t="inlineStr">
+        <is>
           <t>Enterprise Models
 Galaxy A53 5G 
 Galaxy Tab Active4 Pro</t>
         </is>
       </c>
     </row>
-    <row r="243">
-      <c r="A243" s="1" t="n">
-        <v>241</v>
-      </c>
-      <c r="B243" t="inlineStr">
-        <is>
-          <t>Quarterly</t>
-        </is>
-      </c>
-      <c r="C243" t="inlineStr">
-        <is>
-          <t>Galaxy Tab Active5
-Galaxy XCover5</t>
-        </is>
-      </c>
-    </row>
-    <row r="244">
-      <c r="A244" s="1" t="n">
-        <v>242</v>
-      </c>
-      <c r="B244" t="inlineStr">
-        <is>
-          <t>Quarterly</t>
-        </is>
-      </c>
-      <c r="C244" t="inlineStr">
-        <is>
-          <t>Galaxy A53 5G</t>
-        </is>
-      </c>
-    </row>
     <row r="245">
       <c r="A245" s="1" t="n">
         <v>243</v>
@@ -4136,7 +4135,8 @@
       </c>
       <c r="C245" t="inlineStr">
         <is>
-          <t>Galaxy Tab Active4 Pro</t>
+          <t>Galaxy Tab Active5
+Galaxy XCover5</t>
         </is>
       </c>
     </row>
@@ -4151,7 +4151,7 @@
       </c>
       <c r="C246" t="inlineStr">
         <is>
-          <t>Galaxy Tab Active5</t>
+          <t>Galaxy A53 5G</t>
         </is>
       </c>
     </row>
@@ -4166,7 +4166,7 @@
       </c>
       <c r="C247" t="inlineStr">
         <is>
-          <t>Galaxy XCover5</t>
+          <t>Galaxy Tab Active4 Pro</t>
         </is>
       </c>
     </row>
@@ -4181,8 +4181,7 @@
       </c>
       <c r="C248" t="inlineStr">
         <is>
-          <t>Galaxy Watch Series
-Galaxy Watch8 40mm</t>
+          <t>Galaxy Tab Active5</t>
         </is>
       </c>
     </row>
@@ -4197,7 +4196,7 @@
       </c>
       <c r="C249" t="inlineStr">
         <is>
-          <t>Galaxy Watch8 44mm</t>
+          <t>Galaxy XCover5</t>
         </is>
       </c>
     </row>
@@ -4212,22 +4211,53 @@
       </c>
       <c r="C250" t="inlineStr">
         <is>
+          <t>Galaxy Watch Series
+Galaxy Watch8 40mm</t>
+        </is>
+      </c>
+    </row>
+    <row r="251">
+      <c r="A251" s="1" t="n">
+        <v>249</v>
+      </c>
+      <c r="B251" t="inlineStr">
+        <is>
+          <t>Quarterly</t>
+        </is>
+      </c>
+      <c r="C251" t="inlineStr">
+        <is>
+          <t>Galaxy Watch8 44mm</t>
+        </is>
+      </c>
+    </row>
+    <row r="252">
+      <c r="A252" s="1" t="n">
+        <v>250</v>
+      </c>
+      <c r="B252" t="inlineStr">
+        <is>
+          <t>Quarterly</t>
+        </is>
+      </c>
+      <c r="C252" t="inlineStr">
+        <is>
           <t>Galaxy Watch8 Classic 46mm
 Galaxy Watch Ultra
 Galaxy Watch7 40mm</t>
         </is>
       </c>
     </row>
-    <row r="251">
-      <c r="A251" s="1" t="n">
-        <v>249</v>
-      </c>
-      <c r="B251" t="inlineStr">
-        <is>
-          <t>Quarterly</t>
-        </is>
-      </c>
-      <c r="C251" t="inlineStr">
+    <row r="253">
+      <c r="A253" s="1" t="n">
+        <v>251</v>
+      </c>
+      <c r="B253" t="inlineStr">
+        <is>
+          <t>Quarterly</t>
+        </is>
+      </c>
+      <c r="C253" t="inlineStr">
         <is>
           <t>Galaxy Watch7 44mm
 Galaxy Watch FE
@@ -4235,36 +4265,6 @@
         </is>
       </c>
     </row>
-    <row r="252">
-      <c r="A252" s="1" t="n">
-        <v>250</v>
-      </c>
-      <c r="B252" t="inlineStr">
-        <is>
-          <t>Quarterly</t>
-        </is>
-      </c>
-      <c r="C252" t="inlineStr">
-        <is>
-          <t>Galaxy Watch6 44mm</t>
-        </is>
-      </c>
-    </row>
-    <row r="253">
-      <c r="A253" s="1" t="n">
-        <v>251</v>
-      </c>
-      <c r="B253" t="inlineStr">
-        <is>
-          <t>Quarterly</t>
-        </is>
-      </c>
-      <c r="C253" t="inlineStr">
-        <is>
-          <t>Galaxy Watch6 Classic 43mm</t>
-        </is>
-      </c>
-    </row>
     <row r="254">
       <c r="A254" s="1" t="n">
         <v>252</v>
@@ -4276,8 +4276,7 @@
       </c>
       <c r="C254" t="inlineStr">
         <is>
-          <t>Galaxy Watch6 Classic 47mm
-Galaxy Watch5 40mm</t>
+          <t>Galaxy Watch6 44mm</t>
         </is>
       </c>
     </row>
@@ -4292,7 +4291,7 @@
       </c>
       <c r="C255" t="inlineStr">
         <is>
-          <t>Galaxy Watch5 44mm</t>
+          <t>Galaxy Watch6 Classic 43mm</t>
         </is>
       </c>
     </row>
@@ -4307,8 +4306,8 @@
       </c>
       <c r="C256" t="inlineStr">
         <is>
-          <t>Galaxy Watch5 Pro
-Galaxy Watch4 40mm</t>
+          <t>Galaxy Watch6 Classic 47mm
+Galaxy Watch5 40mm</t>
         </is>
       </c>
     </row>
@@ -4323,7 +4322,7 @@
       </c>
       <c r="C257" t="inlineStr">
         <is>
-          <t>Galaxy Watch4 44mm</t>
+          <t>Galaxy Watch5 44mm</t>
         </is>
       </c>
     </row>
@@ -4338,7 +4337,8 @@
       </c>
       <c r="C258" t="inlineStr">
         <is>
-          <t>Galaxy Watch4 Classic 42mm</t>
+          <t>Galaxy Watch5 Pro
+Galaxy Watch4 40mm</t>
         </is>
       </c>
     </row>
@@ -4353,7 +4353,7 @@
       </c>
       <c r="C259" t="inlineStr">
         <is>
-          <t>Galaxy Watch4 Classic 46mm</t>
+          <t>Galaxy Watch4 44mm</t>
         </is>
       </c>
     </row>
@@ -4368,7 +4368,7 @@
       </c>
       <c r="C260" t="inlineStr">
         <is>
-          <t>Galaxy Watch8 40mm</t>
+          <t>Galaxy Watch4 Classic 42mm</t>
         </is>
       </c>
     </row>
@@ -4383,7 +4383,7 @@
       </c>
       <c r="C261" t="inlineStr">
         <is>
-          <t>Galaxy Watch8 44mm</t>
+          <t>Galaxy Watch4 Classic 46mm</t>
         </is>
       </c>
     </row>
@@ -4398,7 +4398,7 @@
       </c>
       <c r="C262" t="inlineStr">
         <is>
-          <t>Galaxy Watch8 Classic 46mm</t>
+          <t>Galaxy Watch8 40mm</t>
         </is>
       </c>
     </row>
@@ -4413,7 +4413,7 @@
       </c>
       <c r="C263" t="inlineStr">
         <is>
-          <t>Galaxy Watch Ultra</t>
+          <t>Galaxy Watch8 44mm</t>
         </is>
       </c>
     </row>
@@ -4428,7 +4428,7 @@
       </c>
       <c r="C264" t="inlineStr">
         <is>
-          <t>Galaxy Watch7 40mm</t>
+          <t>Galaxy Watch8 Classic 46mm</t>
         </is>
       </c>
     </row>
@@ -4443,7 +4443,7 @@
       </c>
       <c r="C265" t="inlineStr">
         <is>
-          <t>Galaxy Watch7 44mm</t>
+          <t>Galaxy Watch Ultra</t>
         </is>
       </c>
     </row>
@@ -4458,7 +4458,7 @@
       </c>
       <c r="C266" t="inlineStr">
         <is>
-          <t>Galaxy Watch FE</t>
+          <t>Galaxy Watch7 40mm</t>
         </is>
       </c>
     </row>
@@ -4473,7 +4473,7 @@
       </c>
       <c r="C267" t="inlineStr">
         <is>
-          <t>Galaxy Watch6 40mm</t>
+          <t>Galaxy Watch7 44mm</t>
         </is>
       </c>
     </row>
@@ -4488,7 +4488,7 @@
       </c>
       <c r="C268" t="inlineStr">
         <is>
-          <t>Galaxy Watch6 44mm</t>
+          <t>Galaxy Watch FE</t>
         </is>
       </c>
     </row>
@@ -4503,7 +4503,7 @@
       </c>
       <c r="C269" t="inlineStr">
         <is>
-          <t>Galaxy Watch6 Classic 43mm</t>
+          <t>Galaxy Watch6 40mm</t>
         </is>
       </c>
     </row>
@@ -4518,7 +4518,7 @@
       </c>
       <c r="C270" t="inlineStr">
         <is>
-          <t>Galaxy Watch6 Classic 47mm</t>
+          <t>Galaxy Watch6 44mm</t>
         </is>
       </c>
     </row>
@@ -4533,7 +4533,7 @@
       </c>
       <c r="C271" t="inlineStr">
         <is>
-          <t>Galaxy Watch5 40mm</t>
+          <t>Galaxy Watch6 Classic 43mm</t>
         </is>
       </c>
     </row>
@@ -4548,7 +4548,7 @@
       </c>
       <c r="C272" t="inlineStr">
         <is>
-          <t>Galaxy Watch5 44mm</t>
+          <t>Galaxy Watch6 Classic 47mm</t>
         </is>
       </c>
     </row>
@@ -4563,7 +4563,7 @@
       </c>
       <c r="C273" t="inlineStr">
         <is>
-          <t>Galaxy Watch5 Pro</t>
+          <t>Galaxy Watch5 40mm</t>
         </is>
       </c>
     </row>
@@ -4578,7 +4578,7 @@
       </c>
       <c r="C274" t="inlineStr">
         <is>
-          <t>Galaxy Watch4 40mm</t>
+          <t>Galaxy Watch5 44mm</t>
         </is>
       </c>
     </row>
@@ -4593,7 +4593,7 @@
       </c>
       <c r="C275" t="inlineStr">
         <is>
-          <t>Galaxy Watch4 44mm</t>
+          <t>Galaxy Watch5 Pro</t>
         </is>
       </c>
     </row>
@@ -4608,7 +4608,7 @@
       </c>
       <c r="C276" t="inlineStr">
         <is>
-          <t>Galaxy Watch4 Classic 42mm</t>
+          <t>Galaxy Watch4 40mm</t>
         </is>
       </c>
     </row>
@@ -4623,7 +4623,7 @@
       </c>
       <c r="C277" t="inlineStr">
         <is>
-          <t>Galaxy Watch4 Classic 46mm</t>
+          <t>Galaxy Watch4 44mm</t>
         </is>
       </c>
     </row>
@@ -4638,8 +4638,7 @@
       </c>
       <c r="C278" t="inlineStr">
         <is>
-          <t>Galaxy XR Series
-Galaxy XR</t>
+          <t>Galaxy Watch4 Classic 42mm</t>
         </is>
       </c>
     </row>
@@ -4654,7 +4653,7 @@
       </c>
       <c r="C279" t="inlineStr">
         <is>
-          <t>Galaxy XR</t>
+          <t>Galaxy Watch4 Classic 46mm</t>
         </is>
       </c>
     </row>
@@ -4664,13 +4663,13 @@
       </c>
       <c r="B280" t="inlineStr">
         <is>
-          <t>No Information</t>
+          <t>Quarterly</t>
         </is>
       </c>
       <c r="C280" t="inlineStr">
         <is>
-          <t>Galaxy Book Series
-Galaxy Book4 Ultra</t>
+          <t>Galaxy XR Series
+Galaxy XR</t>
         </is>
       </c>
     </row>
@@ -4680,12 +4679,12 @@
       </c>
       <c r="B281" t="inlineStr">
         <is>
-          <t>No Information</t>
+          <t>Quarterly</t>
         </is>
       </c>
       <c r="C281" t="inlineStr">
         <is>
-          <t>Galaxy Book4 Pro</t>
+          <t>Galaxy XR</t>
         </is>
       </c>
     </row>
@@ -4700,7 +4699,8 @@
       </c>
       <c r="C282" t="inlineStr">
         <is>
-          <t>Galaxy Book4 Pro 360</t>
+          <t>Galaxy Book Series
+Galaxy Book4 Ultra</t>
         </is>
       </c>
     </row>
@@ -4715,7 +4715,7 @@
       </c>
       <c r="C283" t="inlineStr">
         <is>
-          <t>Galaxy Book4 360</t>
+          <t>Galaxy Book4 Pro</t>
         </is>
       </c>
     </row>
@@ -4730,7 +4730,7 @@
       </c>
       <c r="C284" t="inlineStr">
         <is>
-          <t>Galaxy Book4</t>
+          <t>Galaxy Book4 Pro 360</t>
         </is>
       </c>
     </row>
@@ -4745,7 +4745,7 @@
       </c>
       <c r="C285" t="inlineStr">
         <is>
-          <t>Galaxy Book4 Ultra</t>
+          <t>Galaxy Book4 360</t>
         </is>
       </c>
     </row>
@@ -4760,7 +4760,7 @@
       </c>
       <c r="C286" t="inlineStr">
         <is>
-          <t>Galaxy Book4 Pro</t>
+          <t>Galaxy Book4</t>
         </is>
       </c>
     </row>
@@ -4775,7 +4775,7 @@
       </c>
       <c r="C287" t="inlineStr">
         <is>
-          <t>Galaxy Book4 Pro 360</t>
+          <t>Galaxy Book4 Ultra</t>
         </is>
       </c>
     </row>
@@ -4790,7 +4790,7 @@
       </c>
       <c r="C288" t="inlineStr">
         <is>
-          <t>Galaxy Book4 360</t>
+          <t>Galaxy Book4 Pro</t>
         </is>
       </c>
     </row>
@@ -4804,6 +4804,36 @@
         </is>
       </c>
       <c r="C289" t="inlineStr">
+        <is>
+          <t>Galaxy Book4 Pro 360</t>
+        </is>
+      </c>
+    </row>
+    <row r="290">
+      <c r="A290" s="1" t="n">
+        <v>288</v>
+      </c>
+      <c r="B290" t="inlineStr">
+        <is>
+          <t>No Information</t>
+        </is>
+      </c>
+      <c r="C290" t="inlineStr">
+        <is>
+          <t>Galaxy Book4 360</t>
+        </is>
+      </c>
+    </row>
+    <row r="291">
+      <c r="A291" s="1" t="n">
+        <v>289</v>
+      </c>
+      <c r="B291" t="inlineStr">
+        <is>
+          <t>No Information</t>
+        </is>
+      </c>
+      <c r="C291" t="inlineStr">
         <is>
           <t>Galaxy Book4</t>
         </is>

--- a/dataset/samsung_device_updates.xlsx
+++ b/dataset/samsung_device_updates.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C291"/>
+  <dimension ref="A1:C298"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -513,8 +513,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Galaxy Z Fold Special Edition
-Galaxy Z Flip4</t>
+          <t>Galaxy Z Fold Special Edition</t>
         </is>
       </c>
     </row>
@@ -529,7 +528,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Galaxy Z Flip5</t>
+          <t>Galaxy Z Fold8</t>
         </is>
       </c>
     </row>
@@ -544,7 +543,8 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Galaxy Z Flip6</t>
+          <t>Galaxy Z Fold8 Ultra
+Galaxy Z Flip4</t>
         </is>
       </c>
     </row>
@@ -559,7 +559,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Galaxy Z Flip7</t>
+          <t>Galaxy Z Flip5</t>
         </is>
       </c>
     </row>
@@ -574,8 +574,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Galaxy Z Flip7 FE
-W23</t>
+          <t>Galaxy Z Flip6</t>
         </is>
       </c>
     </row>
@@ -590,7 +589,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>W23 Flip</t>
+          <t>Galaxy Z Flip7</t>
         </is>
       </c>
     </row>
@@ -605,7 +604,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>W24</t>
+          <t>Galaxy Z Flip7 FE</t>
         </is>
       </c>
     </row>
@@ -620,7 +619,8 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>W24 Flip</t>
+          <t>Galaxy Z Flip8
+W23</t>
         </is>
       </c>
     </row>
@@ -635,7 +635,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>W25</t>
+          <t>W23 Flip</t>
         </is>
       </c>
     </row>
@@ -650,7 +650,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>W25 Flip</t>
+          <t>W24</t>
         </is>
       </c>
     </row>
@@ -665,7 +665,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>W26</t>
+          <t>W24 Flip</t>
         </is>
       </c>
     </row>
@@ -680,7 +680,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Galaxy Z TriFold</t>
+          <t>W25</t>
         </is>
       </c>
     </row>
@@ -695,7 +695,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Galaxy Z Fold4</t>
+          <t>W25 Flip</t>
         </is>
       </c>
     </row>
@@ -710,7 +710,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Galaxy Z Fold5</t>
+          <t>W26</t>
         </is>
       </c>
     </row>
@@ -725,7 +725,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Galaxy Z Fold6</t>
+          <t>Galaxy Z TriFold</t>
         </is>
       </c>
     </row>
@@ -740,7 +740,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Galaxy Z Fold7</t>
+          <t>Galaxy Z Fold4</t>
         </is>
       </c>
     </row>
@@ -755,7 +755,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Galaxy Z Fold Special Edition</t>
+          <t>Galaxy Z Fold5</t>
         </is>
       </c>
     </row>
@@ -770,7 +770,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Galaxy Z Flip4</t>
+          <t>Galaxy Z Fold6</t>
         </is>
       </c>
     </row>
@@ -785,7 +785,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Galaxy Z Flip5</t>
+          <t>Galaxy Z Fold7</t>
         </is>
       </c>
     </row>
@@ -800,7 +800,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Galaxy Z Flip6</t>
+          <t>Galaxy Z Fold Special Edition</t>
         </is>
       </c>
     </row>
@@ -815,7 +815,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Galaxy Z Flip7</t>
+          <t>Galaxy Z Fold8</t>
         </is>
       </c>
     </row>
@@ -830,7 +830,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Galaxy Z Flip7 FE</t>
+          <t>Galaxy Z Fold8 Ultra</t>
         </is>
       </c>
     </row>
@@ -845,7 +845,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>W23</t>
+          <t>Galaxy Z Flip4</t>
         </is>
       </c>
     </row>
@@ -860,7 +860,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>W23 Flip</t>
+          <t>Galaxy Z Flip5</t>
         </is>
       </c>
     </row>
@@ -875,7 +875,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>W24</t>
+          <t>Galaxy Z Flip6</t>
         </is>
       </c>
     </row>
@@ -890,7 +890,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>W24 Flip</t>
+          <t>Galaxy Z Flip7</t>
         </is>
       </c>
     </row>
@@ -905,7 +905,7 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>W25</t>
+          <t>Galaxy Z Flip7 FE</t>
         </is>
       </c>
     </row>
@@ -920,7 +920,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>W25 Flip</t>
+          <t>Galaxy Z Flip8</t>
         </is>
       </c>
     </row>
@@ -935,7 +935,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>W26</t>
+          <t>W23</t>
         </is>
       </c>
     </row>
@@ -950,8 +950,7 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Galaxy S Series
-Galaxy S26</t>
+          <t>W23 Flip</t>
         </is>
       </c>
     </row>
@@ -966,7 +965,7 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Galaxy S26+</t>
+          <t>W24</t>
         </is>
       </c>
     </row>
@@ -981,8 +980,7 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Galaxy S26 Ultra
-Galaxy S25</t>
+          <t>W24 Flip</t>
         </is>
       </c>
     </row>
@@ -997,7 +995,7 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Galaxy S25+</t>
+          <t>W25</t>
         </is>
       </c>
     </row>
@@ -1012,7 +1010,7 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Galaxy S25 Ultra</t>
+          <t>W25 Flip</t>
         </is>
       </c>
     </row>
@@ -1027,7 +1025,7 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Galaxy S25 Edge</t>
+          <t>W26</t>
         </is>
       </c>
     </row>
@@ -1042,8 +1040,8 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Galaxy S25 FE
-Galaxy S24</t>
+          <t>Galaxy S Series
+Galaxy S26</t>
         </is>
       </c>
     </row>
@@ -1058,7 +1056,7 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Galaxy S24+</t>
+          <t>Galaxy S26+</t>
         </is>
       </c>
     </row>
@@ -1073,7 +1071,8 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Galaxy S24 Ultra</t>
+          <t>Galaxy S26 Ultra
+Galaxy S25</t>
         </is>
       </c>
     </row>
@@ -1088,8 +1087,7 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Galaxy S24 FE
-Galaxy S23</t>
+          <t>Galaxy S25+</t>
         </is>
       </c>
     </row>
@@ -1104,7 +1102,7 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Galaxy S23+</t>
+          <t>Galaxy S25 Ultra</t>
         </is>
       </c>
     </row>
@@ -1119,7 +1117,7 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Galaxy S23 Ultra</t>
+          <t>Galaxy S25 Edge</t>
         </is>
       </c>
     </row>
@@ -1134,7 +1132,8 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Galaxy S23 FE</t>
+          <t>Galaxy S25 FE
+Galaxy S24</t>
         </is>
       </c>
     </row>
@@ -1149,7 +1148,7 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Galaxy S26</t>
+          <t>Galaxy S24+</t>
         </is>
       </c>
     </row>
@@ -1164,7 +1163,7 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Galaxy S26+</t>
+          <t>Galaxy S24 Ultra</t>
         </is>
       </c>
     </row>
@@ -1179,7 +1178,8 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Galaxy S26 Ultra</t>
+          <t>Galaxy S24 FE
+Galaxy S23</t>
         </is>
       </c>
     </row>
@@ -1194,7 +1194,7 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Galaxy S25</t>
+          <t>Galaxy S23+</t>
         </is>
       </c>
     </row>
@@ -1209,7 +1209,7 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Galaxy S25+</t>
+          <t>Galaxy S23 Ultra</t>
         </is>
       </c>
     </row>
@@ -1224,7 +1224,7 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Galaxy S25 Ultra</t>
+          <t>Galaxy S23 FE</t>
         </is>
       </c>
     </row>
@@ -1239,7 +1239,7 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Galaxy S25 Edge</t>
+          <t>Galaxy S26</t>
         </is>
       </c>
     </row>
@@ -1254,7 +1254,7 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Galaxy S25 FE</t>
+          <t>Galaxy S26+</t>
         </is>
       </c>
     </row>
@@ -1269,7 +1269,7 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Galaxy S24</t>
+          <t>Galaxy S26 Ultra</t>
         </is>
       </c>
     </row>
@@ -1284,7 +1284,7 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Galaxy S24+</t>
+          <t>Galaxy S25</t>
         </is>
       </c>
     </row>
@@ -1299,7 +1299,7 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Galaxy S24 Ultra</t>
+          <t>Galaxy S25+</t>
         </is>
       </c>
     </row>
@@ -1314,7 +1314,7 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Galaxy S24 FE</t>
+          <t>Galaxy S25 Ultra</t>
         </is>
       </c>
     </row>
@@ -1329,7 +1329,7 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Galaxy S23</t>
+          <t>Galaxy S25 Edge</t>
         </is>
       </c>
     </row>
@@ -1344,7 +1344,7 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Galaxy S23+</t>
+          <t>Galaxy S25 FE</t>
         </is>
       </c>
     </row>
@@ -1359,7 +1359,7 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Galaxy S23 Ultra</t>
+          <t>Galaxy S24</t>
         </is>
       </c>
     </row>
@@ -1374,7 +1374,7 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Galaxy S23 FE</t>
+          <t>Galaxy S24+</t>
         </is>
       </c>
     </row>
@@ -1389,8 +1389,7 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Enterprise Models
-Galaxy A54 5G</t>
+          <t>Galaxy S24 Ultra</t>
         </is>
       </c>
     </row>
@@ -1405,7 +1404,7 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Galaxy A55 5G</t>
+          <t>Galaxy S24 FE</t>
         </is>
       </c>
     </row>
@@ -1420,7 +1419,7 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Galaxy A56 5G</t>
+          <t>Galaxy S23</t>
         </is>
       </c>
     </row>
@@ -1435,9 +1434,7 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Galaxy A57 5G
-Galaxy Tab Active5 Pro
-Galaxy XCover6 Pro</t>
+          <t>Galaxy S23+</t>
         </is>
       </c>
     </row>
@@ -1452,7 +1449,7 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Galaxy XCover7</t>
+          <t>Galaxy S23 Ultra</t>
         </is>
       </c>
     </row>
@@ -1467,7 +1464,7 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Galaxy XCover7 Pro</t>
+          <t>Galaxy S23 FE</t>
         </is>
       </c>
     </row>
@@ -1482,7 +1479,8 @@
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Galaxy A54 5G</t>
+          <t>Enterprise Models
+Galaxy A54 5G</t>
         </is>
       </c>
     </row>
@@ -1527,7 +1525,9 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Galaxy A57 5G</t>
+          <t>Galaxy A57 5G
+Galaxy Tab Active5 Pro
+Galaxy XCover7</t>
         </is>
       </c>
     </row>
@@ -1542,7 +1542,7 @@
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Galaxy Tab Active5 Pro</t>
+          <t>Galaxy XCover7 Pro</t>
         </is>
       </c>
     </row>
@@ -1557,7 +1557,7 @@
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Galaxy XCover6 Pro</t>
+          <t>Galaxy A54 5G</t>
         </is>
       </c>
     </row>
@@ -1572,7 +1572,7 @@
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Galaxy XCover7</t>
+          <t>Galaxy A55 5G</t>
         </is>
       </c>
     </row>
@@ -1587,7 +1587,7 @@
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Galaxy XCover7 Pro</t>
+          <t>Galaxy A56 5G</t>
         </is>
       </c>
     </row>
@@ -1597,10 +1597,70 @@
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>Quarterly</t>
+          <t>Monthly</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
+        <is>
+          <t>Galaxy A57 5G</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" s="1" t="n">
+        <v>77</v>
+      </c>
+      <c r="B79" t="inlineStr">
+        <is>
+          <t>Monthly</t>
+        </is>
+      </c>
+      <c r="C79" t="inlineStr">
+        <is>
+          <t>Galaxy Tab Active5 Pro</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" s="1" t="n">
+        <v>78</v>
+      </c>
+      <c r="B80" t="inlineStr">
+        <is>
+          <t>Monthly</t>
+        </is>
+      </c>
+      <c r="C80" t="inlineStr">
+        <is>
+          <t>Galaxy XCover7</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" s="1" t="n">
+        <v>79</v>
+      </c>
+      <c r="B81" t="inlineStr">
+        <is>
+          <t>Monthly</t>
+        </is>
+      </c>
+      <c r="C81" t="inlineStr">
+        <is>
+          <t>Galaxy XCover7 Pro</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" s="1" t="n">
+        <v>80</v>
+      </c>
+      <c r="B82" t="inlineStr">
+        <is>
+          <t>Quarterly</t>
+        </is>
+      </c>
+      <c r="C82" t="inlineStr">
         <is>
           <t>Galaxy Foldable Series
 Galaxy Z Fold3 5G
@@ -1608,67 +1668,6 @@
         </is>
       </c>
     </row>
-    <row r="79">
-      <c r="A79" s="1" t="n">
-        <v>77</v>
-      </c>
-      <c r="B79" t="inlineStr">
-        <is>
-          <t>Quarterly</t>
-        </is>
-      </c>
-      <c r="C79" t="inlineStr">
-        <is>
-          <t>Galaxy Z Fold3 5G</t>
-        </is>
-      </c>
-    </row>
-    <row r="80">
-      <c r="A80" s="1" t="n">
-        <v>78</v>
-      </c>
-      <c r="B80" t="inlineStr">
-        <is>
-          <t>Quarterly</t>
-        </is>
-      </c>
-      <c r="C80" t="inlineStr">
-        <is>
-          <t>Galaxy Z Flip3 5G</t>
-        </is>
-      </c>
-    </row>
-    <row r="81">
-      <c r="A81" s="1" t="n">
-        <v>79</v>
-      </c>
-      <c r="B81" t="inlineStr">
-        <is>
-          <t>Quarterly</t>
-        </is>
-      </c>
-      <c r="C81" t="inlineStr">
-        <is>
-          <t>Galaxy S Series
-Galaxy S22</t>
-        </is>
-      </c>
-    </row>
-    <row r="82">
-      <c r="A82" s="1" t="n">
-        <v>80</v>
-      </c>
-      <c r="B82" t="inlineStr">
-        <is>
-          <t>Quarterly</t>
-        </is>
-      </c>
-      <c r="C82" t="inlineStr">
-        <is>
-          <t>Galaxy S22+</t>
-        </is>
-      </c>
-    </row>
     <row r="83">
       <c r="A83" s="1" t="n">
         <v>81</v>
@@ -1680,8 +1679,7 @@
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Galaxy S22 Ultra
-Galaxy S21 FE 5G</t>
+          <t>Galaxy Z Fold3 5G</t>
         </is>
       </c>
     </row>
@@ -1696,7 +1694,7 @@
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Galaxy S22</t>
+          <t>Galaxy Z Flip3 5G</t>
         </is>
       </c>
     </row>
@@ -1711,7 +1709,8 @@
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Galaxy S22+</t>
+          <t>Galaxy S Series
+Galaxy S22</t>
         </is>
       </c>
     </row>
@@ -1726,7 +1725,7 @@
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Galaxy S22 Ultra</t>
+          <t>Galaxy S22+</t>
         </is>
       </c>
     </row>
@@ -1741,7 +1740,8 @@
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Galaxy S21 FE 5G</t>
+          <t>Galaxy S22 Ultra
+Galaxy S21 FE 5G</t>
         </is>
       </c>
     </row>
@@ -1756,8 +1756,7 @@
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Galaxy A Series
-Galaxy A04</t>
+          <t>Galaxy S22</t>
         </is>
       </c>
     </row>
@@ -1772,7 +1771,7 @@
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Galaxy A04s</t>
+          <t>Galaxy S22+</t>
         </is>
       </c>
     </row>
@@ -1787,7 +1786,7 @@
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Galaxy A04e</t>
+          <t>Galaxy S22 Ultra</t>
         </is>
       </c>
     </row>
@@ -1802,7 +1801,7 @@
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Galaxy A05</t>
+          <t>Galaxy S21 FE 5G</t>
         </is>
       </c>
     </row>
@@ -1817,7 +1816,8 @@
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Galaxy A05s</t>
+          <t>Galaxy A Series
+Galaxy A04</t>
         </is>
       </c>
     </row>
@@ -1832,7 +1832,7 @@
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>Galaxy A06</t>
+          <t>Galaxy A04s</t>
         </is>
       </c>
     </row>
@@ -1847,7 +1847,7 @@
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Galaxy A06 5G</t>
+          <t>Galaxy A04e</t>
         </is>
       </c>
     </row>
@@ -1862,7 +1862,7 @@
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>Galaxy A07</t>
+          <t>Galaxy A05</t>
         </is>
       </c>
     </row>
@@ -1877,8 +1877,7 @@
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>Galaxy A07 5G
-Galaxy A14</t>
+          <t>Galaxy A05s</t>
         </is>
       </c>
     </row>
@@ -1893,7 +1892,7 @@
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>Galaxy A14 5G</t>
+          <t>Galaxy A06</t>
         </is>
       </c>
     </row>
@@ -1908,7 +1907,7 @@
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>Galaxy A15</t>
+          <t>Galaxy A06 5G</t>
         </is>
       </c>
     </row>
@@ -1923,7 +1922,7 @@
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>Galaxy A15 5G</t>
+          <t>Galaxy A07</t>
         </is>
       </c>
     </row>
@@ -1938,7 +1937,8 @@
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>Galaxy A16</t>
+          <t>Galaxy A07 5G
+Galaxy A14</t>
         </is>
       </c>
     </row>
@@ -1953,7 +1953,7 @@
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>Galaxy A16 5G</t>
+          <t>Galaxy A14 5G</t>
         </is>
       </c>
     </row>
@@ -1968,7 +1968,7 @@
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>Galaxy A17</t>
+          <t>Galaxy A15</t>
         </is>
       </c>
     </row>
@@ -1983,8 +1983,7 @@
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>Galaxy A17 5G
-Galaxy A23 5G</t>
+          <t>Galaxy A15 5G</t>
         </is>
       </c>
     </row>
@@ -1999,7 +1998,7 @@
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>Galaxy A24</t>
+          <t>Galaxy A16</t>
         </is>
       </c>
     </row>
@@ -2014,7 +2013,7 @@
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>Galaxy A25 5G</t>
+          <t>Galaxy A16 5G</t>
         </is>
       </c>
     </row>
@@ -2029,7 +2028,7 @@
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>Galaxy A26 5G</t>
+          <t>Galaxy A17</t>
         </is>
       </c>
     </row>
@@ -2044,8 +2043,8 @@
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>Galaxy A27 5G
-Galaxy A33 5G</t>
+          <t>Galaxy A17 5G
+Galaxy A23 5G</t>
         </is>
       </c>
     </row>
@@ -2060,7 +2059,7 @@
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>Galaxy A34 5G</t>
+          <t>Galaxy A24</t>
         </is>
       </c>
     </row>
@@ -2075,7 +2074,7 @@
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>Galaxy A35 5G</t>
+          <t>Galaxy A25 5G</t>
         </is>
       </c>
     </row>
@@ -2090,7 +2089,7 @@
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>Galaxy A36 5G</t>
+          <t>Galaxy A26 5G</t>
         </is>
       </c>
     </row>
@@ -2105,8 +2104,8 @@
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>Galaxy A37 5G
-Galaxy A73 5G</t>
+          <t>Galaxy A27 5G
+Galaxy A33 5G</t>
         </is>
       </c>
     </row>
@@ -2121,7 +2120,7 @@
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>Galaxy A04</t>
+          <t>Galaxy A34 5G</t>
         </is>
       </c>
     </row>
@@ -2136,7 +2135,7 @@
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>Galaxy A04s</t>
+          <t>Galaxy A35 5G</t>
         </is>
       </c>
     </row>
@@ -2151,7 +2150,7 @@
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>Galaxy A04e</t>
+          <t>Galaxy A36 5G</t>
         </is>
       </c>
     </row>
@@ -2166,7 +2165,8 @@
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>Galaxy A05</t>
+          <t>Galaxy A37 5G
+Galaxy A73 5G</t>
         </is>
       </c>
     </row>
@@ -2181,7 +2181,7 @@
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>Galaxy A05s</t>
+          <t>Galaxy A04</t>
         </is>
       </c>
     </row>
@@ -2196,7 +2196,7 @@
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>Galaxy A06</t>
+          <t>Galaxy A04s</t>
         </is>
       </c>
     </row>
@@ -2211,7 +2211,7 @@
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>Galaxy A06 5G</t>
+          <t>Galaxy A04e</t>
         </is>
       </c>
     </row>
@@ -2226,7 +2226,7 @@
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>Galaxy A07</t>
+          <t>Galaxy A05</t>
         </is>
       </c>
     </row>
@@ -2241,7 +2241,7 @@
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>Galaxy A07 5G</t>
+          <t>Galaxy A05s</t>
         </is>
       </c>
     </row>
@@ -2256,7 +2256,7 @@
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>Galaxy A14</t>
+          <t>Galaxy A06</t>
         </is>
       </c>
     </row>
@@ -2271,7 +2271,7 @@
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>Galaxy A14 5G</t>
+          <t>Galaxy A06 5G</t>
         </is>
       </c>
     </row>
@@ -2286,7 +2286,7 @@
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>Galaxy A15</t>
+          <t>Galaxy A07</t>
         </is>
       </c>
     </row>
@@ -2301,7 +2301,7 @@
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>Galaxy A15 5G</t>
+          <t>Galaxy A07 5G</t>
         </is>
       </c>
     </row>
@@ -2316,7 +2316,7 @@
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>Galaxy A16</t>
+          <t>Galaxy A14</t>
         </is>
       </c>
     </row>
@@ -2331,7 +2331,7 @@
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>Galaxy A16 5G</t>
+          <t>Galaxy A14 5G</t>
         </is>
       </c>
     </row>
@@ -2346,7 +2346,7 @@
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>Galaxy A17</t>
+          <t>Galaxy A15</t>
         </is>
       </c>
     </row>
@@ -2361,7 +2361,7 @@
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>Galaxy A17 5G</t>
+          <t>Galaxy A15 5G</t>
         </is>
       </c>
     </row>
@@ -2376,7 +2376,7 @@
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>Galaxy A23 5G</t>
+          <t>Galaxy A16</t>
         </is>
       </c>
     </row>
@@ -2391,7 +2391,7 @@
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>Galaxy A24</t>
+          <t>Galaxy A16 5G</t>
         </is>
       </c>
     </row>
@@ -2406,7 +2406,7 @@
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>Galaxy A25 5G</t>
+          <t>Galaxy A17</t>
         </is>
       </c>
     </row>
@@ -2421,7 +2421,7 @@
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>Galaxy A26 5G</t>
+          <t>Galaxy A17 5G</t>
         </is>
       </c>
     </row>
@@ -2436,7 +2436,7 @@
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>Galaxy A27 5G</t>
+          <t>Galaxy A23 5G</t>
         </is>
       </c>
     </row>
@@ -2451,7 +2451,7 @@
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>Galaxy A33 5G</t>
+          <t>Galaxy A24</t>
         </is>
       </c>
     </row>
@@ -2466,7 +2466,7 @@
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>Galaxy A34 5G</t>
+          <t>Galaxy A25 5G</t>
         </is>
       </c>
     </row>
@@ -2481,7 +2481,7 @@
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>Galaxy A35 5G</t>
+          <t>Galaxy A26 5G</t>
         </is>
       </c>
     </row>
@@ -2496,7 +2496,7 @@
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>Galaxy A36 5G</t>
+          <t>Galaxy A27 5G</t>
         </is>
       </c>
     </row>
@@ -2511,7 +2511,7 @@
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t>Galaxy A37 5G</t>
+          <t>Galaxy A33 5G</t>
         </is>
       </c>
     </row>
@@ -2526,7 +2526,7 @@
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t>Galaxy A73 5G</t>
+          <t>Galaxy A34 5G</t>
         </is>
       </c>
     </row>
@@ -2541,8 +2541,7 @@
       </c>
       <c r="C140" t="inlineStr">
         <is>
-          <t>Galaxy C Series
-Galaxy C55 5G</t>
+          <t>Galaxy A35 5G</t>
         </is>
       </c>
     </row>
@@ -2557,7 +2556,7 @@
       </c>
       <c r="C141" t="inlineStr">
         <is>
-          <t>Galaxy C55 5G</t>
+          <t>Galaxy A36 5G</t>
         </is>
       </c>
     </row>
@@ -2572,8 +2571,7 @@
       </c>
       <c r="C142" t="inlineStr">
         <is>
-          <t>Galaxy M Series
-Galaxy M04</t>
+          <t>Galaxy A37 5G</t>
         </is>
       </c>
     </row>
@@ -2588,7 +2586,7 @@
       </c>
       <c r="C143" t="inlineStr">
         <is>
-          <t>Galaxy M05</t>
+          <t>Galaxy A73 5G</t>
         </is>
       </c>
     </row>
@@ -2603,7 +2601,8 @@
       </c>
       <c r="C144" t="inlineStr">
         <is>
-          <t>Galaxy M06 5G</t>
+          <t>Galaxy C Series
+Galaxy C55 5G</t>
         </is>
       </c>
     </row>
@@ -2618,8 +2617,7 @@
       </c>
       <c r="C145" t="inlineStr">
         <is>
-          <t>Galaxy M07
-Galaxy M13 5G</t>
+          <t>Galaxy C55 5G</t>
         </is>
       </c>
     </row>
@@ -2634,7 +2632,8 @@
       </c>
       <c r="C146" t="inlineStr">
         <is>
-          <t>Galaxy M14</t>
+          <t>Galaxy M Series
+Galaxy M04</t>
         </is>
       </c>
     </row>
@@ -2649,7 +2648,7 @@
       </c>
       <c r="C147" t="inlineStr">
         <is>
-          <t>Galaxy M14 5G</t>
+          <t>Galaxy M05</t>
         </is>
       </c>
     </row>
@@ -2664,7 +2663,7 @@
       </c>
       <c r="C148" t="inlineStr">
         <is>
-          <t>Galaxy M15 5G</t>
+          <t>Galaxy M06 5G</t>
         </is>
       </c>
     </row>
@@ -2679,7 +2678,8 @@
       </c>
       <c r="C149" t="inlineStr">
         <is>
-          <t>Galaxy M16 5G</t>
+          <t>Galaxy M07
+Galaxy M14</t>
         </is>
       </c>
     </row>
@@ -2694,7 +2694,7 @@
       </c>
       <c r="C150" t="inlineStr">
         <is>
-          <t>Galaxy M17 5G</t>
+          <t>Galaxy M14 5G</t>
         </is>
       </c>
     </row>
@@ -2709,8 +2709,7 @@
       </c>
       <c r="C151" t="inlineStr">
         <is>
-          <t>Galaxy M17e 5G
-Galaxy M34 5G</t>
+          <t>Galaxy M15 5G</t>
         </is>
       </c>
     </row>
@@ -2725,7 +2724,7 @@
       </c>
       <c r="C152" t="inlineStr">
         <is>
-          <t>Galaxy M35 5G</t>
+          <t>Galaxy M16 5G</t>
         </is>
       </c>
     </row>
@@ -2740,8 +2739,7 @@
       </c>
       <c r="C153" t="inlineStr">
         <is>
-          <t>Galaxy M36 5G
-Galaxy M44 5G</t>
+          <t>Galaxy M17 5G</t>
         </is>
       </c>
     </row>
@@ -2756,8 +2754,8 @@
       </c>
       <c r="C154" t="inlineStr">
         <is>
-          <t>Galaxy M47 5G
-Galaxy M54 5G</t>
+          <t>Galaxy M17e 5G
+Galaxy M34 5G</t>
         </is>
       </c>
     </row>
@@ -2772,7 +2770,7 @@
       </c>
       <c r="C155" t="inlineStr">
         <is>
-          <t>Galaxy M55 5G</t>
+          <t>Galaxy M35 5G</t>
         </is>
       </c>
     </row>
@@ -2787,7 +2785,8 @@
       </c>
       <c r="C156" t="inlineStr">
         <is>
-          <t>Galaxy M55s 5G</t>
+          <t>Galaxy M36 5G
+Galaxy M44 5G</t>
         </is>
       </c>
     </row>
@@ -2802,7 +2801,8 @@
       </c>
       <c r="C157" t="inlineStr">
         <is>
-          <t>Galaxy M56 5G</t>
+          <t>Galaxy M47 5G
+Galaxy M54 5G</t>
         </is>
       </c>
     </row>
@@ -2817,7 +2817,7 @@
       </c>
       <c r="C158" t="inlineStr">
         <is>
-          <t>Galaxy M04</t>
+          <t>Galaxy M55 5G</t>
         </is>
       </c>
     </row>
@@ -2832,7 +2832,7 @@
       </c>
       <c r="C159" t="inlineStr">
         <is>
-          <t>Galaxy M05</t>
+          <t>Galaxy M55s 5G</t>
         </is>
       </c>
     </row>
@@ -2847,7 +2847,7 @@
       </c>
       <c r="C160" t="inlineStr">
         <is>
-          <t>Galaxy M06 5G</t>
+          <t>Galaxy M56 5G</t>
         </is>
       </c>
     </row>
@@ -2862,7 +2862,7 @@
       </c>
       <c r="C161" t="inlineStr">
         <is>
-          <t>Galaxy M07</t>
+          <t>Galaxy M04</t>
         </is>
       </c>
     </row>
@@ -2877,7 +2877,7 @@
       </c>
       <c r="C162" t="inlineStr">
         <is>
-          <t>Galaxy M13 5G</t>
+          <t>Galaxy M05</t>
         </is>
       </c>
     </row>
@@ -2892,7 +2892,7 @@
       </c>
       <c r="C163" t="inlineStr">
         <is>
-          <t>Galaxy M14</t>
+          <t>Galaxy M06 5G</t>
         </is>
       </c>
     </row>
@@ -2907,7 +2907,7 @@
       </c>
       <c r="C164" t="inlineStr">
         <is>
-          <t>Galaxy M14 5G</t>
+          <t>Galaxy M07</t>
         </is>
       </c>
     </row>
@@ -2922,7 +2922,7 @@
       </c>
       <c r="C165" t="inlineStr">
         <is>
-          <t>Galaxy M15 5G</t>
+          <t>Galaxy M14</t>
         </is>
       </c>
     </row>
@@ -2937,7 +2937,7 @@
       </c>
       <c r="C166" t="inlineStr">
         <is>
-          <t>Galaxy M16 5G</t>
+          <t>Galaxy M14 5G</t>
         </is>
       </c>
     </row>
@@ -2952,7 +2952,7 @@
       </c>
       <c r="C167" t="inlineStr">
         <is>
-          <t>Galaxy M17 5G</t>
+          <t>Galaxy M15 5G</t>
         </is>
       </c>
     </row>
@@ -2967,7 +2967,7 @@
       </c>
       <c r="C168" t="inlineStr">
         <is>
-          <t>Galaxy M17e 5G</t>
+          <t>Galaxy M16 5G</t>
         </is>
       </c>
     </row>
@@ -2982,7 +2982,7 @@
       </c>
       <c r="C169" t="inlineStr">
         <is>
-          <t>Galaxy M34 5G</t>
+          <t>Galaxy M17 5G</t>
         </is>
       </c>
     </row>
@@ -2997,7 +2997,7 @@
       </c>
       <c r="C170" t="inlineStr">
         <is>
-          <t>Galaxy M35 5G</t>
+          <t>Galaxy M17e 5G</t>
         </is>
       </c>
     </row>
@@ -3012,7 +3012,7 @@
       </c>
       <c r="C171" t="inlineStr">
         <is>
-          <t>Galaxy M36 5G</t>
+          <t>Galaxy M34 5G</t>
         </is>
       </c>
     </row>
@@ -3027,7 +3027,7 @@
       </c>
       <c r="C172" t="inlineStr">
         <is>
-          <t>Galaxy M44 5G</t>
+          <t>Galaxy M35 5G</t>
         </is>
       </c>
     </row>
@@ -3042,7 +3042,7 @@
       </c>
       <c r="C173" t="inlineStr">
         <is>
-          <t>Galaxy M47 5G</t>
+          <t>Galaxy M36 5G</t>
         </is>
       </c>
     </row>
@@ -3057,7 +3057,7 @@
       </c>
       <c r="C174" t="inlineStr">
         <is>
-          <t>Galaxy M54 5G</t>
+          <t>Galaxy M44 5G</t>
         </is>
       </c>
     </row>
@@ -3072,7 +3072,7 @@
       </c>
       <c r="C175" t="inlineStr">
         <is>
-          <t>Galaxy M55 5G</t>
+          <t>Galaxy M47 5G</t>
         </is>
       </c>
     </row>
@@ -3087,7 +3087,7 @@
       </c>
       <c r="C176" t="inlineStr">
         <is>
-          <t>Galaxy M55s 5G</t>
+          <t>Galaxy M54 5G</t>
         </is>
       </c>
     </row>
@@ -3102,7 +3102,7 @@
       </c>
       <c r="C177" t="inlineStr">
         <is>
-          <t>Galaxy M56 5G</t>
+          <t>Galaxy M55 5G</t>
         </is>
       </c>
     </row>
@@ -3117,8 +3117,7 @@
       </c>
       <c r="C178" t="inlineStr">
         <is>
-          <t>Galaxy F Series
-Galaxy F04</t>
+          <t>Galaxy M55s 5G</t>
         </is>
       </c>
     </row>
@@ -3133,7 +3132,7 @@
       </c>
       <c r="C179" t="inlineStr">
         <is>
-          <t>Galaxy F05</t>
+          <t>Galaxy M56 5G</t>
         </is>
       </c>
     </row>
@@ -3148,7 +3147,8 @@
       </c>
       <c r="C180" t="inlineStr">
         <is>
-          <t>Galaxy F06 5G</t>
+          <t>Galaxy F Series
+Galaxy F04</t>
         </is>
       </c>
     </row>
@@ -3163,7 +3163,7 @@
       </c>
       <c r="C181" t="inlineStr">
         <is>
-          <t>Galaxy F07</t>
+          <t>Galaxy F05</t>
         </is>
       </c>
     </row>
@@ -3178,8 +3178,7 @@
       </c>
       <c r="C182" t="inlineStr">
         <is>
-          <t>Galaxy F70e 5G
-Galaxy F13</t>
+          <t>Galaxy F06 5G</t>
         </is>
       </c>
     </row>
@@ -3194,7 +3193,7 @@
       </c>
       <c r="C183" t="inlineStr">
         <is>
-          <t>Galaxy F14</t>
+          <t>Galaxy F07</t>
         </is>
       </c>
     </row>
@@ -3209,7 +3208,8 @@
       </c>
       <c r="C184" t="inlineStr">
         <is>
-          <t>Galaxy F14 5G</t>
+          <t>Galaxy F70e 5G
+Galaxy F14</t>
         </is>
       </c>
     </row>
@@ -3224,7 +3224,7 @@
       </c>
       <c r="C185" t="inlineStr">
         <is>
-          <t>Galaxy F15 5G</t>
+          <t>Galaxy F14 5G</t>
         </is>
       </c>
     </row>
@@ -3239,7 +3239,7 @@
       </c>
       <c r="C186" t="inlineStr">
         <is>
-          <t>Galaxy F16 5G</t>
+          <t>Galaxy F15 5G</t>
         </is>
       </c>
     </row>
@@ -3254,8 +3254,7 @@
       </c>
       <c r="C187" t="inlineStr">
         <is>
-          <t>Galaxy F17 5G
-Galaxy F34 5G</t>
+          <t>Galaxy F16 5G</t>
         </is>
       </c>
     </row>
@@ -3270,8 +3269,8 @@
       </c>
       <c r="C188" t="inlineStr">
         <is>
-          <t>Galaxy F36 5G
-Galaxy F54 5G</t>
+          <t>Galaxy F17 5G
+Galaxy F34 5G</t>
         </is>
       </c>
     </row>
@@ -3286,7 +3285,8 @@
       </c>
       <c r="C189" t="inlineStr">
         <is>
-          <t>Galaxy F55 5G</t>
+          <t>Galaxy F36 5G
+Galaxy F54 5G</t>
         </is>
       </c>
     </row>
@@ -3301,7 +3301,7 @@
       </c>
       <c r="C190" t="inlineStr">
         <is>
-          <t>Galaxy F56 5G</t>
+          <t>Galaxy F55 5G</t>
         </is>
       </c>
     </row>
@@ -3316,7 +3316,7 @@
       </c>
       <c r="C191" t="inlineStr">
         <is>
-          <t>Galaxy F04</t>
+          <t>Galaxy F56 5G</t>
         </is>
       </c>
     </row>
@@ -3331,7 +3331,7 @@
       </c>
       <c r="C192" t="inlineStr">
         <is>
-          <t>Galaxy F05</t>
+          <t>Galaxy F04</t>
         </is>
       </c>
     </row>
@@ -3346,7 +3346,7 @@
       </c>
       <c r="C193" t="inlineStr">
         <is>
-          <t>Galaxy F06 5G</t>
+          <t>Galaxy F05</t>
         </is>
       </c>
     </row>
@@ -3361,7 +3361,7 @@
       </c>
       <c r="C194" t="inlineStr">
         <is>
-          <t>Galaxy F07</t>
+          <t>Galaxy F06 5G</t>
         </is>
       </c>
     </row>
@@ -3376,7 +3376,7 @@
       </c>
       <c r="C195" t="inlineStr">
         <is>
-          <t>Galaxy F70e 5G</t>
+          <t>Galaxy F07</t>
         </is>
       </c>
     </row>
@@ -3391,7 +3391,7 @@
       </c>
       <c r="C196" t="inlineStr">
         <is>
-          <t>Galaxy F13</t>
+          <t>Galaxy F70e 5G</t>
         </is>
       </c>
     </row>
@@ -4151,7 +4151,7 @@
       </c>
       <c r="C246" t="inlineStr">
         <is>
-          <t>Galaxy A53 5G</t>
+          <t>Galaxy XCover6 Pro</t>
         </is>
       </c>
     </row>
@@ -4166,7 +4166,7 @@
       </c>
       <c r="C247" t="inlineStr">
         <is>
-          <t>Galaxy Tab Active4 Pro</t>
+          <t>Galaxy A53 5G</t>
         </is>
       </c>
     </row>
@@ -4181,7 +4181,7 @@
       </c>
       <c r="C248" t="inlineStr">
         <is>
-          <t>Galaxy Tab Active5</t>
+          <t>Galaxy Tab Active4 Pro</t>
         </is>
       </c>
     </row>
@@ -4196,7 +4196,7 @@
       </c>
       <c r="C249" t="inlineStr">
         <is>
-          <t>Galaxy XCover5</t>
+          <t>Galaxy Tab Active5</t>
         </is>
       </c>
     </row>
@@ -4211,8 +4211,7 @@
       </c>
       <c r="C250" t="inlineStr">
         <is>
-          <t>Galaxy Watch Series
-Galaxy Watch8 40mm</t>
+          <t>Galaxy XCover5</t>
         </is>
       </c>
     </row>
@@ -4227,7 +4226,7 @@
       </c>
       <c r="C251" t="inlineStr">
         <is>
-          <t>Galaxy Watch8 44mm</t>
+          <t>Galaxy XCover6 Pro</t>
         </is>
       </c>
     </row>
@@ -4242,9 +4241,8 @@
       </c>
       <c r="C252" t="inlineStr">
         <is>
-          <t>Galaxy Watch8 Classic 46mm
-Galaxy Watch Ultra
-Galaxy Watch7 40mm</t>
+          <t>Galaxy Watch Series
+Galaxy Watch9 40mm</t>
         </is>
       </c>
     </row>
@@ -4259,73 +4257,75 @@
       </c>
       <c r="C253" t="inlineStr">
         <is>
+          <t>Galaxy Watch9 44mm
+Galaxy Watch8 40mm</t>
+        </is>
+      </c>
+    </row>
+    <row r="254">
+      <c r="A254" s="1" t="n">
+        <v>252</v>
+      </c>
+      <c r="B254" t="inlineStr">
+        <is>
+          <t>Quarterly</t>
+        </is>
+      </c>
+      <c r="C254" t="inlineStr">
+        <is>
+          <t>Galaxy Watch8 44mm</t>
+        </is>
+      </c>
+    </row>
+    <row r="255">
+      <c r="A255" s="1" t="n">
+        <v>253</v>
+      </c>
+      <c r="B255" t="inlineStr">
+        <is>
+          <t>Quarterly</t>
+        </is>
+      </c>
+      <c r="C255" t="inlineStr">
+        <is>
+          <t>Galaxy Watch8 Classic 46mm
+Galaxy Watch Ultra</t>
+        </is>
+      </c>
+    </row>
+    <row r="256">
+      <c r="A256" s="1" t="n">
+        <v>254</v>
+      </c>
+      <c r="B256" t="inlineStr">
+        <is>
+          <t>Quarterly</t>
+        </is>
+      </c>
+      <c r="C256" t="inlineStr">
+        <is>
+          <t>Galaxy Watch Ultra2
+Galaxy Watch7 40mm</t>
+        </is>
+      </c>
+    </row>
+    <row r="257">
+      <c r="A257" s="1" t="n">
+        <v>255</v>
+      </c>
+      <c r="B257" t="inlineStr">
+        <is>
+          <t>Quarterly</t>
+        </is>
+      </c>
+      <c r="C257" t="inlineStr">
+        <is>
           <t>Galaxy Watch7 44mm
 Galaxy Watch FE
 Galaxy Watch6 40mm</t>
         </is>
       </c>
     </row>
-    <row r="254">
-      <c r="A254" s="1" t="n">
-        <v>252</v>
-      </c>
-      <c r="B254" t="inlineStr">
-        <is>
-          <t>Quarterly</t>
-        </is>
-      </c>
-      <c r="C254" t="inlineStr">
-        <is>
-          <t>Galaxy Watch6 44mm</t>
-        </is>
-      </c>
-    </row>
-    <row r="255">
-      <c r="A255" s="1" t="n">
-        <v>253</v>
-      </c>
-      <c r="B255" t="inlineStr">
-        <is>
-          <t>Quarterly</t>
-        </is>
-      </c>
-      <c r="C255" t="inlineStr">
-        <is>
-          <t>Galaxy Watch6 Classic 43mm</t>
-        </is>
-      </c>
-    </row>
-    <row r="256">
-      <c r="A256" s="1" t="n">
-        <v>254</v>
-      </c>
-      <c r="B256" t="inlineStr">
-        <is>
-          <t>Quarterly</t>
-        </is>
-      </c>
-      <c r="C256" t="inlineStr">
-        <is>
-          <t>Galaxy Watch6 Classic 47mm
-Galaxy Watch5 40mm</t>
-        </is>
-      </c>
-    </row>
-    <row r="257">
-      <c r="A257" s="1" t="n">
-        <v>255</v>
-      </c>
-      <c r="B257" t="inlineStr">
-        <is>
-          <t>Quarterly</t>
-        </is>
-      </c>
-      <c r="C257" t="inlineStr">
-        <is>
-          <t>Galaxy Watch5 44mm</t>
-        </is>
-      </c>
-    </row>
     <row r="258">
       <c r="A258" s="1" t="n">
         <v>256</v>
@@ -4337,8 +4337,7 @@
       </c>
       <c r="C258" t="inlineStr">
         <is>
-          <t>Galaxy Watch5 Pro
-Galaxy Watch4 40mm</t>
+          <t>Galaxy Watch6 44mm</t>
         </is>
       </c>
     </row>
@@ -4353,7 +4352,7 @@
       </c>
       <c r="C259" t="inlineStr">
         <is>
-          <t>Galaxy Watch4 44mm</t>
+          <t>Galaxy Watch6 Classic 43mm</t>
         </is>
       </c>
     </row>
@@ -4368,7 +4367,8 @@
       </c>
       <c r="C260" t="inlineStr">
         <is>
-          <t>Galaxy Watch4 Classic 42mm</t>
+          <t>Galaxy Watch6 Classic 47mm
+Galaxy Watch5 40mm</t>
         </is>
       </c>
     </row>
@@ -4383,7 +4383,7 @@
       </c>
       <c r="C261" t="inlineStr">
         <is>
-          <t>Galaxy Watch4 Classic 46mm</t>
+          <t>Galaxy Watch5 44mm</t>
         </is>
       </c>
     </row>
@@ -4398,7 +4398,8 @@
       </c>
       <c r="C262" t="inlineStr">
         <is>
-          <t>Galaxy Watch8 40mm</t>
+          <t>Galaxy Watch5 Pro
+Galaxy Watch4 40mm</t>
         </is>
       </c>
     </row>
@@ -4413,7 +4414,7 @@
       </c>
       <c r="C263" t="inlineStr">
         <is>
-          <t>Galaxy Watch8 44mm</t>
+          <t>Galaxy Watch4 44mm</t>
         </is>
       </c>
     </row>
@@ -4428,7 +4429,7 @@
       </c>
       <c r="C264" t="inlineStr">
         <is>
-          <t>Galaxy Watch8 Classic 46mm</t>
+          <t>Galaxy Watch4 Classic 42mm</t>
         </is>
       </c>
     </row>
@@ -4443,7 +4444,7 @@
       </c>
       <c r="C265" t="inlineStr">
         <is>
-          <t>Galaxy Watch Ultra</t>
+          <t>Galaxy Watch4 Classic 46mm</t>
         </is>
       </c>
     </row>
@@ -4458,7 +4459,7 @@
       </c>
       <c r="C266" t="inlineStr">
         <is>
-          <t>Galaxy Watch7 40mm</t>
+          <t>Galaxy Watch9 40mm</t>
         </is>
       </c>
     </row>
@@ -4473,7 +4474,7 @@
       </c>
       <c r="C267" t="inlineStr">
         <is>
-          <t>Galaxy Watch7 44mm</t>
+          <t>Galaxy Watch9 44mm</t>
         </is>
       </c>
     </row>
@@ -4488,7 +4489,7 @@
       </c>
       <c r="C268" t="inlineStr">
         <is>
-          <t>Galaxy Watch FE</t>
+          <t>Galaxy Watch8 40mm</t>
         </is>
       </c>
     </row>
@@ -4503,7 +4504,7 @@
       </c>
       <c r="C269" t="inlineStr">
         <is>
-          <t>Galaxy Watch6 40mm</t>
+          <t>Galaxy Watch8 44mm</t>
         </is>
       </c>
     </row>
@@ -4518,7 +4519,7 @@
       </c>
       <c r="C270" t="inlineStr">
         <is>
-          <t>Galaxy Watch6 44mm</t>
+          <t>Galaxy Watch8 Classic 46mm</t>
         </is>
       </c>
     </row>
@@ -4533,7 +4534,7 @@
       </c>
       <c r="C271" t="inlineStr">
         <is>
-          <t>Galaxy Watch6 Classic 43mm</t>
+          <t>Galaxy Watch Ultra</t>
         </is>
       </c>
     </row>
@@ -4548,7 +4549,7 @@
       </c>
       <c r="C272" t="inlineStr">
         <is>
-          <t>Galaxy Watch6 Classic 47mm</t>
+          <t>Galaxy Watch Ultra2</t>
         </is>
       </c>
     </row>
@@ -4563,7 +4564,7 @@
       </c>
       <c r="C273" t="inlineStr">
         <is>
-          <t>Galaxy Watch5 40mm</t>
+          <t>Galaxy Watch7 40mm</t>
         </is>
       </c>
     </row>
@@ -4578,7 +4579,7 @@
       </c>
       <c r="C274" t="inlineStr">
         <is>
-          <t>Galaxy Watch5 44mm</t>
+          <t>Galaxy Watch7 44mm</t>
         </is>
       </c>
     </row>
@@ -4593,7 +4594,7 @@
       </c>
       <c r="C275" t="inlineStr">
         <is>
-          <t>Galaxy Watch5 Pro</t>
+          <t>Galaxy Watch FE</t>
         </is>
       </c>
     </row>
@@ -4608,7 +4609,7 @@
       </c>
       <c r="C276" t="inlineStr">
         <is>
-          <t>Galaxy Watch4 40mm</t>
+          <t>Galaxy Watch6 40mm</t>
         </is>
       </c>
     </row>
@@ -4623,7 +4624,7 @@
       </c>
       <c r="C277" t="inlineStr">
         <is>
-          <t>Galaxy Watch4 44mm</t>
+          <t>Galaxy Watch6 44mm</t>
         </is>
       </c>
     </row>
@@ -4638,7 +4639,7 @@
       </c>
       <c r="C278" t="inlineStr">
         <is>
-          <t>Galaxy Watch4 Classic 42mm</t>
+          <t>Galaxy Watch6 Classic 43mm</t>
         </is>
       </c>
     </row>
@@ -4653,7 +4654,7 @@
       </c>
       <c r="C279" t="inlineStr">
         <is>
-          <t>Galaxy Watch4 Classic 46mm</t>
+          <t>Galaxy Watch6 Classic 47mm</t>
         </is>
       </c>
     </row>
@@ -4668,8 +4669,7 @@
       </c>
       <c r="C280" t="inlineStr">
         <is>
-          <t>Galaxy XR Series
-Galaxy XR</t>
+          <t>Galaxy Watch5 40mm</t>
         </is>
       </c>
     </row>
@@ -4684,7 +4684,7 @@
       </c>
       <c r="C281" t="inlineStr">
         <is>
-          <t>Galaxy XR</t>
+          <t>Galaxy Watch5 44mm</t>
         </is>
       </c>
     </row>
@@ -4694,13 +4694,12 @@
       </c>
       <c r="B282" t="inlineStr">
         <is>
-          <t>No Information</t>
+          <t>Quarterly</t>
         </is>
       </c>
       <c r="C282" t="inlineStr">
         <is>
-          <t>Galaxy Book Series
-Galaxy Book4 Ultra</t>
+          <t>Galaxy Watch5 Pro</t>
         </is>
       </c>
     </row>
@@ -4710,12 +4709,12 @@
       </c>
       <c r="B283" t="inlineStr">
         <is>
-          <t>No Information</t>
+          <t>Quarterly</t>
         </is>
       </c>
       <c r="C283" t="inlineStr">
         <is>
-          <t>Galaxy Book4 Pro</t>
+          <t>Galaxy Watch4 40mm</t>
         </is>
       </c>
     </row>
@@ -4725,12 +4724,12 @@
       </c>
       <c r="B284" t="inlineStr">
         <is>
-          <t>No Information</t>
+          <t>Quarterly</t>
         </is>
       </c>
       <c r="C284" t="inlineStr">
         <is>
-          <t>Galaxy Book4 Pro 360</t>
+          <t>Galaxy Watch4 44mm</t>
         </is>
       </c>
     </row>
@@ -4740,12 +4739,12 @@
       </c>
       <c r="B285" t="inlineStr">
         <is>
-          <t>No Information</t>
+          <t>Quarterly</t>
         </is>
       </c>
       <c r="C285" t="inlineStr">
         <is>
-          <t>Galaxy Book4 360</t>
+          <t>Galaxy Watch4 Classic 42mm</t>
         </is>
       </c>
     </row>
@@ -4755,12 +4754,12 @@
       </c>
       <c r="B286" t="inlineStr">
         <is>
-          <t>No Information</t>
+          <t>Quarterly</t>
         </is>
       </c>
       <c r="C286" t="inlineStr">
         <is>
-          <t>Galaxy Book4</t>
+          <t>Galaxy Watch4 Classic 46mm</t>
         </is>
       </c>
     </row>
@@ -4770,12 +4769,13 @@
       </c>
       <c r="B287" t="inlineStr">
         <is>
-          <t>No Information</t>
+          <t>Quarterly</t>
         </is>
       </c>
       <c r="C287" t="inlineStr">
         <is>
-          <t>Galaxy Book4 Ultra</t>
+          <t>Galaxy XR Series
+Galaxy XR</t>
         </is>
       </c>
     </row>
@@ -4785,12 +4785,12 @@
       </c>
       <c r="B288" t="inlineStr">
         <is>
-          <t>No Information</t>
+          <t>Quarterly</t>
         </is>
       </c>
       <c r="C288" t="inlineStr">
         <is>
-          <t>Galaxy Book4 Pro</t>
+          <t>Galaxy XR</t>
         </is>
       </c>
     </row>
@@ -4805,7 +4805,8 @@
       </c>
       <c r="C289" t="inlineStr">
         <is>
-          <t>Galaxy Book4 Pro 360</t>
+          <t>Galaxy Book Series
+Galaxy Book4 Ultra</t>
         </is>
       </c>
     </row>
@@ -4820,7 +4821,7 @@
       </c>
       <c r="C290" t="inlineStr">
         <is>
-          <t>Galaxy Book4 360</t>
+          <t>Galaxy Book4 Pro</t>
         </is>
       </c>
     </row>
@@ -4834,6 +4835,111 @@
         </is>
       </c>
       <c r="C291" t="inlineStr">
+        <is>
+          <t>Galaxy Book4 Pro 360</t>
+        </is>
+      </c>
+    </row>
+    <row r="292">
+      <c r="A292" s="1" t="n">
+        <v>290</v>
+      </c>
+      <c r="B292" t="inlineStr">
+        <is>
+          <t>No Information</t>
+        </is>
+      </c>
+      <c r="C292" t="inlineStr">
+        <is>
+          <t>Galaxy Book4 360</t>
+        </is>
+      </c>
+    </row>
+    <row r="293">
+      <c r="A293" s="1" t="n">
+        <v>291</v>
+      </c>
+      <c r="B293" t="inlineStr">
+        <is>
+          <t>No Information</t>
+        </is>
+      </c>
+      <c r="C293" t="inlineStr">
+        <is>
+          <t>Galaxy Book4</t>
+        </is>
+      </c>
+    </row>
+    <row r="294">
+      <c r="A294" s="1" t="n">
+        <v>292</v>
+      </c>
+      <c r="B294" t="inlineStr">
+        <is>
+          <t>No Information</t>
+        </is>
+      </c>
+      <c r="C294" t="inlineStr">
+        <is>
+          <t>Galaxy Book4 Ultra</t>
+        </is>
+      </c>
+    </row>
+    <row r="295">
+      <c r="A295" s="1" t="n">
+        <v>293</v>
+      </c>
+      <c r="B295" t="inlineStr">
+        <is>
+          <t>No Information</t>
+        </is>
+      </c>
+      <c r="C295" t="inlineStr">
+        <is>
+          <t>Galaxy Book4 Pro</t>
+        </is>
+      </c>
+    </row>
+    <row r="296">
+      <c r="A296" s="1" t="n">
+        <v>294</v>
+      </c>
+      <c r="B296" t="inlineStr">
+        <is>
+          <t>No Information</t>
+        </is>
+      </c>
+      <c r="C296" t="inlineStr">
+        <is>
+          <t>Galaxy Book4 Pro 360</t>
+        </is>
+      </c>
+    </row>
+    <row r="297">
+      <c r="A297" s="1" t="n">
+        <v>295</v>
+      </c>
+      <c r="B297" t="inlineStr">
+        <is>
+          <t>No Information</t>
+        </is>
+      </c>
+      <c r="C297" t="inlineStr">
+        <is>
+          <t>Galaxy Book4 360</t>
+        </is>
+      </c>
+    </row>
+    <row r="298">
+      <c r="A298" s="1" t="n">
+        <v>296</v>
+      </c>
+      <c r="B298" t="inlineStr">
+        <is>
+          <t>No Information</t>
+        </is>
+      </c>
+      <c r="C298" t="inlineStr">
         <is>
           <t>Galaxy Book4</t>
         </is>
